--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123798135</v>
+        <v>123798142</v>
       </c>
       <c r="B2" t="n">
-        <v>106058</v>
+        <v>105505</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>224098</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,19 +718,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721199</v>
+        <v>721172</v>
       </c>
       <c r="R2" t="n">
-        <v>6380430</v>
+        <v>6380349</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,6 +767,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sumpigare del.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,7 +783,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123798132</v>
+        <v>123798148</v>
       </c>
       <c r="B3" t="n">
-        <v>98374</v>
+        <v>98480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,7 +836,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721130</v>
+        <v>721136</v>
       </c>
       <c r="R3" t="n">
-        <v>6380537</v>
+        <v>6380323</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,11 +891,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123798241</v>
+        <v>123798135</v>
       </c>
       <c r="B4" t="n">
-        <v>95167</v>
+        <v>106076</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +934,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -957,7 +962,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721136</v>
+        <v>721199</v>
       </c>
       <c r="R4" t="n">
-        <v>6380323</v>
+        <v>6380430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1020,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123798105</v>
+        <v>123798126</v>
       </c>
       <c r="B5" t="n">
-        <v>98374</v>
+        <v>106076</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,52 +1050,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721376</v>
+        <v>721153</v>
       </c>
       <c r="R5" t="n">
-        <v>6380469</v>
+        <v>6380582</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1125,6 +1116,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1136,7 +1132,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog fuktig med inslag av ask.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1154,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123798140</v>
+        <v>123798732</v>
       </c>
       <c r="B6" t="n">
-        <v>98374</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,25 +1162,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1192,29 +1188,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721199</v>
+        <v>720940</v>
       </c>
       <c r="R6" t="n">
-        <v>6380430</v>
+        <v>6380132</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1257,7 +1248,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog mjed äldre träd.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1278,7 +1269,7 @@
         <v>123798141</v>
       </c>
       <c r="B7" t="n">
-        <v>98374</v>
+        <v>98480</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1399,7 +1390,7 @@
         <v>123798128</v>
       </c>
       <c r="B8" t="n">
-        <v>106058</v>
+        <v>106076</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1503,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123798126</v>
+        <v>123798140</v>
       </c>
       <c r="B9" t="n">
-        <v>106058</v>
+        <v>98480</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,38 +1506,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721153</v>
+        <v>721199</v>
       </c>
       <c r="R9" t="n">
-        <v>6380582</v>
+        <v>6380430</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1581,11 +1586,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarskog fuktig med inslag av ask.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798732</v>
+        <v>123798127</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
+        <v>98524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,25 +1627,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1653,24 +1653,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720940</v>
+        <v>721153</v>
       </c>
       <c r="R10" t="n">
-        <v>6380132</v>
+        <v>6380582</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1713,7 +1718,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mjed äldre träd.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1731,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123798127</v>
+        <v>123798105</v>
       </c>
       <c r="B11" t="n">
-        <v>98418</v>
+        <v>98480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1752,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721153</v>
+        <v>721376</v>
       </c>
       <c r="R11" t="n">
-        <v>6380582</v>
+        <v>6380469</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1852,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123798142</v>
+        <v>123798241</v>
       </c>
       <c r="B12" t="n">
-        <v>105489</v>
+        <v>95173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,36 +1873,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224098</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721172</v>
+        <v>721136</v>
       </c>
       <c r="R12" t="n">
-        <v>6380349</v>
+        <v>6380323</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1944,11 +1944,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Sumpigare del.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1960,7 +1955,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1978,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123798148</v>
+        <v>123798132</v>
       </c>
       <c r="B13" t="n">
-        <v>98374</v>
+        <v>98480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,7 +2008,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2032,13 +2027,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721136</v>
+        <v>721130</v>
       </c>
       <c r="R13" t="n">
-        <v>6380323</v>
+        <v>6380537</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,6 +2063,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123798142</v>
+        <v>123798140</v>
       </c>
       <c r="B2" t="n">
-        <v>105505</v>
+        <v>98482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224098</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721172</v>
+        <v>721199</v>
       </c>
       <c r="R2" t="n">
-        <v>6380349</v>
+        <v>6380430</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,11 +765,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sumpigare del.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123798148</v>
+        <v>123798142</v>
       </c>
       <c r="B3" t="n">
-        <v>98480</v>
+        <v>105507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>224098</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721136</v>
+        <v>721172</v>
       </c>
       <c r="R3" t="n">
-        <v>6380323</v>
+        <v>6380349</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -891,6 +886,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sumpigare del.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123798135</v>
+        <v>123798127</v>
       </c>
       <c r="B4" t="n">
-        <v>106076</v>
+        <v>98526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,25 +934,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,19 +965,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721199</v>
+        <v>721153</v>
       </c>
       <c r="R4" t="n">
-        <v>6380430</v>
+        <v>6380582</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,7 +1025,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1038,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123798126</v>
+        <v>123798141</v>
       </c>
       <c r="B5" t="n">
-        <v>106076</v>
+        <v>98482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,38 +1055,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721153</v>
+        <v>721205</v>
       </c>
       <c r="R5" t="n">
-        <v>6380582</v>
+        <v>6380399</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,11 +1135,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1132,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarskog fuktig med inslag av ask.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,7 +1167,7 @@
         <v>123798732</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1266,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123798141</v>
+        <v>123798132</v>
       </c>
       <c r="B7" t="n">
-        <v>98480</v>
+        <v>98482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,7 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721205</v>
+        <v>721130</v>
       </c>
       <c r="R7" t="n">
-        <v>6380399</v>
+        <v>6380537</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,6 +1370,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123798128</v>
+        <v>123798105</v>
       </c>
       <c r="B8" t="n">
-        <v>106076</v>
+        <v>98482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,41 +1418,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721130</v>
+        <v>721376</v>
       </c>
       <c r="R8" t="n">
-        <v>6380560</v>
+        <v>6380469</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123798140</v>
+        <v>123798148</v>
       </c>
       <c r="B9" t="n">
-        <v>98480</v>
+        <v>98482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,13 +1581,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721199</v>
+        <v>721136</v>
       </c>
       <c r="R9" t="n">
-        <v>6380430</v>
+        <v>6380323</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798127</v>
+        <v>123798135</v>
       </c>
       <c r="B10" t="n">
-        <v>98524</v>
+        <v>106078</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,25 +1660,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1658,24 +1691,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721153</v>
+        <v>721199</v>
       </c>
       <c r="R10" t="n">
-        <v>6380582</v>
+        <v>6380430</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1718,7 +1746,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1736,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123798105</v>
+        <v>123798126</v>
       </c>
       <c r="B11" t="n">
-        <v>98480</v>
+        <v>106078</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,52 +1776,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721376</v>
+        <v>721153</v>
       </c>
       <c r="R11" t="n">
-        <v>6380469</v>
+        <v>6380582</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,6 +1842,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1839,7 +1858,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog fuktig med inslag av ask.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1860,7 +1879,7 @@
         <v>123798241</v>
       </c>
       <c r="B12" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1973,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123798132</v>
+        <v>123798128</v>
       </c>
       <c r="B13" t="n">
-        <v>98480</v>
+        <v>106078</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,42 +2004,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
@@ -2030,10 +2035,10 @@
         <v>721130</v>
       </c>
       <c r="R13" t="n">
-        <v>6380537</v>
+        <v>6380560</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2063,11 +2068,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -1406,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123798105</v>
+        <v>123798135</v>
       </c>
       <c r="B8" t="n">
-        <v>98482</v>
+        <v>106078</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,25 +1418,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1449,24 +1449,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721376</v>
+        <v>721199</v>
       </c>
       <c r="R8" t="n">
-        <v>6380469</v>
+        <v>6380430</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,7 +1504,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1527,7 +1522,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123798148</v>
+        <v>123798105</v>
       </c>
       <c r="B9" t="n">
         <v>98482</v>
@@ -1581,13 +1576,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721136</v>
+        <v>721376</v>
       </c>
       <c r="R9" t="n">
-        <v>6380323</v>
+        <v>6380469</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1648,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798135</v>
+        <v>123798148</v>
       </c>
       <c r="B10" t="n">
-        <v>106078</v>
+        <v>98482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,25 +1655,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1691,19 +1686,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721199</v>
+        <v>721136</v>
       </c>
       <c r="R10" t="n">
-        <v>6380430</v>
+        <v>6380323</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -1406,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123798135</v>
+        <v>123798105</v>
       </c>
       <c r="B8" t="n">
-        <v>106078</v>
+        <v>98482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,25 +1418,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1449,19 +1449,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721199</v>
+        <v>721376</v>
       </c>
       <c r="R8" t="n">
-        <v>6380430</v>
+        <v>6380469</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1504,7 +1509,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1522,7 +1527,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123798105</v>
+        <v>123798148</v>
       </c>
       <c r="B9" t="n">
         <v>98482</v>
@@ -1576,13 +1581,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721376</v>
+        <v>721136</v>
       </c>
       <c r="R9" t="n">
-        <v>6380469</v>
+        <v>6380323</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1643,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798148</v>
+        <v>123798135</v>
       </c>
       <c r="B10" t="n">
-        <v>98482</v>
+        <v>106078</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,25 +1660,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1686,24 +1691,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721136</v>
+        <v>721199</v>
       </c>
       <c r="R10" t="n">
-        <v>6380323</v>
+        <v>6380430</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123798140</v>
+        <v>123798141</v>
       </c>
       <c r="B2" t="n">
-        <v>98482</v>
+        <v>98057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721199</v>
+        <v>721205</v>
       </c>
       <c r="R2" t="n">
-        <v>6380430</v>
+        <v>6380399</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123798142</v>
+        <v>123798732</v>
       </c>
       <c r="B3" t="n">
-        <v>105507</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,55 +808,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224098</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721172</v>
+        <v>720940</v>
       </c>
       <c r="R3" t="n">
-        <v>6380349</v>
+        <v>6380132</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,11 +883,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sumpigare del.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -904,7 +894,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog mjed äldre träd.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123798127</v>
+        <v>123798142</v>
       </c>
       <c r="B4" t="n">
-        <v>98526</v>
+        <v>105082</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,26 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>224098</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,13 +966,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721153</v>
+        <v>721172</v>
       </c>
       <c r="R4" t="n">
-        <v>6380582</v>
+        <v>6380349</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,6 +1002,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sumpigare del.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123798141</v>
+        <v>123798135</v>
       </c>
       <c r="B5" t="n">
-        <v>98482</v>
+        <v>105653</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,30 +1050,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1086,24 +1081,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721205</v>
+        <v>721199</v>
       </c>
       <c r="R5" t="n">
-        <v>6380399</v>
+        <v>6380430</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1136,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1164,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123798732</v>
+        <v>123798128</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>105653</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,47 +1166,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720940</v>
+        <v>721130</v>
       </c>
       <c r="R6" t="n">
-        <v>6380132</v>
+        <v>6380560</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1262,7 +1243,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mjed äldre träd.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1280,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123798132</v>
+        <v>123798126</v>
       </c>
       <c r="B7" t="n">
-        <v>98482</v>
+        <v>105653</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,52 +1273,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721130</v>
+        <v>721153</v>
       </c>
       <c r="R7" t="n">
-        <v>6380537</v>
+        <v>6380582</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1374,7 +1341,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ängsbarrskog.</t>
+          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,7 +1355,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog fuktig med inslag av ask.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1406,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123798105</v>
+        <v>123798148</v>
       </c>
       <c r="B8" t="n">
-        <v>98482</v>
+        <v>98057</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1460,13 +1427,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721376</v>
+        <v>721136</v>
       </c>
       <c r="R8" t="n">
-        <v>6380469</v>
+        <v>6380323</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1527,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123798148</v>
+        <v>123798241</v>
       </c>
       <c r="B9" t="n">
-        <v>98482</v>
+        <v>95683</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1567,12 +1534,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1587,7 +1549,7 @@
         <v>6380323</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1630,7 +1592,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1648,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798135</v>
+        <v>123798132</v>
       </c>
       <c r="B10" t="n">
-        <v>106078</v>
+        <v>98057</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,30 +1622,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1691,19 +1653,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721199</v>
+        <v>721130</v>
       </c>
       <c r="R10" t="n">
-        <v>6380430</v>
+        <v>6380537</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1735,6 +1702,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1746,7 +1718,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1764,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123798126</v>
+        <v>123798127</v>
       </c>
       <c r="B11" t="n">
-        <v>106078</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,28 +1748,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
@@ -1842,11 +1828,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1858,7 +1839,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarskog fuktig med inslag av ask.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1876,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123798241</v>
+        <v>123798140</v>
       </c>
       <c r="B12" t="n">
-        <v>95175</v>
+        <v>98057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1892,21 +1873,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1916,7 +1897,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1925,13 +1911,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721136</v>
+        <v>721199</v>
       </c>
       <c r="R12" t="n">
-        <v>6380323</v>
+        <v>6380430</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1974,7 +1960,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1992,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123798128</v>
+        <v>123798105</v>
       </c>
       <c r="B13" t="n">
-        <v>106078</v>
+        <v>98057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,41 +1990,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721130</v>
+        <v>721376</v>
       </c>
       <c r="R13" t="n">
-        <v>6380560</v>
+        <v>6380469</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123798141</v>
+        <v>123798105</v>
       </c>
       <c r="B2" t="n">
         <v>98057</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721205</v>
+        <v>721376</v>
       </c>
       <c r="R2" t="n">
-        <v>6380399</v>
+        <v>6380469</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123798732</v>
+        <v>123798127</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,24 +834,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720940</v>
+        <v>721153</v>
       </c>
       <c r="R3" t="n">
-        <v>6380132</v>
+        <v>6380582</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,7 +899,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mjed äldre träd.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123798142</v>
+        <v>123798141</v>
       </c>
       <c r="B4" t="n">
-        <v>105082</v>
+        <v>98057</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,26 +933,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224098</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,13 +971,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721172</v>
+        <v>721205</v>
       </c>
       <c r="R4" t="n">
-        <v>6380349</v>
+        <v>6380399</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,11 +1007,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sumpigare del.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123798135</v>
+        <v>123798140</v>
       </c>
       <c r="B5" t="n">
-        <v>105653</v>
+        <v>98057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,25 +1050,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1079,6 +1079,11 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1093,7 +1098,7 @@
         <v>6380430</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,7 +1141,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1154,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123798128</v>
+        <v>123798732</v>
       </c>
       <c r="B6" t="n">
-        <v>105653</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,38 +1171,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721130</v>
+        <v>720940</v>
       </c>
       <c r="R6" t="n">
-        <v>6380560</v>
+        <v>6380132</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,7 +1257,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog mjed äldre träd.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1261,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123798126</v>
+        <v>123798132</v>
       </c>
       <c r="B7" t="n">
-        <v>105653</v>
+        <v>98057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,38 +1287,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721153</v>
+        <v>721130</v>
       </c>
       <c r="R7" t="n">
-        <v>6380582</v>
+        <v>6380537</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,7 +1369,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1383,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarskog fuktig med inslag av ask.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1373,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123798148</v>
+        <v>123798128</v>
       </c>
       <c r="B8" t="n">
-        <v>98057</v>
+        <v>105653</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,55 +1413,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721136</v>
+        <v>721130</v>
       </c>
       <c r="R8" t="n">
-        <v>6380323</v>
+        <v>6380560</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123798241</v>
+        <v>123798148</v>
       </c>
       <c r="B9" t="n">
-        <v>95683</v>
+        <v>98057</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1524,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1534,7 +1548,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1549,7 +1568,7 @@
         <v>6380323</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,7 +1611,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1610,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798132</v>
+        <v>123798142</v>
       </c>
       <c r="B10" t="n">
-        <v>98057</v>
+        <v>105082</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,26 +1645,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>224098</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1664,13 +1683,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721130</v>
+        <v>721172</v>
       </c>
       <c r="R10" t="n">
-        <v>6380537</v>
+        <v>6380349</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,7 +1723,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ängsbarrskog.</t>
+          <t>Sumpigare del.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1755,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123798127</v>
+        <v>123798135</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>105653</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,25 +1767,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1779,24 +1798,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721153</v>
+        <v>721199</v>
       </c>
       <c r="R11" t="n">
-        <v>6380582</v>
+        <v>6380430</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1839,7 +1853,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1857,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123798140</v>
+        <v>123798241</v>
       </c>
       <c r="B12" t="n">
-        <v>98057</v>
+        <v>95683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,21 +1887,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1897,12 +1911,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1911,13 +1920,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721199</v>
+        <v>721136</v>
       </c>
       <c r="R12" t="n">
-        <v>6380430</v>
+        <v>6380323</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1960,7 +1969,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1978,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123798105</v>
+        <v>123798126</v>
       </c>
       <c r="B13" t="n">
-        <v>98057</v>
+        <v>105653</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,52 +1999,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721376</v>
+        <v>721153</v>
       </c>
       <c r="R13" t="n">
-        <v>6380469</v>
+        <v>6380582</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2070,6 +2065,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog fuktig med inslag av ask.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123798105</v>
+        <v>123798241</v>
       </c>
       <c r="B2" t="n">
-        <v>98057</v>
+        <v>95683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,12 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721376</v>
+        <v>721136</v>
       </c>
       <c r="R2" t="n">
-        <v>6380469</v>
+        <v>6380323</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -778,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123798127</v>
+        <v>123798128</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>105653</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,55 +803,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721153</v>
+        <v>721130</v>
       </c>
       <c r="R3" t="n">
-        <v>6380582</v>
+        <v>6380560</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -917,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123798141</v>
+        <v>123798132</v>
       </c>
       <c r="B4" t="n">
         <v>98057</v>
@@ -952,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -971,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721205</v>
+        <v>721130</v>
       </c>
       <c r="R4" t="n">
-        <v>6380399</v>
+        <v>6380537</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,6 +988,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123798140</v>
+        <v>123798135</v>
       </c>
       <c r="B5" t="n">
-        <v>98057</v>
+        <v>105653</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,25 +1036,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1079,11 +1065,6 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1098,7 +1079,7 @@
         <v>6380430</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,7 +1122,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1159,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123798732</v>
+        <v>123798142</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>105082</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,50 +1152,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>224098</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720940</v>
+        <v>721172</v>
       </c>
       <c r="R6" t="n">
-        <v>6380132</v>
+        <v>6380349</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,6 +1232,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sumpigare del.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1257,7 +1248,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mjed äldre träd.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,7 +1266,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123798132</v>
+        <v>123798140</v>
       </c>
       <c r="B7" t="n">
         <v>98057</v>
@@ -1310,7 +1301,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1329,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721130</v>
+        <v>721199</v>
       </c>
       <c r="R7" t="n">
-        <v>6380537</v>
+        <v>6380430</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1365,11 +1356,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123798128</v>
+        <v>123798141</v>
       </c>
       <c r="B8" t="n">
-        <v>105653</v>
+        <v>98057</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,41 +1399,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721130</v>
+        <v>721205</v>
       </c>
       <c r="R8" t="n">
-        <v>6380560</v>
+        <v>6380399</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798142</v>
+        <v>123798126</v>
       </c>
       <c r="B10" t="n">
-        <v>105082</v>
+        <v>105653</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,55 +1641,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224098</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721172</v>
+        <v>721153</v>
       </c>
       <c r="R10" t="n">
-        <v>6380349</v>
+        <v>6380582</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,7 +1709,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sumpigare del.</t>
+          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,7 +1723,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog fuktig med inslag av ask.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1755,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123798135</v>
+        <v>123798105</v>
       </c>
       <c r="B11" t="n">
-        <v>105653</v>
+        <v>98057</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,25 +1753,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1798,19 +1784,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721199</v>
+        <v>721376</v>
       </c>
       <c r="R11" t="n">
-        <v>6380430</v>
+        <v>6380469</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1853,7 +1844,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1871,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123798241</v>
+        <v>123798127</v>
       </c>
       <c r="B12" t="n">
-        <v>95683</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,21 +1878,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>219862</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1911,7 +1902,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1920,13 +1916,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721136</v>
+        <v>721153</v>
       </c>
       <c r="R12" t="n">
-        <v>6380323</v>
+        <v>6380582</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1969,7 +1965,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1987,10 +1983,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123798126</v>
+        <v>123798732</v>
       </c>
       <c r="B13" t="n">
-        <v>105653</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,41 +1995,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721153</v>
+        <v>720940</v>
       </c>
       <c r="R13" t="n">
-        <v>6380582</v>
+        <v>6380132</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,11 +2070,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarskog fuktig med inslag av ask.</t>
+          <t>Kalkbarrskog mjed äldre träd.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123798241</v>
+        <v>123798105</v>
       </c>
       <c r="B2" t="n">
-        <v>95683</v>
+        <v>98057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721136</v>
+        <v>721376</v>
       </c>
       <c r="R2" t="n">
-        <v>6380323</v>
+        <v>6380469</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,7 +778,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123798128</v>
+        <v>123798140</v>
       </c>
       <c r="B3" t="n">
-        <v>105653</v>
+        <v>98057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,41 +808,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721130</v>
+        <v>721199</v>
       </c>
       <c r="R3" t="n">
-        <v>6380560</v>
+        <v>6380430</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123798132</v>
+        <v>123798135</v>
       </c>
       <c r="B4" t="n">
-        <v>98057</v>
+        <v>105654</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,30 +929,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -941,24 +960,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721130</v>
+        <v>721199</v>
       </c>
       <c r="R4" t="n">
-        <v>6380537</v>
+        <v>6380430</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,11 +1004,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1006,7 +1015,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1024,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123798135</v>
+        <v>123798127</v>
       </c>
       <c r="B5" t="n">
-        <v>105653</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,25 +1045,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,19 +1076,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721199</v>
+        <v>721153</v>
       </c>
       <c r="R5" t="n">
-        <v>6380430</v>
+        <v>6380582</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1136,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1140,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123798142</v>
+        <v>123798132</v>
       </c>
       <c r="B6" t="n">
-        <v>105082</v>
+        <v>98057</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,26 +1170,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224098</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1194,13 +1208,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721172</v>
+        <v>721130</v>
       </c>
       <c r="R6" t="n">
-        <v>6380349</v>
+        <v>6380537</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1248,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sumpigare del.</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123798140</v>
+        <v>123798142</v>
       </c>
       <c r="B7" t="n">
-        <v>98057</v>
+        <v>105082</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,26 +1296,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>224098</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,13 +1334,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721199</v>
+        <v>721172</v>
       </c>
       <c r="R7" t="n">
-        <v>6380430</v>
+        <v>6380349</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,6 +1370,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Sumpigare del.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,7 +1406,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123798141</v>
+        <v>123798148</v>
       </c>
       <c r="B8" t="n">
         <v>98057</v>
@@ -1422,7 +1441,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,13 +1460,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721205</v>
+        <v>721136</v>
       </c>
       <c r="R8" t="n">
-        <v>6380399</v>
+        <v>6380323</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1508,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123798148</v>
+        <v>123798732</v>
       </c>
       <c r="B9" t="n">
-        <v>98057</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,25 +1539,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1546,29 +1565,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721136</v>
+        <v>720940</v>
       </c>
       <c r="R9" t="n">
-        <v>6380323</v>
+        <v>6380132</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1611,7 +1625,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog mjed äldre träd.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1629,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798126</v>
+        <v>123798128</v>
       </c>
       <c r="B10" t="n">
-        <v>105653</v>
+        <v>105654</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,13 +1683,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721153</v>
+        <v>721130</v>
       </c>
       <c r="R10" t="n">
-        <v>6380582</v>
+        <v>6380560</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1707,11 +1721,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1723,7 +1732,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarskog fuktig med inslag av ask.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1741,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123798105</v>
+        <v>123798241</v>
       </c>
       <c r="B11" t="n">
-        <v>98057</v>
+        <v>95683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,21 +1766,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1781,12 +1790,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1795,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721376</v>
+        <v>721136</v>
       </c>
       <c r="R11" t="n">
-        <v>6380469</v>
+        <v>6380323</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1844,7 +1848,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1862,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123798127</v>
+        <v>123798141</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>98057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,26 +1882,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1916,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721153</v>
+        <v>721205</v>
       </c>
       <c r="R12" t="n">
-        <v>6380582</v>
+        <v>6380399</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1983,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123798732</v>
+        <v>123798126</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>105654</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,50 +1999,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720940</v>
+        <v>721153</v>
       </c>
       <c r="R13" t="n">
-        <v>6380132</v>
+        <v>6380582</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2070,6 +2065,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mjed äldre träd.</t>
+          <t>Kalkbarskog fuktig med inslag av ask.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123798105</v>
+        <v>123798148</v>
       </c>
       <c r="B2" t="n">
         <v>98057</v>
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721376</v>
+        <v>721136</v>
       </c>
       <c r="R2" t="n">
-        <v>6380469</v>
+        <v>6380323</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123798135</v>
+        <v>123798127</v>
       </c>
       <c r="B4" t="n">
-        <v>105654</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -960,19 +960,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721199</v>
+        <v>721153</v>
       </c>
       <c r="R4" t="n">
-        <v>6380430</v>
+        <v>6380582</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,7 +1020,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123798127</v>
+        <v>123798126</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>105654</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,42 +1050,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
@@ -1125,6 +1116,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1136,7 +1132,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog fuktig med inslag av ask.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1154,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123798132</v>
+        <v>123798105</v>
       </c>
       <c r="B6" t="n">
         <v>98057</v>
@@ -1189,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1208,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721130</v>
+        <v>721376</v>
       </c>
       <c r="R6" t="n">
-        <v>6380537</v>
+        <v>6380469</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,11 +1240,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123798142</v>
+        <v>123798132</v>
       </c>
       <c r="B7" t="n">
-        <v>105082</v>
+        <v>98057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,26 +1287,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224098</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1334,13 +1325,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721172</v>
+        <v>721130</v>
       </c>
       <c r="R7" t="n">
-        <v>6380349</v>
+        <v>6380537</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,7 +1365,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sumpigare del.</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123798148</v>
+        <v>123798141</v>
       </c>
       <c r="B8" t="n">
         <v>98057</v>
@@ -1441,7 +1432,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1460,13 +1451,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721136</v>
+        <v>721205</v>
       </c>
       <c r="R8" t="n">
-        <v>6380323</v>
+        <v>6380399</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1527,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123798732</v>
+        <v>123798128</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>105654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,47 +1530,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720940</v>
+        <v>721130</v>
       </c>
       <c r="R9" t="n">
-        <v>6380132</v>
+        <v>6380560</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1625,7 +1607,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mjed äldre träd.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1643,10 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798128</v>
+        <v>123798241</v>
       </c>
       <c r="B10" t="n">
-        <v>105654</v>
+        <v>95683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,41 +1637,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721130</v>
+        <v>721136</v>
       </c>
       <c r="R10" t="n">
-        <v>6380560</v>
+        <v>6380323</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1732,7 +1723,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1750,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123798241</v>
+        <v>123798732</v>
       </c>
       <c r="B11" t="n">
-        <v>95683</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,25 +1753,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1788,24 +1779,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721136</v>
+        <v>720940</v>
       </c>
       <c r="R11" t="n">
-        <v>6380323</v>
+        <v>6380132</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1848,7 +1839,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog mjed äldre träd.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1866,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123798141</v>
+        <v>123798135</v>
       </c>
       <c r="B12" t="n">
-        <v>98057</v>
+        <v>105654</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,30 +1869,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1909,24 +1900,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721205</v>
+        <v>721199</v>
       </c>
       <c r="R12" t="n">
-        <v>6380399</v>
+        <v>6380430</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1969,7 +1955,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd.. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1987,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123798126</v>
+        <v>123798142</v>
       </c>
       <c r="B13" t="n">
-        <v>105654</v>
+        <v>105082</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,41 +1985,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>224098</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721153</v>
+        <v>721172</v>
       </c>
       <c r="R13" t="n">
-        <v>6380582</v>
+        <v>6380349</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
+          <t>Sumpigare del.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarskog fuktig med inslag av ask.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123798140</v>
+        <v>123798241</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>95705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,12 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721199</v>
+        <v>721136</v>
       </c>
       <c r="R2" t="n">
-        <v>6380430</v>
+        <v>6380323</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -778,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123798132</v>
+        <v>123798732</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,55 +803,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721130</v>
+        <v>720940</v>
       </c>
       <c r="R3" t="n">
-        <v>6380537</v>
+        <v>6380132</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,11 +878,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -904,7 +889,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog mjed äldre träd.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123798142</v>
+        <v>123798140</v>
       </c>
       <c r="B4" t="n">
-        <v>105104</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,26 +923,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224098</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721172</v>
+        <v>721199</v>
       </c>
       <c r="R4" t="n">
-        <v>6380349</v>
+        <v>6380430</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,11 +997,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sumpigare del.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123798141</v>
+        <v>123798142</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>105104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,26 +1044,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>224098</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1102,13 +1082,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721205</v>
+        <v>721172</v>
       </c>
       <c r="R5" t="n">
-        <v>6380399</v>
+        <v>6380349</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,6 +1118,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sumpigare del.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123798241</v>
+        <v>123798128</v>
       </c>
       <c r="B6" t="n">
-        <v>95705</v>
+        <v>105676</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,50 +1166,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721136</v>
+        <v>721130</v>
       </c>
       <c r="R6" t="n">
-        <v>6380323</v>
+        <v>6380560</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,7 +1243,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1285,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123798126</v>
+        <v>123798132</v>
       </c>
       <c r="B7" t="n">
-        <v>105676</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,38 +1273,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721153</v>
+        <v>721130</v>
       </c>
       <c r="R7" t="n">
-        <v>6380582</v>
+        <v>6380537</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1365,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,7 +1369,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarskog fuktig med inslag av ask.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1397,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123798105</v>
+        <v>123798127</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>98123</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,21 +1403,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1451,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721376</v>
+        <v>721153</v>
       </c>
       <c r="R8" t="n">
-        <v>6380469</v>
+        <v>6380582</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1518,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123798127</v>
+        <v>123798141</v>
       </c>
       <c r="B9" t="n">
-        <v>98123</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,26 +1524,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721153</v>
+        <v>721205</v>
       </c>
       <c r="R9" t="n">
-        <v>6380582</v>
+        <v>6380399</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1639,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798128</v>
+        <v>123798148</v>
       </c>
       <c r="B10" t="n">
-        <v>105676</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,41 +1641,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721130</v>
+        <v>721136</v>
       </c>
       <c r="R10" t="n">
-        <v>6380560</v>
+        <v>6380323</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1862,7 +1866,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123798148</v>
+        <v>123798105</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1916,13 +1920,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721136</v>
+        <v>721376</v>
       </c>
       <c r="R12" t="n">
-        <v>6380323</v>
+        <v>6380469</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1983,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123798732</v>
+        <v>123798126</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>105676</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,50 +1999,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720940</v>
+        <v>721153</v>
       </c>
       <c r="R13" t="n">
-        <v>6380132</v>
+        <v>6380582</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2070,6 +2065,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mjed äldre träd.</t>
+          <t>Kalkbarskog fuktig med inslag av ask.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123798241</v>
+        <v>123798148</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -730,7 +735,7 @@
         <v>6380323</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,7 +778,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123798732</v>
+        <v>123798142</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>105104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,50 +808,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>224098</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720940</v>
+        <v>721172</v>
       </c>
       <c r="R3" t="n">
-        <v>6380132</v>
+        <v>6380349</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +888,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sumpigare del.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -889,7 +904,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mjed äldre träd.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1028,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123798142</v>
+        <v>123798241</v>
       </c>
       <c r="B5" t="n">
-        <v>105104</v>
+        <v>95705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,36 +1059,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224098</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1082,13 +1092,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721172</v>
+        <v>721136</v>
       </c>
       <c r="R5" t="n">
-        <v>6380349</v>
+        <v>6380323</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,11 +1130,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sumpigare del.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1136,7 +1141,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1154,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123798128</v>
+        <v>123798732</v>
       </c>
       <c r="B6" t="n">
-        <v>105676</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,38 +1171,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrlanda, Burs 1:30 (2), Gtl</t>
+          <t>Norrlanda, Burs 1:30 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721130</v>
+        <v>720940</v>
       </c>
       <c r="R6" t="n">
-        <v>6380560</v>
+        <v>6380132</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,7 +1257,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarrskog mjed äldre träd.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1261,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123798132</v>
+        <v>123798126</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>105676</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,52 +1287,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrlanda, Burs 1:30 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721130</v>
+        <v>721153</v>
       </c>
       <c r="R7" t="n">
-        <v>6380537</v>
+        <v>6380582</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ängsbarrskog.</t>
+          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
+          <t>Kalkbarskog fuktig med inslag av ask.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123798127</v>
+        <v>123798105</v>
       </c>
       <c r="B8" t="n">
-        <v>98123</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,21 +1403,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721153</v>
+        <v>721376</v>
       </c>
       <c r="R8" t="n">
-        <v>6380582</v>
+        <v>6380469</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123798141</v>
+        <v>123798132</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721205</v>
+        <v>721130</v>
       </c>
       <c r="R9" t="n">
-        <v>6380399</v>
+        <v>6380537</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1598,6 +1598,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,7 +1634,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123798148</v>
+        <v>123798141</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1664,7 +1669,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1683,13 +1688,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721136</v>
+        <v>721205</v>
       </c>
       <c r="R10" t="n">
-        <v>6380323</v>
+        <v>6380399</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1866,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123798105</v>
+        <v>123798127</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>98123</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1882,21 +1887,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1920,10 +1925,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721376</v>
+        <v>721153</v>
       </c>
       <c r="R12" t="n">
-        <v>6380469</v>
+        <v>6380582</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1987,7 +1992,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123798126</v>
+        <v>123798128</v>
       </c>
       <c r="B13" t="n">
         <v>105676</v>
@@ -2027,13 +2032,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721153</v>
+        <v>721130</v>
       </c>
       <c r="R13" t="n">
-        <v>6380582</v>
+        <v>6380560</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,11 +2070,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med skott samt äldre döda, stående och fallna.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarskog fuktig med inslag av ask.</t>
+          <t>Kalkbarskog äldre med gran och tall (även återväxt med yngre träd), en del grova (örntallar) och med en hel del döda stående och liggande träd..</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2097,6 +2097,8467 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127265497</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>721247</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6380342</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127265532</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>721484</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6380450</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127265518</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>721330</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6380365</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127265587</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>721591</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6380497</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127265540</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>721546</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6380552</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med löv.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127265479</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>721212</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6380346</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127265530</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98472</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>721463</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6380440</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127265492</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>721239</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6380330</v>
+      </c>
+      <c r="S21" t="n">
+        <v>7</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127265600</v>
+      </c>
+      <c r="B22" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>721547</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6380409</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127265610</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>721466</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6380394</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127265590</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98472</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>721580</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6380472</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127265496</v>
+      </c>
+      <c r="B25" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>721247</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6380342</v>
+      </c>
+      <c r="S25" t="n">
+        <v>7</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127265624</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>721199</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6380248</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127265473</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>721232</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6380313</v>
+      </c>
+      <c r="S27" t="n">
+        <v>7</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127265475</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>721209</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6380333</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127265503</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>721272</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6380356</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127265598</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>721557</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6380422</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127265548</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99653</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>174</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Strävlosta</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bromopsis benekenii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>721578</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6380576</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med löv.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127265606</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>721475</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6380396</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127265486</v>
+      </c>
+      <c r="B33" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>721231</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6380342</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127296661</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58334</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>721560</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6380582</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med löv.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127265594</v>
+      </c>
+      <c r="B35" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>721572</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6380434</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127265584</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>721601</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6380518</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127265541</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>721546</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6380552</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med löv.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127265612</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>721424</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6380372</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127265566</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>721615</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6380615</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Åkant, troligen rätad med höga kanter.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127265582</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>721601</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6380518</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127265579</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>721577</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6380550</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127265545</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>721560</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6380582</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med löv.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127265623</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>721199</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6380248</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127265534</v>
+      </c>
+      <c r="B44" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>721493</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6380446</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127265515</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>721315</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6380362</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127265571</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>721594</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6380563</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127265478</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>721212</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6380346</v>
+      </c>
+      <c r="S47" t="n">
+        <v>8</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127265626</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>721183</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6380248</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127265597</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>721557</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6380422</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127265628</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>721173</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6380248</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127265507</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>721307</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6380360</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127265593</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>721572</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6380434</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127265472</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>721232</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6380313</v>
+      </c>
+      <c r="S53" t="n">
+        <v>7</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127296631</v>
+      </c>
+      <c r="B54" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>721557</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6380495</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127265583</v>
+      </c>
+      <c r="B55" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>721601</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6380518</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127265494</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98458</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>721247</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6380342</v>
+      </c>
+      <c r="S56" t="n">
+        <v>7</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127265484</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>721220</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6380355</v>
+      </c>
+      <c r="S57" t="n">
+        <v>7</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127265622</v>
+      </c>
+      <c r="B58" t="n">
+        <v>103889</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>721252</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6380274</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127265481</v>
+      </c>
+      <c r="B59" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>721220</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6380355</v>
+      </c>
+      <c r="S59" t="n">
+        <v>7</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127265471</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>721232</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6380313</v>
+      </c>
+      <c r="S60" t="n">
+        <v>7</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127265505</v>
+      </c>
+      <c r="B61" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>721284</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6380359</v>
+      </c>
+      <c r="S61" t="n">
+        <v>7</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127265488</v>
+      </c>
+      <c r="B62" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>721231</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6380342</v>
+      </c>
+      <c r="S62" t="n">
+        <v>3</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127265474</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>721232</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6380313</v>
+      </c>
+      <c r="S63" t="n">
+        <v>7</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127265504</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>721272</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6380356</v>
+      </c>
+      <c r="S64" t="n">
+        <v>7</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127265495</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>721247</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6380342</v>
+      </c>
+      <c r="S65" t="n">
+        <v>7</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127265533</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99187</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>721484</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6380450</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127265617</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98458</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>721357</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6380338</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127265517</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>721330</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6380365</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127265546</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>721560</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6380582</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med löv.</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127265525</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>721433</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6380417</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127265476</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>721209</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6380333</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127265528</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>721460</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6380438</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127265586</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>721591</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6380497</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127265526</v>
+      </c>
+      <c r="B74" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>721433</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6380417</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127265535</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>721493</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6380446</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127265588</v>
+      </c>
+      <c r="B76" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>721591</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6380497</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127265508</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>721307</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6380360</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127265513</v>
+      </c>
+      <c r="B78" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>721315</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6380362</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127265493</v>
+      </c>
+      <c r="B79" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>721247</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6380342</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127265605</v>
+      </c>
+      <c r="B80" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>721466</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6380394</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127265489</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>721231</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6380342</v>
+      </c>
+      <c r="S81" t="n">
+        <v>3</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127265491</v>
+      </c>
+      <c r="B82" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>721239</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6380330</v>
+      </c>
+      <c r="S82" t="n">
+        <v>7</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127296632</v>
+      </c>
+      <c r="B83" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>721578</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6380530</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lundstarr rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127265549</v>
+      </c>
+      <c r="B84" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>721590</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6380571</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med löv.</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127265511</v>
+      </c>
+      <c r="B85" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>721315</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6380362</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127265499</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>721247</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6380342</v>
+      </c>
+      <c r="S86" t="n">
+        <v>7</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127265572</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>721594</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6380563</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127265483</v>
+      </c>
+      <c r="B88" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>721220</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6380355</v>
+      </c>
+      <c r="S88" t="n">
+        <v>7</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127265519</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>721330</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6380365</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127265500</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>721263</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6380356</v>
+      </c>
+      <c r="S90" t="n">
+        <v>7</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127265506</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>721284</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6380359</v>
+      </c>
+      <c r="S91" t="n">
+        <v>7</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265497</v>
+        <v>127265479</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,26 +2110,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721247</v>
+        <v>721212</v>
       </c>
       <c r="R14" t="n">
-        <v>6380342</v>
+        <v>6380346</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,45 +2210,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265532</v>
+        <v>127265530</v>
       </c>
       <c r="B15" t="n">
-        <v>106031</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220785</v>
+        <v>223621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721484</v>
+        <v>721463</v>
       </c>
       <c r="R15" t="n">
-        <v>6380450</v>
+        <v>6380440</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,54 +2321,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265518</v>
+        <v>127265532</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>106037</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721330</v>
+        <v>721484</v>
       </c>
       <c r="R16" t="n">
-        <v>6380365</v>
+        <v>6380450</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2426,7 +2426,7 @@
         <v>127265587</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127265540</v>
       </c>
       <c r="B18" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265479</v>
+        <v>127265492</v>
       </c>
       <c r="B19" t="n">
-        <v>98354</v>
+        <v>98465</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,26 +2647,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2680,13 +2680,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721212</v>
+        <v>721239</v>
       </c>
       <c r="R19" t="n">
-        <v>6380346</v>
+        <v>6380330</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2747,54 +2747,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265530</v>
+        <v>127265600</v>
       </c>
       <c r="B20" t="n">
-        <v>98472</v>
+        <v>109266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721463</v>
+        <v>721547</v>
       </c>
       <c r="R20" t="n">
-        <v>6380440</v>
+        <v>6380409</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2858,10 +2849,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265492</v>
+        <v>127265518</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,17 +2889,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721239</v>
+        <v>721330</v>
       </c>
       <c r="R21" t="n">
-        <v>6380330</v>
+        <v>6380365</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2969,48 +2960,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265600</v>
+        <v>127265497</v>
       </c>
       <c r="B22" t="n">
-        <v>109260</v>
+        <v>98465</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721547</v>
+        <v>721247</v>
       </c>
       <c r="R22" t="n">
-        <v>6380409</v>
+        <v>6380342</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>127265610</v>
       </c>
       <c r="B23" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>127265590</v>
       </c>
       <c r="B24" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>127265496</v>
       </c>
       <c r="B25" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>127265624</v>
       </c>
       <c r="B26" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,54 +3511,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265473</v>
+        <v>127265503</v>
       </c>
       <c r="B27" t="n">
-        <v>98414</v>
+        <v>106037</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721232</v>
+        <v>721272</v>
       </c>
       <c r="R27" t="n">
-        <v>6380313</v>
+        <v>6380356</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3625,7 +3616,7 @@
         <v>127265475</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3733,45 +3724,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265503</v>
+        <v>127265473</v>
       </c>
       <c r="B29" t="n">
-        <v>106031</v>
+        <v>98420</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721272</v>
+        <v>721232</v>
       </c>
       <c r="R29" t="n">
-        <v>6380356</v>
+        <v>6380313</v>
       </c>
       <c r="S29" t="n">
         <v>7</v>
@@ -3838,7 +3838,7 @@
         <v>127265598</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>127265548</v>
       </c>
       <c r="B31" t="n">
-        <v>99653</v>
+        <v>99659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>127265606</v>
       </c>
       <c r="B32" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>127265486</v>
       </c>
       <c r="B33" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127296661</v>
+        <v>127265584</v>
       </c>
       <c r="B34" t="n">
-        <v>58334</v>
+        <v>98465</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,46 +4286,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>219847</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721560</v>
+        <v>721601</v>
       </c>
       <c r="R34" t="n">
-        <v>6380582</v>
+        <v>6380518</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4386,48 +4386,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265594</v>
+        <v>127296661</v>
       </c>
       <c r="B35" t="n">
-        <v>109260</v>
+        <v>58334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>103044</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721572</v>
+        <v>721560</v>
       </c>
       <c r="R35" t="n">
-        <v>6380434</v>
+        <v>6380582</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4459,11 +4468,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4475,7 +4479,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4493,54 +4497,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265584</v>
+        <v>127265594</v>
       </c>
       <c r="B36" t="n">
-        <v>98459</v>
+        <v>109266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721601</v>
+        <v>721572</v>
       </c>
       <c r="R36" t="n">
-        <v>6380518</v>
+        <v>6380434</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4573,6 +4568,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4604,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127265541</v>
+        <v>127265612</v>
       </c>
       <c r="B37" t="n">
-        <v>98354</v>
+        <v>98479</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,34 +4615,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721546</v>
+        <v>721424</v>
       </c>
       <c r="R37" t="n">
-        <v>6380552</v>
+        <v>6380372</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,7 +4697,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4706,10 +4715,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265612</v>
+        <v>127265541</v>
       </c>
       <c r="B38" t="n">
-        <v>98473</v>
+        <v>98360</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4717,43 +4726,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721424</v>
+        <v>721546</v>
       </c>
       <c r="R38" t="n">
-        <v>6380372</v>
+        <v>6380552</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4820,7 +4820,7 @@
         <v>127265566</v>
       </c>
       <c r="B39" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>127265582</v>
       </c>
       <c r="B40" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5030,48 +5030,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127265579</v>
+        <v>127265623</v>
       </c>
       <c r="B41" t="n">
-        <v>106031</v>
+        <v>98420</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721577</v>
+        <v>721199</v>
       </c>
       <c r="R41" t="n">
-        <v>6380550</v>
+        <v>6380248</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5132,10 +5141,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265545</v>
+        <v>127265579</v>
       </c>
       <c r="B42" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5163,14 +5172,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721560</v>
+        <v>721577</v>
       </c>
       <c r="R42" t="n">
-        <v>6380582</v>
+        <v>6380550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5216,7 +5225,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5234,57 +5243,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127265623</v>
+        <v>127265545</v>
       </c>
       <c r="B43" t="n">
-        <v>98414</v>
+        <v>106037</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721199</v>
+        <v>721560</v>
       </c>
       <c r="R43" t="n">
-        <v>6380248</v>
+        <v>6380582</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5345,45 +5345,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265534</v>
+        <v>127265571</v>
       </c>
       <c r="B44" t="n">
-        <v>109260</v>
+        <v>98360</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721493</v>
+        <v>721594</v>
       </c>
       <c r="R44" t="n">
-        <v>6380446</v>
+        <v>6380563</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5447,57 +5456,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265515</v>
+        <v>127265534</v>
       </c>
       <c r="B45" t="n">
-        <v>98414</v>
+        <v>109266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721315</v>
+        <v>721493</v>
       </c>
       <c r="R45" t="n">
-        <v>6380362</v>
+        <v>6380446</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265571</v>
+        <v>127265515</v>
       </c>
       <c r="B46" t="n">
-        <v>98354</v>
+        <v>98420</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5569,26 +5569,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5598,17 +5598,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721594</v>
+        <v>721315</v>
       </c>
       <c r="R46" t="n">
-        <v>6380563</v>
+        <v>6380362</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127265478</v>
+        <v>127265626</v>
       </c>
       <c r="B47" t="n">
-        <v>98414</v>
+        <v>98360</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,26 +5680,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721212</v>
+        <v>721183</v>
       </c>
       <c r="R47" t="n">
-        <v>6380346</v>
+        <v>6380248</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127265626</v>
+        <v>127265597</v>
       </c>
       <c r="B48" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5824,13 +5824,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721183</v>
+        <v>721557</v>
       </c>
       <c r="R48" t="n">
-        <v>6380248</v>
+        <v>6380422</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127265597</v>
+        <v>127265478</v>
       </c>
       <c r="B49" t="n">
-        <v>98354</v>
+        <v>98420</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,26 +5902,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721557</v>
+        <v>721212</v>
       </c>
       <c r="R49" t="n">
-        <v>6380422</v>
+        <v>6380346</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6005,7 +6005,7 @@
         <v>127265628</v>
       </c>
       <c r="B50" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>127265507</v>
       </c>
       <c r="B51" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>127265593</v>
       </c>
       <c r="B52" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>127265472</v>
       </c>
       <c r="B53" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6437,64 +6437,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B54" t="n">
-        <v>43228</v>
+        <v>106037</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R54" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,45 +6539,64 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B55" t="n">
-        <v>106031</v>
+        <v>43228</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R55" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265494</v>
+        <v>127265484</v>
       </c>
       <c r="B56" t="n">
-        <v>98458</v>
+        <v>98360</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6671,26 +6671,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721247</v>
+        <v>721220</v>
       </c>
       <c r="R56" t="n">
-        <v>6380342</v>
+        <v>6380355</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -6771,54 +6771,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265484</v>
+        <v>127265471</v>
       </c>
       <c r="B57" t="n">
-        <v>98354</v>
+        <v>106037</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R57" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S57" t="n">
         <v>7</v>
@@ -6882,10 +6873,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265622</v>
+        <v>127265481</v>
       </c>
       <c r="B58" t="n">
-        <v>103889</v>
+        <v>109266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6893,46 +6884,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721252</v>
+        <v>721220</v>
       </c>
       <c r="R58" t="n">
-        <v>6380274</v>
+        <v>6380355</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6993,10 +6975,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265481</v>
+        <v>127265622</v>
       </c>
       <c r="B59" t="n">
-        <v>109260</v>
+        <v>103895</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7004,37 +6986,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721220</v>
+        <v>721252</v>
       </c>
       <c r="R59" t="n">
-        <v>6380355</v>
+        <v>6380274</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7095,45 +7086,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265471</v>
+        <v>127265494</v>
       </c>
       <c r="B60" t="n">
-        <v>106031</v>
+        <v>98464</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721232</v>
+        <v>721247</v>
       </c>
       <c r="R60" t="n">
-        <v>6380313</v>
+        <v>6380342</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7197,45 +7197,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265505</v>
+        <v>127265474</v>
       </c>
       <c r="B61" t="n">
-        <v>106031</v>
+        <v>98360</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721284</v>
+        <v>721232</v>
       </c>
       <c r="R61" t="n">
-        <v>6380359</v>
+        <v>6380313</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7299,48 +7308,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265488</v>
+        <v>127265504</v>
       </c>
       <c r="B62" t="n">
-        <v>106031</v>
+        <v>98360</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721231</v>
+        <v>721272</v>
       </c>
       <c r="R62" t="n">
-        <v>6380342</v>
+        <v>6380356</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7401,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265474</v>
+        <v>127265546</v>
       </c>
       <c r="B63" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7431,7 +7449,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7441,17 +7459,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721232</v>
+        <v>721560</v>
       </c>
       <c r="R63" t="n">
-        <v>6380313</v>
+        <v>6380582</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7494,7 +7512,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7512,54 +7530,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265504</v>
+        <v>127265505</v>
       </c>
       <c r="B64" t="n">
-        <v>98354</v>
+        <v>106037</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721272</v>
+        <v>721284</v>
       </c>
       <c r="R64" t="n">
-        <v>6380356</v>
+        <v>6380359</v>
       </c>
       <c r="S64" t="n">
         <v>7</v>
@@ -7623,57 +7632,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265495</v>
+        <v>127265488</v>
       </c>
       <c r="B65" t="n">
-        <v>98414</v>
+        <v>106037</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721247</v>
+        <v>721231</v>
       </c>
       <c r="R65" t="n">
         <v>6380342</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>127265533</v>
       </c>
       <c r="B66" t="n">
-        <v>99187</v>
+        <v>99193</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7845,10 +7845,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265617</v>
+        <v>127265517</v>
       </c>
       <c r="B67" t="n">
-        <v>98458</v>
+        <v>98420</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7856,26 +7856,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7883,24 +7883,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721357</v>
+        <v>721330</v>
       </c>
       <c r="R67" t="n">
-        <v>6380338</v>
+        <v>6380365</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7961,10 +7956,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265517</v>
+        <v>127265495</v>
       </c>
       <c r="B68" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7991,7 +7986,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8001,17 +7996,17 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721330</v>
+        <v>721247</v>
       </c>
       <c r="R68" t="n">
-        <v>6380365</v>
+        <v>6380342</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8072,10 +8067,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265546</v>
+        <v>127265617</v>
       </c>
       <c r="B69" t="n">
-        <v>98354</v>
+        <v>98464</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8083,21 +8078,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8110,19 +8105,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721560</v>
+        <v>721357</v>
       </c>
       <c r="R69" t="n">
-        <v>6380582</v>
+        <v>6380338</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127265525</v>
+        <v>127265476</v>
       </c>
       <c r="B70" t="n">
-        <v>98414</v>
+        <v>98360</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,26 +8194,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8223,17 +8223,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>721433</v>
+        <v>721209</v>
       </c>
       <c r="R70" t="n">
-        <v>6380417</v>
+        <v>6380333</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8263,6 +8263,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8294,10 +8299,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127265476</v>
+        <v>127265525</v>
       </c>
       <c r="B71" t="n">
-        <v>98354</v>
+        <v>98420</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8305,26 +8310,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8334,17 +8339,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>721209</v>
+        <v>721433</v>
       </c>
       <c r="R71" t="n">
-        <v>6380333</v>
+        <v>6380417</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8374,11 +8379,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8413,7 +8413,7 @@
         <v>127265528</v>
       </c>
       <c r="B72" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>127265586</v>
       </c>
       <c r="B73" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>127265526</v>
       </c>
       <c r="B74" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>127265535</v>
       </c>
       <c r="B75" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>127265588</v>
       </c>
       <c r="B76" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>127265508</v>
       </c>
       <c r="B77" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>127265513</v>
       </c>
       <c r="B78" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9165,48 +9165,67 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127265493</v>
+        <v>127296632</v>
       </c>
       <c r="B79" t="n">
-        <v>106031</v>
+        <v>43228</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>721247</v>
+        <v>721578</v>
       </c>
       <c r="R79" t="n">
-        <v>6380342</v>
+        <v>6380530</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9238,6 +9257,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Lundstarr rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9249,7 +9273,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9267,48 +9291,57 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265605</v>
+        <v>127265489</v>
       </c>
       <c r="B80" t="n">
-        <v>109260</v>
+        <v>98360</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721466</v>
+        <v>721231</v>
       </c>
       <c r="R80" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9369,57 +9402,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265489</v>
+        <v>127265493</v>
       </c>
       <c r="B81" t="n">
-        <v>98354</v>
+        <v>106037</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721231</v>
+        <v>721247</v>
       </c>
       <c r="R81" t="n">
         <v>6380342</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9483,7 +9507,7 @@
         <v>127265491</v>
       </c>
       <c r="B82" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,10 +9606,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127296632</v>
+        <v>127265605</v>
       </c>
       <c r="B83" t="n">
-        <v>43228</v>
+        <v>109266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9593,53 +9617,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721578</v>
+        <v>721466</v>
       </c>
       <c r="R83" t="n">
-        <v>6380530</v>
+        <v>6380394</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9674,11 +9679,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Lundstarr rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9708,48 +9708,57 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265549</v>
+        <v>127265499</v>
       </c>
       <c r="B84" t="n">
-        <v>106031</v>
+        <v>98360</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721590</v>
+        <v>721247</v>
       </c>
       <c r="R84" t="n">
-        <v>6380571</v>
+        <v>6380342</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9792,7 +9801,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9810,10 +9819,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265511</v>
+        <v>127265549</v>
       </c>
       <c r="B85" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9841,17 +9850,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721315</v>
+        <v>721590</v>
       </c>
       <c r="R85" t="n">
-        <v>6380362</v>
+        <v>6380571</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9894,7 +9903,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9912,57 +9921,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265499</v>
+        <v>127265511</v>
       </c>
       <c r="B86" t="n">
-        <v>98354</v>
+        <v>106037</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721247</v>
+        <v>721315</v>
       </c>
       <c r="R86" t="n">
-        <v>6380342</v>
+        <v>6380362</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>127265572</v>
       </c>
       <c r="B87" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>127265483</v>
       </c>
       <c r="B88" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>127265519</v>
       </c>
       <c r="B89" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>127265500</v>
       </c>
       <c r="B90" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>127265506</v>
       </c>
       <c r="B91" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265479</v>
+        <v>127265497</v>
       </c>
       <c r="B14" t="n">
-        <v>98360</v>
+        <v>98465</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,26 +2110,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721212</v>
+        <v>721247</v>
       </c>
       <c r="R14" t="n">
-        <v>6380346</v>
+        <v>6380342</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265530</v>
+        <v>127265518</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>98465</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721463</v>
+        <v>721330</v>
       </c>
       <c r="R15" t="n">
-        <v>6380440</v>
+        <v>6380365</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,48 +2321,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265532</v>
+        <v>127265492</v>
       </c>
       <c r="B16" t="n">
-        <v>106037</v>
+        <v>98465</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721484</v>
+        <v>721239</v>
       </c>
       <c r="R16" t="n">
-        <v>6380450</v>
+        <v>6380330</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2534,7 +2543,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265540</v>
+        <v>127265532</v>
       </c>
       <c r="B18" t="n">
         <v>106037</v>
@@ -2569,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721546</v>
+        <v>721484</v>
       </c>
       <c r="R18" t="n">
-        <v>6380552</v>
+        <v>6380450</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,7 +2627,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2636,57 +2645,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265492</v>
+        <v>127265540</v>
       </c>
       <c r="B19" t="n">
-        <v>98465</v>
+        <v>106037</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721239</v>
+        <v>721546</v>
       </c>
       <c r="R19" t="n">
-        <v>6380330</v>
+        <v>6380552</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2747,48 +2747,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265600</v>
+        <v>127265479</v>
       </c>
       <c r="B20" t="n">
-        <v>109266</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721547</v>
+        <v>721212</v>
       </c>
       <c r="R20" t="n">
-        <v>6380409</v>
+        <v>6380346</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2849,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265518</v>
+        <v>127265530</v>
       </c>
       <c r="B21" t="n">
-        <v>98465</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,21 +2869,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2893,10 +2902,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721330</v>
+        <v>721463</v>
       </c>
       <c r="R21" t="n">
-        <v>6380365</v>
+        <v>6380440</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,57 +2969,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265497</v>
+        <v>127265600</v>
       </c>
       <c r="B22" t="n">
-        <v>98465</v>
+        <v>109266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721247</v>
+        <v>721547</v>
       </c>
       <c r="R22" t="n">
-        <v>6380342</v>
+        <v>6380409</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3071,57 +3071,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265610</v>
+        <v>127265496</v>
       </c>
       <c r="B23" t="n">
-        <v>98360</v>
+        <v>109266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721466</v>
+        <v>721247</v>
       </c>
       <c r="R23" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3182,10 +3173,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127265590</v>
+        <v>127265610</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>98360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,21 +3184,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223621</v>
+        <v>223591</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3226,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721580</v>
+        <v>721466</v>
       </c>
       <c r="R24" t="n">
-        <v>6380472</v>
+        <v>6380394</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3264,11 +3255,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3280,7 +3266,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3298,48 +3284,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265496</v>
+        <v>127265590</v>
       </c>
       <c r="B25" t="n">
-        <v>109266</v>
+        <v>98478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721247</v>
+        <v>721580</v>
       </c>
       <c r="R25" t="n">
-        <v>6380342</v>
+        <v>6380472</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3371,6 +3366,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265624</v>
+        <v>127265473</v>
       </c>
       <c r="B26" t="n">
-        <v>98360</v>
+        <v>98420</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3411,26 +3411,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721199</v>
+        <v>721232</v>
       </c>
       <c r="R26" t="n">
-        <v>6380248</v>
+        <v>6380313</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,48 +3511,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265503</v>
+        <v>127265475</v>
       </c>
       <c r="B27" t="n">
-        <v>106037</v>
+        <v>98465</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721272</v>
+        <v>721209</v>
       </c>
       <c r="R27" t="n">
-        <v>6380356</v>
+        <v>6380333</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3613,57 +3622,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265475</v>
+        <v>127265503</v>
       </c>
       <c r="B28" t="n">
-        <v>98465</v>
+        <v>106037</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721209</v>
+        <v>721272</v>
       </c>
       <c r="R28" t="n">
-        <v>6380333</v>
+        <v>6380356</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265473</v>
+        <v>127265624</v>
       </c>
       <c r="B29" t="n">
-        <v>98420</v>
+        <v>98360</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3735,26 +3735,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3764,17 +3764,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721232</v>
+        <v>721199</v>
       </c>
       <c r="R29" t="n">
-        <v>6380313</v>
+        <v>6380248</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265598</v>
+        <v>127265606</v>
       </c>
       <c r="B30" t="n">
         <v>98465</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721557</v>
+        <v>721475</v>
       </c>
       <c r="R30" t="n">
-        <v>6380422</v>
+        <v>6380396</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4062,7 +4062,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265606</v>
+        <v>127265598</v>
       </c>
       <c r="B32" t="n">
         <v>98465</v>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721475</v>
+        <v>721557</v>
       </c>
       <c r="R32" t="n">
-        <v>6380396</v>
+        <v>6380422</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127265584</v>
+        <v>127296661</v>
       </c>
       <c r="B34" t="n">
-        <v>98465</v>
+        <v>58334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,46 +4286,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721601</v>
+        <v>721560</v>
       </c>
       <c r="R34" t="n">
-        <v>6380518</v>
+        <v>6380582</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4386,10 +4386,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127296661</v>
+        <v>127265584</v>
       </c>
       <c r="B35" t="n">
-        <v>58334</v>
+        <v>98465</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,46 +4397,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103044</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721560</v>
+        <v>721601</v>
       </c>
       <c r="R35" t="n">
-        <v>6380582</v>
+        <v>6380518</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5030,57 +5030,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127265623</v>
+        <v>127265579</v>
       </c>
       <c r="B41" t="n">
-        <v>98420</v>
+        <v>106037</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721199</v>
+        <v>721577</v>
       </c>
       <c r="R41" t="n">
-        <v>6380248</v>
+        <v>6380550</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5141,7 +5132,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265579</v>
+        <v>127265545</v>
       </c>
       <c r="B42" t="n">
         <v>106037</v>
@@ -5172,14 +5163,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721577</v>
+        <v>721560</v>
       </c>
       <c r="R42" t="n">
-        <v>6380550</v>
+        <v>6380582</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5225,7 +5216,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5243,48 +5234,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127265545</v>
+        <v>127265623</v>
       </c>
       <c r="B43" t="n">
-        <v>106037</v>
+        <v>98420</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721560</v>
+        <v>721199</v>
       </c>
       <c r="R43" t="n">
-        <v>6380582</v>
+        <v>6380248</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265571</v>
+        <v>127265515</v>
       </c>
       <c r="B44" t="n">
-        <v>98360</v>
+        <v>98420</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5356,26 +5356,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5385,17 +5385,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721594</v>
+        <v>721315</v>
       </c>
       <c r="R44" t="n">
-        <v>6380563</v>
+        <v>6380362</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265515</v>
+        <v>127265571</v>
       </c>
       <c r="B46" t="n">
-        <v>98420</v>
+        <v>98360</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5569,26 +5569,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5598,17 +5598,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R46" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127265628</v>
+        <v>127265593</v>
       </c>
       <c r="B50" t="n">
-        <v>98360</v>
+        <v>98465</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,46 +6013,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721173</v>
+        <v>721572</v>
       </c>
       <c r="R50" t="n">
-        <v>6380248</v>
+        <v>6380434</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6113,10 +6104,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127265507</v>
+        <v>127265472</v>
       </c>
       <c r="B51" t="n">
-        <v>98360</v>
+        <v>98465</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,21 +6115,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6157,13 +6148,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721307</v>
+        <v>721232</v>
       </c>
       <c r="R51" t="n">
-        <v>6380360</v>
+        <v>6380313</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6224,10 +6215,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127265593</v>
+        <v>127265628</v>
       </c>
       <c r="B52" t="n">
-        <v>98465</v>
+        <v>98360</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,37 +6226,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721572</v>
+        <v>721173</v>
       </c>
       <c r="R52" t="n">
-        <v>6380434</v>
+        <v>6380248</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127265472</v>
+        <v>127265507</v>
       </c>
       <c r="B53" t="n">
-        <v>98465</v>
+        <v>98360</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6370,13 +6370,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721232</v>
+        <v>721307</v>
       </c>
       <c r="R53" t="n">
-        <v>6380313</v>
+        <v>6380360</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6437,45 +6437,64 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B54" t="n">
-        <v>106037</v>
+        <v>43228</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R54" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6539,64 +6558,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B55" t="n">
-        <v>43228</v>
+        <v>106037</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R55" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265484</v>
+        <v>127265494</v>
       </c>
       <c r="B56" t="n">
-        <v>98360</v>
+        <v>98464</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6671,26 +6671,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721220</v>
+        <v>721247</v>
       </c>
       <c r="R56" t="n">
-        <v>6380355</v>
+        <v>6380342</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -6771,27 +6771,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265471</v>
+        <v>127265481</v>
       </c>
       <c r="B57" t="n">
-        <v>106037</v>
+        <v>109266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721232</v>
+        <v>721220</v>
       </c>
       <c r="R57" t="n">
-        <v>6380313</v>
+        <v>6380355</v>
       </c>
       <c r="S57" t="n">
         <v>7</v>
@@ -6873,10 +6873,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265481</v>
+        <v>127265622</v>
       </c>
       <c r="B58" t="n">
-        <v>109266</v>
+        <v>103895</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6884,37 +6884,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721220</v>
+        <v>721252</v>
       </c>
       <c r="R58" t="n">
-        <v>6380355</v>
+        <v>6380274</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6975,37 +6984,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265622</v>
+        <v>127265484</v>
       </c>
       <c r="B59" t="n">
-        <v>103895</v>
+        <v>98360</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220164</v>
+        <v>223591</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7015,17 +7024,17 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721252</v>
+        <v>721220</v>
       </c>
       <c r="R59" t="n">
-        <v>6380274</v>
+        <v>6380355</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7086,54 +7095,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265494</v>
+        <v>127265471</v>
       </c>
       <c r="B60" t="n">
-        <v>98464</v>
+        <v>106037</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721247</v>
+        <v>721232</v>
       </c>
       <c r="R60" t="n">
-        <v>6380342</v>
+        <v>6380313</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7197,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265474</v>
+        <v>127265617</v>
       </c>
       <c r="B61" t="n">
-        <v>98360</v>
+        <v>98464</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7208,26 +7208,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7235,19 +7235,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721232</v>
+        <v>721357</v>
       </c>
       <c r="R61" t="n">
-        <v>6380313</v>
+        <v>6380338</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7308,37 +7313,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265504</v>
+        <v>127265533</v>
       </c>
       <c r="B62" t="n">
-        <v>98360</v>
+        <v>99193</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7348,17 +7353,17 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721272</v>
+        <v>721484</v>
       </c>
       <c r="R62" t="n">
-        <v>6380356</v>
+        <v>6380450</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7419,7 +7424,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265546</v>
+        <v>127265474</v>
       </c>
       <c r="B63" t="n">
         <v>98360</v>
@@ -7449,7 +7454,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7459,17 +7464,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721560</v>
+        <v>721232</v>
       </c>
       <c r="R63" t="n">
-        <v>6380582</v>
+        <v>6380313</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7512,7 +7517,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7530,45 +7535,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265505</v>
+        <v>127265504</v>
       </c>
       <c r="B64" t="n">
-        <v>106037</v>
+        <v>98360</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721284</v>
+        <v>721272</v>
       </c>
       <c r="R64" t="n">
-        <v>6380359</v>
+        <v>6380356</v>
       </c>
       <c r="S64" t="n">
         <v>7</v>
@@ -7632,48 +7646,57 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265488</v>
+        <v>127265546</v>
       </c>
       <c r="B65" t="n">
-        <v>106037</v>
+        <v>98360</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721231</v>
+        <v>721560</v>
       </c>
       <c r="R65" t="n">
-        <v>6380342</v>
+        <v>6380582</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7716,7 +7739,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7734,27 +7757,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265533</v>
+        <v>127265505</v>
       </c>
       <c r="B66" t="n">
-        <v>99193</v>
+        <v>106037</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222361</v>
+        <v>220785</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7762,29 +7785,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721484</v>
+        <v>721284</v>
       </c>
       <c r="R66" t="n">
-        <v>6380450</v>
+        <v>6380359</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7845,57 +7859,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265517</v>
+        <v>127265488</v>
       </c>
       <c r="B67" t="n">
-        <v>98420</v>
+        <v>106037</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721330</v>
+        <v>721231</v>
       </c>
       <c r="R67" t="n">
-        <v>6380365</v>
+        <v>6380342</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8067,10 +8072,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265617</v>
+        <v>127265517</v>
       </c>
       <c r="B69" t="n">
-        <v>98464</v>
+        <v>98420</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8078,26 +8083,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8105,24 +8110,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721357</v>
+        <v>721330</v>
       </c>
       <c r="R69" t="n">
-        <v>6380338</v>
+        <v>6380365</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8183,10 +8183,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127265476</v>
+        <v>127265525</v>
       </c>
       <c r="B70" t="n">
-        <v>98360</v>
+        <v>98420</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,26 +8194,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8223,17 +8223,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>721209</v>
+        <v>721433</v>
       </c>
       <c r="R70" t="n">
-        <v>6380333</v>
+        <v>6380417</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8263,11 +8263,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8299,10 +8294,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127265525</v>
+        <v>127265476</v>
       </c>
       <c r="B71" t="n">
-        <v>98420</v>
+        <v>98360</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8310,26 +8305,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8339,17 +8334,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>721433</v>
+        <v>721209</v>
       </c>
       <c r="R71" t="n">
-        <v>6380417</v>
+        <v>6380333</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8379,6 +8374,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265528</v>
+        <v>127265586</v>
       </c>
       <c r="B72" t="n">
-        <v>98360</v>
+        <v>98465</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721460</v>
+        <v>721591</v>
       </c>
       <c r="R72" t="n">
-        <v>6380438</v>
+        <v>6380497</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8521,54 +8521,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265586</v>
+        <v>127265526</v>
       </c>
       <c r="B73" t="n">
-        <v>98465</v>
+        <v>109266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721591</v>
+        <v>721433</v>
       </c>
       <c r="R73" t="n">
-        <v>6380497</v>
+        <v>6380417</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8601,6 +8592,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8632,45 +8628,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127265526</v>
+        <v>127265528</v>
       </c>
       <c r="B74" t="n">
-        <v>109266</v>
+        <v>98360</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>721433</v>
+        <v>721460</v>
       </c>
       <c r="R74" t="n">
-        <v>6380417</v>
+        <v>6380438</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8703,11 +8708,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9291,57 +9291,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265489</v>
+        <v>127265493</v>
       </c>
       <c r="B80" t="n">
-        <v>98360</v>
+        <v>106037</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721231</v>
+        <v>721247</v>
       </c>
       <c r="R80" t="n">
         <v>6380342</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9402,7 +9393,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265493</v>
+        <v>127265491</v>
       </c>
       <c r="B81" t="n">
         <v>106037</v>
@@ -9437,10 +9428,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721247</v>
+        <v>721239</v>
       </c>
       <c r="R81" t="n">
-        <v>6380342</v>
+        <v>6380330</v>
       </c>
       <c r="S81" t="n">
         <v>7</v>
@@ -9504,48 +9495,57 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265491</v>
+        <v>127265489</v>
       </c>
       <c r="B82" t="n">
-        <v>106037</v>
+        <v>98360</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721239</v>
+        <v>721231</v>
       </c>
       <c r="R82" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9708,57 +9708,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265499</v>
+        <v>127265549</v>
       </c>
       <c r="B84" t="n">
-        <v>98360</v>
+        <v>106037</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721247</v>
+        <v>721590</v>
       </c>
       <c r="R84" t="n">
-        <v>6380342</v>
+        <v>6380571</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9801,7 +9792,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9819,7 +9810,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265549</v>
+        <v>127265511</v>
       </c>
       <c r="B85" t="n">
         <v>106037</v>
@@ -9850,17 +9841,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721590</v>
+        <v>721315</v>
       </c>
       <c r="R85" t="n">
-        <v>6380571</v>
+        <v>6380362</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9903,7 +9894,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9921,48 +9912,57 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265511</v>
+        <v>127265499</v>
       </c>
       <c r="B86" t="n">
-        <v>106037</v>
+        <v>98360</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721315</v>
+        <v>721247</v>
       </c>
       <c r="R86" t="n">
-        <v>6380362</v>
+        <v>6380342</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -3071,48 +3071,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265496</v>
+        <v>127265610</v>
       </c>
       <c r="B23" t="n">
-        <v>109266</v>
+        <v>98360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R23" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3173,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127265610</v>
+        <v>127265590</v>
       </c>
       <c r="B24" t="n">
-        <v>98360</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,21 +3193,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3217,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721466</v>
+        <v>721580</v>
       </c>
       <c r="R24" t="n">
-        <v>6380394</v>
+        <v>6380472</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,6 +3264,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3266,7 +3280,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3284,57 +3298,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265590</v>
+        <v>127265496</v>
       </c>
       <c r="B25" t="n">
-        <v>98478</v>
+        <v>109266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721580</v>
+        <v>721247</v>
       </c>
       <c r="R25" t="n">
-        <v>6380472</v>
+        <v>6380342</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3366,11 +3371,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127296661</v>
+        <v>127265584</v>
       </c>
       <c r="B34" t="n">
-        <v>58334</v>
+        <v>98465</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,46 +4286,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>219847</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721560</v>
+        <v>721601</v>
       </c>
       <c r="R34" t="n">
-        <v>6380582</v>
+        <v>6380518</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4386,54 +4386,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265584</v>
+        <v>127265594</v>
       </c>
       <c r="B35" t="n">
-        <v>98465</v>
+        <v>109266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721601</v>
+        <v>721572</v>
       </c>
       <c r="R35" t="n">
-        <v>6380518</v>
+        <v>6380434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,6 +4457,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,48 +4493,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265594</v>
+        <v>127296661</v>
       </c>
       <c r="B36" t="n">
-        <v>109266</v>
+        <v>58334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721572</v>
+        <v>721560</v>
       </c>
       <c r="R36" t="n">
-        <v>6380434</v>
+        <v>6380582</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,11 +4575,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -7197,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265617</v>
+        <v>127265495</v>
       </c>
       <c r="B61" t="n">
-        <v>98464</v>
+        <v>98420</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7208,26 +7208,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7235,24 +7235,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721357</v>
+        <v>721247</v>
       </c>
       <c r="R61" t="n">
-        <v>6380338</v>
+        <v>6380342</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7313,37 +7308,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265533</v>
+        <v>127265517</v>
       </c>
       <c r="B62" t="n">
-        <v>99193</v>
+        <v>98420</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7357,10 +7352,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721484</v>
+        <v>721330</v>
       </c>
       <c r="R62" t="n">
-        <v>6380450</v>
+        <v>6380365</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7424,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265474</v>
+        <v>127265617</v>
       </c>
       <c r="B63" t="n">
-        <v>98360</v>
+        <v>98464</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7435,26 +7430,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7462,19 +7457,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721232</v>
+        <v>721357</v>
       </c>
       <c r="R63" t="n">
-        <v>6380313</v>
+        <v>6380338</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7535,37 +7535,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265504</v>
+        <v>127265533</v>
       </c>
       <c r="B64" t="n">
-        <v>98360</v>
+        <v>99193</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7575,17 +7575,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721272</v>
+        <v>721484</v>
       </c>
       <c r="R64" t="n">
-        <v>6380356</v>
+        <v>6380450</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265546</v>
+        <v>127265474</v>
       </c>
       <c r="B65" t="n">
         <v>98360</v>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7686,17 +7686,17 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721560</v>
+        <v>721232</v>
       </c>
       <c r="R65" t="n">
-        <v>6380582</v>
+        <v>6380313</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7757,45 +7757,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265505</v>
+        <v>127265504</v>
       </c>
       <c r="B66" t="n">
-        <v>106037</v>
+        <v>98360</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721284</v>
+        <v>721272</v>
       </c>
       <c r="R66" t="n">
-        <v>6380359</v>
+        <v>6380356</v>
       </c>
       <c r="S66" t="n">
         <v>7</v>
@@ -7859,48 +7868,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265488</v>
+        <v>127265546</v>
       </c>
       <c r="B67" t="n">
-        <v>106037</v>
+        <v>98360</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721231</v>
+        <v>721560</v>
       </c>
       <c r="R67" t="n">
-        <v>6380342</v>
+        <v>6380582</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7943,7 +7961,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7961,54 +7979,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265495</v>
+        <v>127265505</v>
       </c>
       <c r="B68" t="n">
-        <v>98420</v>
+        <v>106037</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721247</v>
+        <v>721284</v>
       </c>
       <c r="R68" t="n">
-        <v>6380342</v>
+        <v>6380359</v>
       </c>
       <c r="S68" t="n">
         <v>7</v>
@@ -8072,57 +8081,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265517</v>
+        <v>127265488</v>
       </c>
       <c r="B69" t="n">
-        <v>98420</v>
+        <v>106037</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721330</v>
+        <v>721231</v>
       </c>
       <c r="R69" t="n">
-        <v>6380365</v>
+        <v>6380342</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8952,57 +8952,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127265508</v>
+        <v>127265513</v>
       </c>
       <c r="B77" t="n">
-        <v>98420</v>
+        <v>109266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721307</v>
+        <v>721315</v>
       </c>
       <c r="R77" t="n">
-        <v>6380360</v>
+        <v>6380362</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9063,48 +9054,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127265513</v>
+        <v>127265508</v>
       </c>
       <c r="B78" t="n">
-        <v>109266</v>
+        <v>98420</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721315</v>
+        <v>721307</v>
       </c>
       <c r="R78" t="n">
-        <v>6380362</v>
+        <v>6380360</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9291,27 +9291,27 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265493</v>
+        <v>127265605</v>
       </c>
       <c r="B80" t="n">
-        <v>106037</v>
+        <v>109266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9322,17 +9322,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R80" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265491</v>
+        <v>127265493</v>
       </c>
       <c r="B81" t="n">
         <v>106037</v>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R81" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S81" t="n">
         <v>7</v>
@@ -9495,57 +9495,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265489</v>
+        <v>127265491</v>
       </c>
       <c r="B82" t="n">
-        <v>98360</v>
+        <v>106037</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721231</v>
+        <v>721239</v>
       </c>
       <c r="R82" t="n">
-        <v>6380342</v>
+        <v>6380330</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9606,48 +9597,57 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127265605</v>
+        <v>127265489</v>
       </c>
       <c r="B83" t="n">
-        <v>109266</v>
+        <v>98360</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721466</v>
+        <v>721231</v>
       </c>
       <c r="R83" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265497</v>
+        <v>127265479</v>
       </c>
       <c r="B14" t="n">
-        <v>98465</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,26 +2110,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721247</v>
+        <v>721212</v>
       </c>
       <c r="R14" t="n">
-        <v>6380342</v>
+        <v>6380346</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265518</v>
+        <v>127265530</v>
       </c>
       <c r="B15" t="n">
-        <v>98465</v>
+        <v>98479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721330</v>
+        <v>721463</v>
       </c>
       <c r="R15" t="n">
-        <v>6380365</v>
+        <v>6380440</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265492</v>
+        <v>127265587</v>
       </c>
       <c r="B16" t="n">
-        <v>98465</v>
+        <v>105478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721239</v>
+        <v>721591</v>
       </c>
       <c r="R16" t="n">
-        <v>6380330</v>
+        <v>6380497</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265587</v>
+        <v>127265497</v>
       </c>
       <c r="B17" t="n">
-        <v>105477</v>
+        <v>98466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,26 +2443,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721591</v>
+        <v>721247</v>
       </c>
       <c r="R17" t="n">
-        <v>6380497</v>
+        <v>6380342</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2543,45 +2543,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265532</v>
+        <v>127265518</v>
       </c>
       <c r="B18" t="n">
-        <v>106037</v>
+        <v>98466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721484</v>
+        <v>721330</v>
       </c>
       <c r="R18" t="n">
-        <v>6380450</v>
+        <v>6380365</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2645,48 +2654,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265540</v>
+        <v>127265492</v>
       </c>
       <c r="B19" t="n">
-        <v>106037</v>
+        <v>98466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721546</v>
+        <v>721239</v>
       </c>
       <c r="R19" t="n">
-        <v>6380552</v>
+        <v>6380330</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2729,7 +2747,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2747,57 +2765,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265479</v>
+        <v>127265600</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>109267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721212</v>
+        <v>721547</v>
       </c>
       <c r="R20" t="n">
-        <v>6380346</v>
+        <v>6380409</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2858,54 +2867,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265530</v>
+        <v>127265532</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>106038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223621</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721463</v>
+        <v>721484</v>
       </c>
       <c r="R21" t="n">
-        <v>6380440</v>
+        <v>6380450</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,27 +2969,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265600</v>
+        <v>127265540</v>
       </c>
       <c r="B22" t="n">
-        <v>109266</v>
+        <v>106038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3000,14 +3000,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721547</v>
+        <v>721546</v>
       </c>
       <c r="R22" t="n">
-        <v>6380409</v>
+        <v>6380552</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3071,57 +3071,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265610</v>
+        <v>127265496</v>
       </c>
       <c r="B23" t="n">
-        <v>98360</v>
+        <v>109267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721466</v>
+        <v>721247</v>
       </c>
       <c r="R23" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3185,7 +3176,7 @@
         <v>127265590</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>98479</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3298,48 +3289,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265496</v>
+        <v>127265610</v>
       </c>
       <c r="B25" t="n">
-        <v>109266</v>
+        <v>98361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R25" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3400,54 +3400,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265473</v>
+        <v>127265503</v>
       </c>
       <c r="B26" t="n">
-        <v>98420</v>
+        <v>106038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721232</v>
+        <v>721272</v>
       </c>
       <c r="R26" t="n">
-        <v>6380313</v>
+        <v>6380356</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3511,10 +3502,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265475</v>
+        <v>127265624</v>
       </c>
       <c r="B27" t="n">
-        <v>98465</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,21 +3513,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3551,14 +3542,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721209</v>
+        <v>721199</v>
       </c>
       <c r="R27" t="n">
-        <v>6380333</v>
+        <v>6380248</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3622,45 +3613,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265503</v>
+        <v>127265473</v>
       </c>
       <c r="B28" t="n">
-        <v>106037</v>
+        <v>98421</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721272</v>
+        <v>721232</v>
       </c>
       <c r="R28" t="n">
-        <v>6380356</v>
+        <v>6380313</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265624</v>
+        <v>127265475</v>
       </c>
       <c r="B29" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3735,21 +3735,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721199</v>
+        <v>721209</v>
       </c>
       <c r="R29" t="n">
-        <v>6380248</v>
+        <v>6380333</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265606</v>
+        <v>127265598</v>
       </c>
       <c r="B30" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721475</v>
+        <v>721557</v>
       </c>
       <c r="R30" t="n">
-        <v>6380396</v>
+        <v>6380422</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265548</v>
+        <v>127265606</v>
       </c>
       <c r="B31" t="n">
-        <v>99659</v>
+        <v>98466</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3957,31 +3957,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>174</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721578</v>
+        <v>721475</v>
       </c>
       <c r="R31" t="n">
-        <v>6380576</v>
+        <v>6380396</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4028,11 +4028,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4044,7 +4039,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4062,57 +4057,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265598</v>
+        <v>127265486</v>
       </c>
       <c r="B32" t="n">
-        <v>98465</v>
+        <v>109267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721557</v>
+        <v>721231</v>
       </c>
       <c r="R32" t="n">
-        <v>6380422</v>
+        <v>6380342</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4155,7 +4141,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4173,45 +4159,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265486</v>
+        <v>127265548</v>
       </c>
       <c r="B33" t="n">
-        <v>109266</v>
+        <v>99660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>174</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721231</v>
+        <v>721578</v>
       </c>
       <c r="R33" t="n">
-        <v>6380342</v>
+        <v>6380576</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4246,6 +4241,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127265584</v>
+        <v>127296661</v>
       </c>
       <c r="B34" t="n">
-        <v>98465</v>
+        <v>58334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,46 +4286,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721601</v>
+        <v>721560</v>
       </c>
       <c r="R34" t="n">
-        <v>6380518</v>
+        <v>6380582</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4389,7 +4389,7 @@
         <v>127265594</v>
       </c>
       <c r="B35" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296661</v>
+        <v>127265584</v>
       </c>
       <c r="B36" t="n">
-        <v>58334</v>
+        <v>98466</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4504,46 +4504,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721560</v>
+        <v>721601</v>
       </c>
       <c r="R36" t="n">
-        <v>6380582</v>
+        <v>6380518</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127265612</v>
+        <v>127265566</v>
       </c>
       <c r="B37" t="n">
-        <v>98479</v>
+        <v>98361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,43 +4615,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721424</v>
+        <v>721615</v>
       </c>
       <c r="R37" t="n">
-        <v>6380372</v>
+        <v>6380615</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4697,7 +4688,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4715,10 +4706,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265541</v>
+        <v>127265582</v>
       </c>
       <c r="B38" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4743,17 +4734,26 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721546</v>
+        <v>721601</v>
       </c>
       <c r="R38" t="n">
-        <v>6380552</v>
+        <v>6380518</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265566</v>
+        <v>127265541</v>
       </c>
       <c r="B39" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4848,14 +4848,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721615</v>
+        <v>721546</v>
       </c>
       <c r="R39" t="n">
-        <v>6380615</v>
+        <v>6380552</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265582</v>
+        <v>127265612</v>
       </c>
       <c r="B40" t="n">
-        <v>98360</v>
+        <v>98480</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,21 +4930,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721601</v>
+        <v>721424</v>
       </c>
       <c r="R40" t="n">
-        <v>6380518</v>
+        <v>6380372</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5033,7 +5033,7 @@
         <v>127265579</v>
       </c>
       <c r="B41" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>127265545</v>
       </c>
       <c r="B42" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>127265623</v>
       </c>
       <c r="B43" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,57 +5345,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265515</v>
+        <v>127265534</v>
       </c>
       <c r="B44" t="n">
-        <v>98420</v>
+        <v>109267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721315</v>
+        <v>721493</v>
       </c>
       <c r="R44" t="n">
-        <v>6380362</v>
+        <v>6380446</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5456,45 +5447,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265534</v>
+        <v>127265571</v>
       </c>
       <c r="B45" t="n">
-        <v>109266</v>
+        <v>98361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721493</v>
+        <v>721594</v>
       </c>
       <c r="R45" t="n">
-        <v>6380446</v>
+        <v>6380563</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265571</v>
+        <v>127265515</v>
       </c>
       <c r="B46" t="n">
-        <v>98360</v>
+        <v>98421</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5569,26 +5569,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5598,17 +5598,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721594</v>
+        <v>721315</v>
       </c>
       <c r="R46" t="n">
-        <v>6380563</v>
+        <v>6380362</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127265626</v>
+        <v>127265478</v>
       </c>
       <c r="B47" t="n">
-        <v>98360</v>
+        <v>98421</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,26 +5680,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721183</v>
+        <v>721212</v>
       </c>
       <c r="R47" t="n">
-        <v>6380248</v>
+        <v>6380346</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127265597</v>
+        <v>127265626</v>
       </c>
       <c r="B48" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5824,13 +5824,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721557</v>
+        <v>721183</v>
       </c>
       <c r="R48" t="n">
-        <v>6380422</v>
+        <v>6380248</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127265478</v>
+        <v>127265597</v>
       </c>
       <c r="B49" t="n">
-        <v>98420</v>
+        <v>98361</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,26 +5902,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721212</v>
+        <v>721557</v>
       </c>
       <c r="R49" t="n">
-        <v>6380346</v>
+        <v>6380422</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127265593</v>
+        <v>127265628</v>
       </c>
       <c r="B50" t="n">
-        <v>98465</v>
+        <v>98361</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,37 +6013,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721572</v>
+        <v>721173</v>
       </c>
       <c r="R50" t="n">
-        <v>6380434</v>
+        <v>6380248</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6104,10 +6113,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127265472</v>
+        <v>127265507</v>
       </c>
       <c r="B51" t="n">
-        <v>98465</v>
+        <v>98361</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,21 +6124,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6148,13 +6157,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721232</v>
+        <v>721307</v>
       </c>
       <c r="R51" t="n">
-        <v>6380313</v>
+        <v>6380360</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6215,10 +6224,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127265628</v>
+        <v>127265593</v>
       </c>
       <c r="B52" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6226,46 +6235,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721173</v>
+        <v>721572</v>
       </c>
       <c r="R52" t="n">
-        <v>6380248</v>
+        <v>6380434</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127265507</v>
+        <v>127265472</v>
       </c>
       <c r="B53" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6370,13 +6370,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721307</v>
+        <v>721232</v>
       </c>
       <c r="R53" t="n">
-        <v>6380360</v>
+        <v>6380313</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>127265583</v>
       </c>
       <c r="B55" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6660,54 +6660,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265494</v>
+        <v>127265481</v>
       </c>
       <c r="B56" t="n">
-        <v>98464</v>
+        <v>109267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721247</v>
+        <v>721220</v>
       </c>
       <c r="R56" t="n">
-        <v>6380342</v>
+        <v>6380355</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -6771,10 +6762,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265481</v>
+        <v>127265622</v>
       </c>
       <c r="B57" t="n">
-        <v>109266</v>
+        <v>103896</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,37 +6773,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721220</v>
+        <v>721252</v>
       </c>
       <c r="R57" t="n">
-        <v>6380355</v>
+        <v>6380274</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6873,32 +6873,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265622</v>
+        <v>127265494</v>
       </c>
       <c r="B58" t="n">
-        <v>103895</v>
+        <v>98465</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220164</v>
+        <v>219862</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6913,17 +6913,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721252</v>
+        <v>721247</v>
       </c>
       <c r="R58" t="n">
-        <v>6380274</v>
+        <v>6380342</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6984,54 +6984,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265484</v>
+        <v>127265471</v>
       </c>
       <c r="B59" t="n">
-        <v>98360</v>
+        <v>106038</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R59" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7095,45 +7086,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265471</v>
+        <v>127265484</v>
       </c>
       <c r="B60" t="n">
-        <v>106037</v>
+        <v>98361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721232</v>
+        <v>721220</v>
       </c>
       <c r="R60" t="n">
-        <v>6380313</v>
+        <v>6380355</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7197,54 +7197,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265495</v>
+        <v>127265505</v>
       </c>
       <c r="B61" t="n">
-        <v>98420</v>
+        <v>106038</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721247</v>
+        <v>721284</v>
       </c>
       <c r="R61" t="n">
-        <v>6380342</v>
+        <v>6380359</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7308,57 +7299,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265517</v>
+        <v>127265488</v>
       </c>
       <c r="B62" t="n">
-        <v>98420</v>
+        <v>106038</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721330</v>
+        <v>721231</v>
       </c>
       <c r="R62" t="n">
-        <v>6380365</v>
+        <v>6380342</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7419,10 +7401,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265617</v>
+        <v>127265504</v>
       </c>
       <c r="B63" t="n">
-        <v>98464</v>
+        <v>98361</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,26 +7412,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7457,24 +7439,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721357</v>
+        <v>721272</v>
       </c>
       <c r="R63" t="n">
-        <v>6380338</v>
+        <v>6380356</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7535,37 +7512,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265533</v>
+        <v>127265474</v>
       </c>
       <c r="B64" t="n">
-        <v>99193</v>
+        <v>98361</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222361</v>
+        <v>223591</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7575,17 +7552,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721484</v>
+        <v>721232</v>
       </c>
       <c r="R64" t="n">
-        <v>6380450</v>
+        <v>6380313</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7646,10 +7623,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265474</v>
+        <v>127265546</v>
       </c>
       <c r="B65" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7676,7 +7653,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7686,17 +7663,17 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721232</v>
+        <v>721560</v>
       </c>
       <c r="R65" t="n">
-        <v>6380313</v>
+        <v>6380582</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7739,7 +7716,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7757,37 +7734,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265504</v>
+        <v>127265533</v>
       </c>
       <c r="B66" t="n">
-        <v>98360</v>
+        <v>99194</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7797,17 +7774,17 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721272</v>
+        <v>721484</v>
       </c>
       <c r="R66" t="n">
-        <v>6380356</v>
+        <v>6380450</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7868,10 +7845,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265546</v>
+        <v>127265495</v>
       </c>
       <c r="B67" t="n">
-        <v>98360</v>
+        <v>98421</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,26 +7856,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7908,17 +7885,17 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721560</v>
+        <v>721247</v>
       </c>
       <c r="R67" t="n">
-        <v>6380582</v>
+        <v>6380342</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7961,7 +7938,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7979,48 +7956,62 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265505</v>
+        <v>127265617</v>
       </c>
       <c r="B68" t="n">
-        <v>106037</v>
+        <v>98465</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721284</v>
+        <v>721357</v>
       </c>
       <c r="R68" t="n">
-        <v>6380359</v>
+        <v>6380338</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8081,48 +8072,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265488</v>
+        <v>127265517</v>
       </c>
       <c r="B69" t="n">
-        <v>106037</v>
+        <v>98421</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721231</v>
+        <v>721330</v>
       </c>
       <c r="R69" t="n">
-        <v>6380342</v>
+        <v>6380365</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8183,10 +8183,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127265525</v>
+        <v>127265476</v>
       </c>
       <c r="B70" t="n">
-        <v>98420</v>
+        <v>98361</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,26 +8194,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8223,17 +8223,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>721433</v>
+        <v>721209</v>
       </c>
       <c r="R70" t="n">
-        <v>6380417</v>
+        <v>6380333</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8263,6 +8263,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8294,10 +8299,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127265476</v>
+        <v>127265525</v>
       </c>
       <c r="B71" t="n">
-        <v>98360</v>
+        <v>98421</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8305,26 +8310,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8334,17 +8339,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>721209</v>
+        <v>721433</v>
       </c>
       <c r="R71" t="n">
-        <v>6380333</v>
+        <v>6380417</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8374,11 +8379,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8410,54 +8410,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265586</v>
+        <v>127265526</v>
       </c>
       <c r="B72" t="n">
-        <v>98465</v>
+        <v>109267</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721591</v>
+        <v>721433</v>
       </c>
       <c r="R72" t="n">
-        <v>6380497</v>
+        <v>6380417</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8490,6 +8481,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8521,45 +8517,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265526</v>
+        <v>127265528</v>
       </c>
       <c r="B73" t="n">
-        <v>109266</v>
+        <v>98361</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721433</v>
+        <v>721460</v>
       </c>
       <c r="R73" t="n">
-        <v>6380417</v>
+        <v>6380438</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8592,11 +8597,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8628,10 +8628,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127265528</v>
+        <v>127265586</v>
       </c>
       <c r="B74" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8639,21 +8639,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8668,14 +8668,14 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>721460</v>
+        <v>721591</v>
       </c>
       <c r="R74" t="n">
-        <v>6380438</v>
+        <v>6380497</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8739,54 +8739,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B75" t="n">
-        <v>98465</v>
+        <v>109267</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R75" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8850,45 +8841,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B76" t="n">
-        <v>109266</v>
+        <v>98466</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R76" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8955,7 +8955,7 @@
         <v>127265513</v>
       </c>
       <c r="B77" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>127265508</v>
       </c>
       <c r="B78" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9291,27 +9291,27 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265605</v>
+        <v>127265491</v>
       </c>
       <c r="B80" t="n">
-        <v>109266</v>
+        <v>106038</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9322,17 +9322,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721466</v>
+        <v>721239</v>
       </c>
       <c r="R80" t="n">
-        <v>6380394</v>
+        <v>6380330</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>127265493</v>
       </c>
       <c r="B81" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9495,27 +9495,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265491</v>
+        <v>127265605</v>
       </c>
       <c r="B82" t="n">
-        <v>106037</v>
+        <v>109267</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9526,17 +9526,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721239</v>
+        <v>721466</v>
       </c>
       <c r="R82" t="n">
-        <v>6380330</v>
+        <v>6380394</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>127265489</v>
       </c>
       <c r="B83" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265549</v>
+        <v>127265511</v>
       </c>
       <c r="B84" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9739,17 +9739,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721590</v>
+        <v>721315</v>
       </c>
       <c r="R84" t="n">
-        <v>6380571</v>
+        <v>6380362</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9810,10 +9810,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265511</v>
+        <v>127265549</v>
       </c>
       <c r="B85" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9841,17 +9841,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721315</v>
+        <v>721590</v>
       </c>
       <c r="R85" t="n">
-        <v>6380362</v>
+        <v>6380571</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9915,7 +9915,7 @@
         <v>127265499</v>
       </c>
       <c r="B86" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>127265572</v>
       </c>
       <c r="B87" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10134,45 +10134,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127265483</v>
+        <v>127265500</v>
       </c>
       <c r="B88" t="n">
-        <v>106037</v>
+        <v>98361</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>721220</v>
+        <v>721263</v>
       </c>
       <c r="R88" t="n">
-        <v>6380355</v>
+        <v>6380356</v>
       </c>
       <c r="S88" t="n">
         <v>7</v>
@@ -10239,7 +10248,7 @@
         <v>127265519</v>
       </c>
       <c r="B89" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10338,10 +10347,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265500</v>
+        <v>127265506</v>
       </c>
       <c r="B90" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10368,7 +10377,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10382,10 +10391,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721263</v>
+        <v>721284</v>
       </c>
       <c r="R90" t="n">
-        <v>6380356</v>
+        <v>6380359</v>
       </c>
       <c r="S90" t="n">
         <v>7</v>
@@ -10449,54 +10458,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127265506</v>
+        <v>127265483</v>
       </c>
       <c r="B91" t="n">
-        <v>98360</v>
+        <v>106038</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>721284</v>
+        <v>721220</v>
       </c>
       <c r="R91" t="n">
-        <v>6380359</v>
+        <v>6380355</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265479</v>
+        <v>127265497</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,26 +2110,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721212</v>
+        <v>721247</v>
       </c>
       <c r="R14" t="n">
-        <v>6380346</v>
+        <v>6380342</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265530</v>
+        <v>127265518</v>
       </c>
       <c r="B15" t="n">
-        <v>98479</v>
+        <v>98466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721463</v>
+        <v>721330</v>
       </c>
       <c r="R15" t="n">
-        <v>6380440</v>
+        <v>6380365</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265587</v>
+        <v>127265492</v>
       </c>
       <c r="B16" t="n">
-        <v>105478</v>
+        <v>98466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721591</v>
+        <v>721239</v>
       </c>
       <c r="R16" t="n">
-        <v>6380497</v>
+        <v>6380330</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2432,57 +2432,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265497</v>
+        <v>127265600</v>
       </c>
       <c r="B17" t="n">
-        <v>98466</v>
+        <v>109267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721247</v>
+        <v>721547</v>
       </c>
       <c r="R17" t="n">
-        <v>6380342</v>
+        <v>6380409</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2543,54 +2534,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265518</v>
+        <v>127265532</v>
       </c>
       <c r="B18" t="n">
-        <v>98466</v>
+        <v>106038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721330</v>
+        <v>721484</v>
       </c>
       <c r="R18" t="n">
-        <v>6380365</v>
+        <v>6380450</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2654,57 +2636,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265492</v>
+        <v>127265540</v>
       </c>
       <c r="B19" t="n">
-        <v>98466</v>
+        <v>106038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721239</v>
+        <v>721546</v>
       </c>
       <c r="R19" t="n">
-        <v>6380330</v>
+        <v>6380552</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2747,7 +2720,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2765,45 +2738,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265600</v>
+        <v>127265587</v>
       </c>
       <c r="B20" t="n">
-        <v>109267</v>
+        <v>105478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721547</v>
+        <v>721591</v>
       </c>
       <c r="R20" t="n">
-        <v>6380409</v>
+        <v>6380497</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2867,48 +2849,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265532</v>
+        <v>127265479</v>
       </c>
       <c r="B21" t="n">
-        <v>106038</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721484</v>
+        <v>721212</v>
       </c>
       <c r="R21" t="n">
-        <v>6380450</v>
+        <v>6380346</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2969,45 +2960,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265540</v>
+        <v>127265530</v>
       </c>
       <c r="B22" t="n">
-        <v>106038</v>
+        <v>98479</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>223621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721546</v>
+        <v>721463</v>
       </c>
       <c r="R22" t="n">
-        <v>6380552</v>
+        <v>6380440</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265598</v>
+        <v>127265548</v>
       </c>
       <c r="B30" t="n">
-        <v>98466</v>
+        <v>99660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3846,31 +3846,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>174</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3879,13 +3879,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721557</v>
+        <v>721578</v>
       </c>
       <c r="R30" t="n">
-        <v>6380422</v>
+        <v>6380576</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,6 +3917,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3928,7 +3933,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3946,57 +3951,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265606</v>
+        <v>127265486</v>
       </c>
       <c r="B31" t="n">
-        <v>98466</v>
+        <v>109267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721475</v>
+        <v>721231</v>
       </c>
       <c r="R31" t="n">
-        <v>6380396</v>
+        <v>6380342</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4057,48 +4053,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265486</v>
+        <v>127265598</v>
       </c>
       <c r="B32" t="n">
-        <v>109267</v>
+        <v>98466</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721231</v>
+        <v>721557</v>
       </c>
       <c r="R32" t="n">
-        <v>6380342</v>
+        <v>6380422</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4141,7 +4146,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4159,10 +4164,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265548</v>
+        <v>127265606</v>
       </c>
       <c r="B33" t="n">
-        <v>99660</v>
+        <v>98466</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4170,31 +4175,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>174</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4203,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721578</v>
+        <v>721475</v>
       </c>
       <c r="R33" t="n">
-        <v>6380576</v>
+        <v>6380396</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4241,11 +4246,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4275,57 +4275,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127296661</v>
+        <v>127265594</v>
       </c>
       <c r="B34" t="n">
-        <v>58334</v>
+        <v>109267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721560</v>
+        <v>721572</v>
       </c>
       <c r="R34" t="n">
-        <v>6380582</v>
+        <v>6380434</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4357,6 +4348,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4368,7 +4364,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4386,45 +4382,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265594</v>
+        <v>127265584</v>
       </c>
       <c r="B35" t="n">
-        <v>109267</v>
+        <v>98466</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721572</v>
+        <v>721601</v>
       </c>
       <c r="R35" t="n">
-        <v>6380434</v>
+        <v>6380518</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4457,11 +4462,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,10 +4493,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265584</v>
+        <v>127296661</v>
       </c>
       <c r="B36" t="n">
-        <v>98466</v>
+        <v>58334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4504,46 +4504,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721601</v>
+        <v>721560</v>
       </c>
       <c r="R36" t="n">
-        <v>6380518</v>
+        <v>6380582</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127265566</v>
+        <v>127265612</v>
       </c>
       <c r="B37" t="n">
-        <v>98361</v>
+        <v>98480</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,34 +4615,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721615</v>
+        <v>721424</v>
       </c>
       <c r="R37" t="n">
-        <v>6380615</v>
+        <v>6380372</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,7 +4697,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4706,7 +4715,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265582</v>
+        <v>127265566</v>
       </c>
       <c r="B38" t="n">
         <v>98361</v>
@@ -4734,26 +4743,17 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721601</v>
+        <v>721615</v>
       </c>
       <c r="R38" t="n">
-        <v>6380518</v>
+        <v>6380615</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265541</v>
+        <v>127265582</v>
       </c>
       <c r="B39" t="n">
         <v>98361</v>
@@ -4845,17 +4845,26 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721546</v>
+        <v>721601</v>
       </c>
       <c r="R39" t="n">
-        <v>6380552</v>
+        <v>6380518</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4901,7 +4910,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4919,10 +4928,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265612</v>
+        <v>127265541</v>
       </c>
       <c r="B40" t="n">
-        <v>98480</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,43 +4939,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721424</v>
+        <v>721546</v>
       </c>
       <c r="R40" t="n">
-        <v>6380372</v>
+        <v>6380552</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127265478</v>
+        <v>127265626</v>
       </c>
       <c r="B47" t="n">
-        <v>98421</v>
+        <v>98361</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,26 +5680,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721212</v>
+        <v>721183</v>
       </c>
       <c r="R47" t="n">
-        <v>6380346</v>
+        <v>6380248</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127265626</v>
+        <v>127265597</v>
       </c>
       <c r="B48" t="n">
         <v>98361</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5824,13 +5824,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721183</v>
+        <v>721557</v>
       </c>
       <c r="R48" t="n">
-        <v>6380248</v>
+        <v>6380422</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127265597</v>
+        <v>127265478</v>
       </c>
       <c r="B49" t="n">
-        <v>98361</v>
+        <v>98421</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,26 +5902,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721557</v>
+        <v>721212</v>
       </c>
       <c r="R49" t="n">
-        <v>6380422</v>
+        <v>6380346</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265497</v>
+        <v>127265479</v>
       </c>
       <c r="B14" t="n">
-        <v>98466</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,26 +2110,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721247</v>
+        <v>721212</v>
       </c>
       <c r="R14" t="n">
-        <v>6380342</v>
+        <v>6380346</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265518</v>
+        <v>127265530</v>
       </c>
       <c r="B15" t="n">
-        <v>98466</v>
+        <v>98479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721330</v>
+        <v>721463</v>
       </c>
       <c r="R15" t="n">
-        <v>6380365</v>
+        <v>6380440</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,7 +2321,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265492</v>
+        <v>127265497</v>
       </c>
       <c r="B16" t="n">
         <v>98466</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R16" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S16" t="n">
         <v>7</v>
@@ -2432,45 +2432,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265600</v>
+        <v>127265518</v>
       </c>
       <c r="B17" t="n">
-        <v>109267</v>
+        <v>98466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721547</v>
+        <v>721330</v>
       </c>
       <c r="R17" t="n">
-        <v>6380409</v>
+        <v>6380365</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,48 +2543,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265532</v>
+        <v>127265492</v>
       </c>
       <c r="B18" t="n">
-        <v>106038</v>
+        <v>98466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721484</v>
+        <v>721239</v>
       </c>
       <c r="R18" t="n">
-        <v>6380450</v>
+        <v>6380330</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2636,7 +2654,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265540</v>
+        <v>127265532</v>
       </c>
       <c r="B19" t="n">
         <v>106038</v>
@@ -2671,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721546</v>
+        <v>721484</v>
       </c>
       <c r="R19" t="n">
-        <v>6380552</v>
+        <v>6380450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,7 +2738,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2849,57 +2867,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265479</v>
+        <v>127265540</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>106038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721212</v>
+        <v>721546</v>
       </c>
       <c r="R21" t="n">
-        <v>6380346</v>
+        <v>6380552</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2942,7 +2951,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2960,54 +2969,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265530</v>
+        <v>127265600</v>
       </c>
       <c r="B22" t="n">
-        <v>98479</v>
+        <v>109267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721463</v>
+        <v>721547</v>
       </c>
       <c r="R22" t="n">
-        <v>6380440</v>
+        <v>6380409</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127265590</v>
+        <v>127265610</v>
       </c>
       <c r="B24" t="n">
-        <v>98479</v>
+        <v>98361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,21 +3184,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223621</v>
+        <v>223591</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721580</v>
+        <v>721466</v>
       </c>
       <c r="R24" t="n">
-        <v>6380472</v>
+        <v>6380394</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,11 +3255,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3271,7 +3266,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3289,10 +3284,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265610</v>
+        <v>127265590</v>
       </c>
       <c r="B25" t="n">
-        <v>98361</v>
+        <v>98479</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3300,21 +3295,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3333,10 +3328,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721466</v>
+        <v>721580</v>
       </c>
       <c r="R25" t="n">
-        <v>6380394</v>
+        <v>6380472</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,6 +3366,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3951,48 +3951,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265486</v>
+        <v>127265598</v>
       </c>
       <c r="B31" t="n">
-        <v>109267</v>
+        <v>98466</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721231</v>
+        <v>721557</v>
       </c>
       <c r="R31" t="n">
-        <v>6380342</v>
+        <v>6380422</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4035,7 +4044,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4053,7 +4062,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265598</v>
+        <v>127265606</v>
       </c>
       <c r="B32" t="n">
         <v>98466</v>
@@ -4083,7 +4092,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4097,10 +4106,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721557</v>
+        <v>721475</v>
       </c>
       <c r="R32" t="n">
-        <v>6380422</v>
+        <v>6380396</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4146,7 +4155,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4164,57 +4173,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265606</v>
+        <v>127265486</v>
       </c>
       <c r="B33" t="n">
-        <v>98466</v>
+        <v>109267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721475</v>
+        <v>721231</v>
       </c>
       <c r="R33" t="n">
-        <v>6380396</v>
+        <v>6380342</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4275,45 +4275,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127265594</v>
+        <v>127265584</v>
       </c>
       <c r="B34" t="n">
-        <v>109267</v>
+        <v>98466</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721572</v>
+        <v>721601</v>
       </c>
       <c r="R34" t="n">
-        <v>6380434</v>
+        <v>6380518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4346,11 +4355,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,10 +4386,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265584</v>
+        <v>127296661</v>
       </c>
       <c r="B35" t="n">
-        <v>98466</v>
+        <v>58334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4393,46 +4397,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>103044</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721601</v>
+        <v>721560</v>
       </c>
       <c r="R35" t="n">
-        <v>6380518</v>
+        <v>6380582</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4475,7 +4479,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4493,57 +4497,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296661</v>
+        <v>127265594</v>
       </c>
       <c r="B36" t="n">
-        <v>58334</v>
+        <v>109267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721560</v>
+        <v>721572</v>
       </c>
       <c r="R36" t="n">
-        <v>6380582</v>
+        <v>6380434</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4575,6 +4570,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4715,7 +4715,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265566</v>
+        <v>127265541</v>
       </c>
       <c r="B38" t="n">
         <v>98361</v>
@@ -4746,14 +4746,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721615</v>
+        <v>721546</v>
       </c>
       <c r="R38" t="n">
-        <v>6380615</v>
+        <v>6380552</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265582</v>
+        <v>127265566</v>
       </c>
       <c r="B39" t="n">
         <v>98361</v>
@@ -4845,26 +4845,17 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721601</v>
+        <v>721615</v>
       </c>
       <c r="R39" t="n">
-        <v>6380518</v>
+        <v>6380615</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4910,7 +4901,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4928,7 +4919,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265541</v>
+        <v>127265582</v>
       </c>
       <c r="B40" t="n">
         <v>98361</v>
@@ -4956,17 +4947,26 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721546</v>
+        <v>721601</v>
       </c>
       <c r="R40" t="n">
-        <v>6380552</v>
+        <v>6380518</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5030,48 +5030,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127265579</v>
+        <v>127265623</v>
       </c>
       <c r="B41" t="n">
-        <v>106038</v>
+        <v>98421</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721577</v>
+        <v>721199</v>
       </c>
       <c r="R41" t="n">
-        <v>6380550</v>
+        <v>6380248</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5132,7 +5141,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265545</v>
+        <v>127265579</v>
       </c>
       <c r="B42" t="n">
         <v>106038</v>
@@ -5163,14 +5172,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721560</v>
+        <v>721577</v>
       </c>
       <c r="R42" t="n">
-        <v>6380582</v>
+        <v>6380550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5216,7 +5225,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5234,57 +5243,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127265623</v>
+        <v>127265545</v>
       </c>
       <c r="B43" t="n">
-        <v>98421</v>
+        <v>106038</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721199</v>
+        <v>721560</v>
       </c>
       <c r="R43" t="n">
-        <v>6380248</v>
+        <v>6380582</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5345,45 +5345,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265534</v>
+        <v>127265571</v>
       </c>
       <c r="B44" t="n">
-        <v>109267</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721493</v>
+        <v>721594</v>
       </c>
       <c r="R44" t="n">
-        <v>6380446</v>
+        <v>6380563</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5447,54 +5456,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265571</v>
+        <v>127265534</v>
       </c>
       <c r="B45" t="n">
-        <v>98361</v>
+        <v>109267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721594</v>
+        <v>721493</v>
       </c>
       <c r="R45" t="n">
-        <v>6380563</v>
+        <v>6380446</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127265628</v>
+        <v>127265593</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>98466</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,46 +6013,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721173</v>
+        <v>721572</v>
       </c>
       <c r="R50" t="n">
-        <v>6380248</v>
+        <v>6380434</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6113,10 +6104,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127265507</v>
+        <v>127265472</v>
       </c>
       <c r="B51" t="n">
-        <v>98361</v>
+        <v>98466</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,21 +6115,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6157,13 +6148,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721307</v>
+        <v>721232</v>
       </c>
       <c r="R51" t="n">
-        <v>6380360</v>
+        <v>6380313</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6224,10 +6215,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127265593</v>
+        <v>127265628</v>
       </c>
       <c r="B52" t="n">
-        <v>98466</v>
+        <v>98361</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,37 +6226,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721572</v>
+        <v>721173</v>
       </c>
       <c r="R52" t="n">
-        <v>6380434</v>
+        <v>6380248</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127265472</v>
+        <v>127265507</v>
       </c>
       <c r="B53" t="n">
-        <v>98466</v>
+        <v>98361</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6370,13 +6370,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721232</v>
+        <v>721307</v>
       </c>
       <c r="R53" t="n">
-        <v>6380313</v>
+        <v>6380360</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6660,35 +6660,44 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265481</v>
+        <v>127265484</v>
       </c>
       <c r="B56" t="n">
-        <v>109267</v>
+        <v>98361</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
@@ -6762,32 +6771,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265622</v>
+        <v>127265494</v>
       </c>
       <c r="B57" t="n">
-        <v>103896</v>
+        <v>98465</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220164</v>
+        <v>219862</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6802,17 +6811,17 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721252</v>
+        <v>721247</v>
       </c>
       <c r="R57" t="n">
-        <v>6380274</v>
+        <v>6380342</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6873,32 +6882,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265494</v>
+        <v>127265622</v>
       </c>
       <c r="B58" t="n">
-        <v>98465</v>
+        <v>103896</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219862</v>
+        <v>220164</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6913,17 +6922,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721247</v>
+        <v>721252</v>
       </c>
       <c r="R58" t="n">
-        <v>6380342</v>
+        <v>6380274</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6984,27 +6993,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265471</v>
+        <v>127265481</v>
       </c>
       <c r="B59" t="n">
-        <v>106038</v>
+        <v>109267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7019,10 +7028,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721232</v>
+        <v>721220</v>
       </c>
       <c r="R59" t="n">
-        <v>6380313</v>
+        <v>6380355</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7086,54 +7095,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265484</v>
+        <v>127265471</v>
       </c>
       <c r="B60" t="n">
-        <v>98361</v>
+        <v>106038</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R60" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7197,27 +7197,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265505</v>
+        <v>127265533</v>
       </c>
       <c r="B61" t="n">
-        <v>106038</v>
+        <v>99194</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220785</v>
+        <v>222361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7225,20 +7225,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721284</v>
+        <v>721484</v>
       </c>
       <c r="R61" t="n">
-        <v>6380359</v>
+        <v>6380450</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7299,48 +7308,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265488</v>
+        <v>127265474</v>
       </c>
       <c r="B62" t="n">
-        <v>106038</v>
+        <v>98361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721231</v>
+        <v>721232</v>
       </c>
       <c r="R62" t="n">
-        <v>6380342</v>
+        <v>6380313</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7512,7 +7530,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265474</v>
+        <v>127265546</v>
       </c>
       <c r="B64" t="n">
         <v>98361</v>
@@ -7542,7 +7560,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7552,17 +7570,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721232</v>
+        <v>721560</v>
       </c>
       <c r="R64" t="n">
-        <v>6380313</v>
+        <v>6380582</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7605,7 +7623,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7623,10 +7641,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265546</v>
+        <v>127265495</v>
       </c>
       <c r="B65" t="n">
-        <v>98361</v>
+        <v>98421</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7634,26 +7652,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7663,17 +7681,17 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721560</v>
+        <v>721247</v>
       </c>
       <c r="R65" t="n">
-        <v>6380582</v>
+        <v>6380342</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7716,7 +7734,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7734,37 +7752,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265533</v>
+        <v>127265617</v>
       </c>
       <c r="B66" t="n">
-        <v>99194</v>
+        <v>98465</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222361</v>
+        <v>219862</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7772,19 +7790,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721484</v>
+        <v>721357</v>
       </c>
       <c r="R66" t="n">
-        <v>6380450</v>
+        <v>6380338</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7845,7 +7868,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265495</v>
+        <v>127265517</v>
       </c>
       <c r="B67" t="n">
         <v>98421</v>
@@ -7875,7 +7898,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7885,17 +7908,17 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721247</v>
+        <v>721330</v>
       </c>
       <c r="R67" t="n">
-        <v>6380342</v>
+        <v>6380365</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7956,62 +7979,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265617</v>
+        <v>127265505</v>
       </c>
       <c r="B68" t="n">
-        <v>98465</v>
+        <v>106038</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721357</v>
+        <v>721284</v>
       </c>
       <c r="R68" t="n">
-        <v>6380338</v>
+        <v>6380359</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8072,57 +8081,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265517</v>
+        <v>127265488</v>
       </c>
       <c r="B69" t="n">
-        <v>98421</v>
+        <v>106038</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721330</v>
+        <v>721231</v>
       </c>
       <c r="R69" t="n">
-        <v>6380365</v>
+        <v>6380342</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8410,45 +8410,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265526</v>
+        <v>127265528</v>
       </c>
       <c r="B72" t="n">
-        <v>109267</v>
+        <v>98361</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721433</v>
+        <v>721460</v>
       </c>
       <c r="R72" t="n">
-        <v>6380417</v>
+        <v>6380438</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8481,11 +8490,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8517,10 +8521,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265528</v>
+        <v>127265586</v>
       </c>
       <c r="B73" t="n">
-        <v>98361</v>
+        <v>98466</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8528,21 +8532,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8557,14 +8561,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721460</v>
+        <v>721591</v>
       </c>
       <c r="R73" t="n">
-        <v>6380438</v>
+        <v>6380497</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8628,54 +8632,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127265586</v>
+        <v>127265526</v>
       </c>
       <c r="B74" t="n">
-        <v>98466</v>
+        <v>109267</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>721591</v>
+        <v>721433</v>
       </c>
       <c r="R74" t="n">
-        <v>6380497</v>
+        <v>6380417</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8708,6 +8703,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8739,45 +8739,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B75" t="n">
-        <v>109267</v>
+        <v>98466</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R75" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8841,54 +8850,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B76" t="n">
-        <v>98466</v>
+        <v>109267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R76" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8952,48 +8952,57 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127265513</v>
+        <v>127265508</v>
       </c>
       <c r="B77" t="n">
-        <v>109267</v>
+        <v>98421</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721315</v>
+        <v>721307</v>
       </c>
       <c r="R77" t="n">
-        <v>6380362</v>
+        <v>6380360</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9054,57 +9063,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127265508</v>
+        <v>127265513</v>
       </c>
       <c r="B78" t="n">
-        <v>98421</v>
+        <v>109267</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721307</v>
+        <v>721315</v>
       </c>
       <c r="R78" t="n">
-        <v>6380360</v>
+        <v>6380362</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9291,48 +9291,57 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265491</v>
+        <v>127265489</v>
       </c>
       <c r="B80" t="n">
-        <v>106038</v>
+        <v>98361</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721239</v>
+        <v>721231</v>
       </c>
       <c r="R80" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9597,57 +9606,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127265489</v>
+        <v>127265491</v>
       </c>
       <c r="B83" t="n">
-        <v>98361</v>
+        <v>106038</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721231</v>
+        <v>721239</v>
       </c>
       <c r="R83" t="n">
-        <v>6380342</v>
+        <v>6380330</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9708,48 +9708,57 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265511</v>
+        <v>127265499</v>
       </c>
       <c r="B84" t="n">
-        <v>106038</v>
+        <v>98361</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721315</v>
+        <v>721247</v>
       </c>
       <c r="R84" t="n">
-        <v>6380362</v>
+        <v>6380342</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9912,57 +9921,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265499</v>
+        <v>127265511</v>
       </c>
       <c r="B86" t="n">
-        <v>98361</v>
+        <v>106038</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721247</v>
+        <v>721315</v>
       </c>
       <c r="R86" t="n">
-        <v>6380342</v>
+        <v>6380362</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127265500</v>
+        <v>127265519</v>
       </c>
       <c r="B88" t="n">
         <v>98361</v>
@@ -10162,29 +10162,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>721263</v>
+        <v>721330</v>
       </c>
       <c r="R88" t="n">
-        <v>6380356</v>
+        <v>6380365</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10245,7 +10236,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265519</v>
+        <v>127265500</v>
       </c>
       <c r="B89" t="n">
         <v>98361</v>
@@ -10273,20 +10264,29 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721330</v>
+        <v>721263</v>
       </c>
       <c r="R89" t="n">
-        <v>6380365</v>
+        <v>6380356</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -3071,48 +3071,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265496</v>
+        <v>127265610</v>
       </c>
       <c r="B23" t="n">
-        <v>109267</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R23" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3173,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127265610</v>
+        <v>127265590</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>98479</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,21 +3193,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3217,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721466</v>
+        <v>721580</v>
       </c>
       <c r="R24" t="n">
-        <v>6380394</v>
+        <v>6380472</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,6 +3264,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3266,7 +3280,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3284,57 +3298,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265590</v>
+        <v>127265496</v>
       </c>
       <c r="B25" t="n">
-        <v>98479</v>
+        <v>109267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721580</v>
+        <v>721247</v>
       </c>
       <c r="R25" t="n">
-        <v>6380472</v>
+        <v>6380342</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3366,11 +3371,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3400,48 +3400,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265503</v>
+        <v>127265624</v>
       </c>
       <c r="B26" t="n">
-        <v>106038</v>
+        <v>98361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721272</v>
+        <v>721199</v>
       </c>
       <c r="R26" t="n">
-        <v>6380356</v>
+        <v>6380248</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3502,10 +3511,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265624</v>
+        <v>127265473</v>
       </c>
       <c r="B27" t="n">
-        <v>98361</v>
+        <v>98421</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3513,26 +3522,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3542,17 +3551,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721199</v>
+        <v>721232</v>
       </c>
       <c r="R27" t="n">
-        <v>6380248</v>
+        <v>6380313</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3613,10 +3622,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265473</v>
+        <v>127265475</v>
       </c>
       <c r="B28" t="n">
-        <v>98421</v>
+        <v>98466</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,26 +3633,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3657,13 +3666,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721232</v>
+        <v>721209</v>
       </c>
       <c r="R28" t="n">
-        <v>6380313</v>
+        <v>6380333</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3724,57 +3733,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265475</v>
+        <v>127265503</v>
       </c>
       <c r="B29" t="n">
-        <v>98466</v>
+        <v>106038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721209</v>
+        <v>721272</v>
       </c>
       <c r="R29" t="n">
-        <v>6380333</v>
+        <v>6380356</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127265584</v>
+        <v>127296661</v>
       </c>
       <c r="B34" t="n">
-        <v>98466</v>
+        <v>58334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,46 +4286,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721601</v>
+        <v>721560</v>
       </c>
       <c r="R34" t="n">
-        <v>6380518</v>
+        <v>6380582</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4386,10 +4386,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127296661</v>
+        <v>127265584</v>
       </c>
       <c r="B35" t="n">
-        <v>58334</v>
+        <v>98466</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,46 +4397,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103044</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721560</v>
+        <v>721601</v>
       </c>
       <c r="R35" t="n">
-        <v>6380582</v>
+        <v>6380518</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265571</v>
+        <v>127265515</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>98421</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5356,26 +5356,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5385,17 +5385,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721594</v>
+        <v>721315</v>
       </c>
       <c r="R44" t="n">
-        <v>6380563</v>
+        <v>6380362</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5456,45 +5456,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265534</v>
+        <v>127265571</v>
       </c>
       <c r="B45" t="n">
-        <v>109267</v>
+        <v>98361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721493</v>
+        <v>721594</v>
       </c>
       <c r="R45" t="n">
-        <v>6380446</v>
+        <v>6380563</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5558,57 +5567,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265515</v>
+        <v>127265534</v>
       </c>
       <c r="B46" t="n">
-        <v>98421</v>
+        <v>109267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721315</v>
+        <v>721493</v>
       </c>
       <c r="R46" t="n">
-        <v>6380362</v>
+        <v>6380446</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127265593</v>
+        <v>127265628</v>
       </c>
       <c r="B50" t="n">
-        <v>98466</v>
+        <v>98361</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,37 +6013,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721572</v>
+        <v>721173</v>
       </c>
       <c r="R50" t="n">
-        <v>6380434</v>
+        <v>6380248</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6104,10 +6113,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127265472</v>
+        <v>127265507</v>
       </c>
       <c r="B51" t="n">
-        <v>98466</v>
+        <v>98361</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,21 +6124,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6148,13 +6157,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721232</v>
+        <v>721307</v>
       </c>
       <c r="R51" t="n">
-        <v>6380313</v>
+        <v>6380360</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6215,10 +6224,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127265628</v>
+        <v>127265593</v>
       </c>
       <c r="B52" t="n">
-        <v>98361</v>
+        <v>98466</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6226,46 +6235,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721173</v>
+        <v>721572</v>
       </c>
       <c r="R52" t="n">
-        <v>6380248</v>
+        <v>6380434</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127265507</v>
+        <v>127265472</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>98466</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6370,13 +6370,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721307</v>
+        <v>721232</v>
       </c>
       <c r="R53" t="n">
-        <v>6380360</v>
+        <v>6380313</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7197,37 +7197,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265533</v>
+        <v>127265474</v>
       </c>
       <c r="B61" t="n">
-        <v>99194</v>
+        <v>98361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222361</v>
+        <v>223591</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721484</v>
+        <v>721232</v>
       </c>
       <c r="R61" t="n">
-        <v>6380450</v>
+        <v>6380313</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265474</v>
+        <v>127265504</v>
       </c>
       <c r="B62" t="n">
         <v>98361</v>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721232</v>
+        <v>721272</v>
       </c>
       <c r="R62" t="n">
-        <v>6380313</v>
+        <v>6380356</v>
       </c>
       <c r="S62" t="n">
         <v>7</v>
@@ -7419,7 +7419,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265504</v>
+        <v>127265546</v>
       </c>
       <c r="B63" t="n">
         <v>98361</v>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7459,17 +7459,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721272</v>
+        <v>721560</v>
       </c>
       <c r="R63" t="n">
-        <v>6380356</v>
+        <v>6380582</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265546</v>
+        <v>127265495</v>
       </c>
       <c r="B64" t="n">
-        <v>98361</v>
+        <v>98421</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7541,26 +7541,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7570,17 +7570,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721560</v>
+        <v>721247</v>
       </c>
       <c r="R64" t="n">
-        <v>6380582</v>
+        <v>6380342</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265495</v>
+        <v>127265617</v>
       </c>
       <c r="B65" t="n">
-        <v>98421</v>
+        <v>98465</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7652,26 +7652,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7679,19 +7679,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721247</v>
+        <v>721357</v>
       </c>
       <c r="R65" t="n">
-        <v>6380342</v>
+        <v>6380338</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7752,10 +7757,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265617</v>
+        <v>127265517</v>
       </c>
       <c r="B66" t="n">
-        <v>98465</v>
+        <v>98421</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7763,26 +7768,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7790,24 +7795,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721357</v>
+        <v>721330</v>
       </c>
       <c r="R66" t="n">
-        <v>6380338</v>
+        <v>6380365</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7868,57 +7868,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265517</v>
+        <v>127265505</v>
       </c>
       <c r="B67" t="n">
-        <v>98421</v>
+        <v>106038</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721330</v>
+        <v>721284</v>
       </c>
       <c r="R67" t="n">
-        <v>6380365</v>
+        <v>6380359</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7979,7 +7970,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265505</v>
+        <v>127265488</v>
       </c>
       <c r="B68" t="n">
         <v>106038</v>
@@ -8014,13 +8005,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721284</v>
+        <v>721231</v>
       </c>
       <c r="R68" t="n">
-        <v>6380359</v>
+        <v>6380342</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8081,27 +8072,27 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265488</v>
+        <v>127265533</v>
       </c>
       <c r="B69" t="n">
-        <v>106038</v>
+        <v>99194</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220785</v>
+        <v>222361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8109,20 +8100,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721231</v>
+        <v>721484</v>
       </c>
       <c r="R69" t="n">
-        <v>6380342</v>
+        <v>6380450</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -3400,57 +3400,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265624</v>
+        <v>127265503</v>
       </c>
       <c r="B26" t="n">
-        <v>98361</v>
+        <v>106038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721199</v>
+        <v>721272</v>
       </c>
       <c r="R26" t="n">
-        <v>6380248</v>
+        <v>6380356</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,10 +3502,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265473</v>
+        <v>127265624</v>
       </c>
       <c r="B27" t="n">
-        <v>98421</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,26 +3513,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3551,17 +3542,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721232</v>
+        <v>721199</v>
       </c>
       <c r="R27" t="n">
-        <v>6380313</v>
+        <v>6380248</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3622,10 +3613,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265475</v>
+        <v>127265473</v>
       </c>
       <c r="B28" t="n">
-        <v>98466</v>
+        <v>98421</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,26 +3624,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3666,13 +3657,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721209</v>
+        <v>721232</v>
       </c>
       <c r="R28" t="n">
-        <v>6380333</v>
+        <v>6380313</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3733,48 +3724,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265503</v>
+        <v>127265475</v>
       </c>
       <c r="B29" t="n">
-        <v>106038</v>
+        <v>98466</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721272</v>
+        <v>721209</v>
       </c>
       <c r="R29" t="n">
-        <v>6380356</v>
+        <v>6380333</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265548</v>
+        <v>127265598</v>
       </c>
       <c r="B30" t="n">
-        <v>99660</v>
+        <v>98466</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3846,31 +3846,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>174</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3879,13 +3879,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721578</v>
+        <v>721557</v>
       </c>
       <c r="R30" t="n">
-        <v>6380576</v>
+        <v>6380422</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,11 +3917,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3933,7 +3928,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3951,7 +3946,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265598</v>
+        <v>127265606</v>
       </c>
       <c r="B31" t="n">
         <v>98466</v>
@@ -3981,7 +3976,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3995,10 +3990,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721557</v>
+        <v>721475</v>
       </c>
       <c r="R31" t="n">
-        <v>6380422</v>
+        <v>6380396</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,7 +4039,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4062,57 +4057,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265606</v>
+        <v>127265486</v>
       </c>
       <c r="B32" t="n">
-        <v>98466</v>
+        <v>109267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721475</v>
+        <v>721231</v>
       </c>
       <c r="R32" t="n">
-        <v>6380396</v>
+        <v>6380342</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4173,45 +4159,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265486</v>
+        <v>127265548</v>
       </c>
       <c r="B33" t="n">
-        <v>109267</v>
+        <v>99660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>174</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721231</v>
+        <v>721578</v>
       </c>
       <c r="R33" t="n">
-        <v>6380342</v>
+        <v>6380576</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4246,6 +4241,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5030,57 +5030,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127265623</v>
+        <v>127265579</v>
       </c>
       <c r="B41" t="n">
-        <v>98421</v>
+        <v>106038</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721199</v>
+        <v>721577</v>
       </c>
       <c r="R41" t="n">
-        <v>6380248</v>
+        <v>6380550</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5141,7 +5132,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265579</v>
+        <v>127265545</v>
       </c>
       <c r="B42" t="n">
         <v>106038</v>
@@ -5172,14 +5163,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721577</v>
+        <v>721560</v>
       </c>
       <c r="R42" t="n">
-        <v>6380550</v>
+        <v>6380582</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5225,7 +5216,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5243,48 +5234,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127265545</v>
+        <v>127265623</v>
       </c>
       <c r="B43" t="n">
-        <v>106038</v>
+        <v>98421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721560</v>
+        <v>721199</v>
       </c>
       <c r="R43" t="n">
-        <v>6380582</v>
+        <v>6380248</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265515</v>
+        <v>127265571</v>
       </c>
       <c r="B44" t="n">
-        <v>98421</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5356,26 +5356,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5385,17 +5385,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R44" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5456,54 +5456,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265571</v>
+        <v>127265534</v>
       </c>
       <c r="B45" t="n">
-        <v>98361</v>
+        <v>109267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721594</v>
+        <v>721493</v>
       </c>
       <c r="R45" t="n">
-        <v>6380563</v>
+        <v>6380446</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5567,48 +5558,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265534</v>
+        <v>127265515</v>
       </c>
       <c r="B46" t="n">
-        <v>109267</v>
+        <v>98421</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721493</v>
+        <v>721315</v>
       </c>
       <c r="R46" t="n">
-        <v>6380446</v>
+        <v>6380362</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6437,64 +6437,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B54" t="n">
-        <v>43228</v>
+        <v>106038</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R54" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,45 +6539,64 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B55" t="n">
-        <v>106038</v>
+        <v>43228</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R55" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -10134,48 +10134,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127265519</v>
+        <v>127265483</v>
       </c>
       <c r="B88" t="n">
-        <v>98361</v>
+        <v>106038</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>721330</v>
+        <v>721220</v>
       </c>
       <c r="R88" t="n">
-        <v>6380365</v>
+        <v>6380355</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265500</v>
+        <v>127265519</v>
       </c>
       <c r="B89" t="n">
         <v>98361</v>
@@ -10264,29 +10264,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721263</v>
+        <v>721330</v>
       </c>
       <c r="R89" t="n">
-        <v>6380356</v>
+        <v>6380365</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10347,7 +10338,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265506</v>
+        <v>127265500</v>
       </c>
       <c r="B90" t="n">
         <v>98361</v>
@@ -10377,7 +10368,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10391,10 +10382,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721284</v>
+        <v>721263</v>
       </c>
       <c r="R90" t="n">
-        <v>6380359</v>
+        <v>6380356</v>
       </c>
       <c r="S90" t="n">
         <v>7</v>
@@ -10458,45 +10449,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127265483</v>
+        <v>127265506</v>
       </c>
       <c r="B91" t="n">
-        <v>106038</v>
+        <v>98361</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>721220</v>
+        <v>721284</v>
       </c>
       <c r="R91" t="n">
-        <v>6380355</v>
+        <v>6380359</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265479</v>
+        <v>127265492</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,26 +2110,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721212</v>
+        <v>721239</v>
       </c>
       <c r="R14" t="n">
-        <v>6380346</v>
+        <v>6380330</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,54 +2210,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265530</v>
+        <v>127265600</v>
       </c>
       <c r="B15" t="n">
-        <v>98479</v>
+        <v>109273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721463</v>
+        <v>721547</v>
       </c>
       <c r="R15" t="n">
-        <v>6380440</v>
+        <v>6380409</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265497</v>
+        <v>127265518</v>
       </c>
       <c r="B16" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2342,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2361,17 +2352,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721247</v>
+        <v>721330</v>
       </c>
       <c r="R16" t="n">
-        <v>6380342</v>
+        <v>6380365</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2432,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265518</v>
+        <v>127265497</v>
       </c>
       <c r="B17" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,7 +2453,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2472,17 +2463,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721330</v>
+        <v>721247</v>
       </c>
       <c r="R17" t="n">
-        <v>6380365</v>
+        <v>6380342</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2543,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265492</v>
+        <v>127265479</v>
       </c>
       <c r="B18" t="n">
-        <v>98466</v>
+        <v>98365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,26 +2545,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2587,13 +2578,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721239</v>
+        <v>721212</v>
       </c>
       <c r="R18" t="n">
-        <v>6380330</v>
+        <v>6380346</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2654,45 +2645,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265532</v>
+        <v>127265530</v>
       </c>
       <c r="B19" t="n">
-        <v>106038</v>
+        <v>98483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>223621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721484</v>
+        <v>721463</v>
       </c>
       <c r="R19" t="n">
-        <v>6380450</v>
+        <v>6380440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,54 +2756,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265587</v>
+        <v>127265532</v>
       </c>
       <c r="B20" t="n">
-        <v>105478</v>
+        <v>106044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721591</v>
+        <v>721484</v>
       </c>
       <c r="R20" t="n">
-        <v>6380497</v>
+        <v>6380450</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2867,45 +2858,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265540</v>
+        <v>127265587</v>
       </c>
       <c r="B21" t="n">
-        <v>106038</v>
+        <v>105484</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220785</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721546</v>
+        <v>721591</v>
       </c>
       <c r="R21" t="n">
-        <v>6380552</v>
+        <v>6380497</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2969,27 +2969,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265600</v>
+        <v>127265540</v>
       </c>
       <c r="B22" t="n">
-        <v>109267</v>
+        <v>106044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3000,14 +3000,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721547</v>
+        <v>721546</v>
       </c>
       <c r="R22" t="n">
-        <v>6380409</v>
+        <v>6380552</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3071,57 +3071,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265610</v>
+        <v>127265496</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>109273</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721466</v>
+        <v>721247</v>
       </c>
       <c r="R23" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3182,10 +3173,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127265590</v>
+        <v>127265610</v>
       </c>
       <c r="B24" t="n">
-        <v>98479</v>
+        <v>98365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,21 +3184,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223621</v>
+        <v>223591</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3226,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721580</v>
+        <v>721466</v>
       </c>
       <c r="R24" t="n">
-        <v>6380472</v>
+        <v>6380394</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3264,11 +3255,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3280,7 +3266,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3298,48 +3284,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265496</v>
+        <v>127265590</v>
       </c>
       <c r="B25" t="n">
-        <v>109267</v>
+        <v>98483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721247</v>
+        <v>721580</v>
       </c>
       <c r="R25" t="n">
-        <v>6380342</v>
+        <v>6380472</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3371,6 +3366,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3403,7 +3403,7 @@
         <v>127265503</v>
       </c>
       <c r="B26" t="n">
-        <v>106038</v>
+        <v>106044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265624</v>
+        <v>127265475</v>
       </c>
       <c r="B27" t="n">
-        <v>98361</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3542,14 +3542,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721199</v>
+        <v>721209</v>
       </c>
       <c r="R27" t="n">
-        <v>6380248</v>
+        <v>6380333</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3616,7 +3616,7 @@
         <v>127265473</v>
       </c>
       <c r="B28" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265475</v>
+        <v>127265624</v>
       </c>
       <c r="B29" t="n">
-        <v>98466</v>
+        <v>98365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3735,21 +3735,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721209</v>
+        <v>721199</v>
       </c>
       <c r="R29" t="n">
-        <v>6380333</v>
+        <v>6380248</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265598</v>
+        <v>127265548</v>
       </c>
       <c r="B30" t="n">
-        <v>98466</v>
+        <v>99664</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3846,31 +3846,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>174</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3879,13 +3879,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721557</v>
+        <v>721578</v>
       </c>
       <c r="R30" t="n">
-        <v>6380422</v>
+        <v>6380576</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,6 +3917,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3928,7 +3933,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3946,10 +3951,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265606</v>
+        <v>127265598</v>
       </c>
       <c r="B31" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3976,7 +3981,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3990,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721475</v>
+        <v>721557</v>
       </c>
       <c r="R31" t="n">
-        <v>6380396</v>
+        <v>6380422</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4039,7 +4044,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4057,48 +4062,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265486</v>
+        <v>127265606</v>
       </c>
       <c r="B32" t="n">
-        <v>109267</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721231</v>
+        <v>721475</v>
       </c>
       <c r="R32" t="n">
-        <v>6380342</v>
+        <v>6380396</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4159,54 +4173,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265548</v>
+        <v>127265486</v>
       </c>
       <c r="B33" t="n">
-        <v>99660</v>
+        <v>109273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>174</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721578</v>
+        <v>721231</v>
       </c>
       <c r="R33" t="n">
-        <v>6380576</v>
+        <v>6380342</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4241,11 +4246,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4275,57 +4275,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127296661</v>
+        <v>127265594</v>
       </c>
       <c r="B34" t="n">
-        <v>58334</v>
+        <v>109273</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721560</v>
+        <v>721572</v>
       </c>
       <c r="R34" t="n">
-        <v>6380582</v>
+        <v>6380434</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4357,6 +4348,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4368,7 +4364,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4389,7 +4385,7 @@
         <v>127265584</v>
       </c>
       <c r="B35" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4497,48 +4493,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265594</v>
+        <v>127296661</v>
       </c>
       <c r="B36" t="n">
-        <v>109267</v>
+        <v>58338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721572</v>
+        <v>721560</v>
       </c>
       <c r="R36" t="n">
-        <v>6380434</v>
+        <v>6380582</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,11 +4575,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4607,7 +4607,7 @@
         <v>127265612</v>
       </c>
       <c r="B37" t="n">
-        <v>98480</v>
+        <v>98484</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>127265541</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>98365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>127265566</v>
       </c>
       <c r="B39" t="n">
-        <v>98361</v>
+        <v>98365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>127265582</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>98365</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>127265579</v>
       </c>
       <c r="B41" t="n">
-        <v>106038</v>
+        <v>106044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>127265545</v>
       </c>
       <c r="B42" t="n">
-        <v>106038</v>
+        <v>106044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>127265623</v>
       </c>
       <c r="B43" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,54 +5345,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265571</v>
+        <v>127265534</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>109273</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721594</v>
+        <v>721493</v>
       </c>
       <c r="R44" t="n">
-        <v>6380563</v>
+        <v>6380446</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5456,48 +5447,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265534</v>
+        <v>127265515</v>
       </c>
       <c r="B45" t="n">
-        <v>109267</v>
+        <v>98425</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721493</v>
+        <v>721315</v>
       </c>
       <c r="R45" t="n">
-        <v>6380446</v>
+        <v>6380362</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265515</v>
+        <v>127265571</v>
       </c>
       <c r="B46" t="n">
-        <v>98421</v>
+        <v>98365</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5569,26 +5569,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5598,17 +5598,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R46" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>127265626</v>
       </c>
       <c r="B47" t="n">
-        <v>98361</v>
+        <v>98365</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>127265597</v>
       </c>
       <c r="B48" t="n">
-        <v>98361</v>
+        <v>98365</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>127265478</v>
       </c>
       <c r="B49" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127265628</v>
+        <v>127265593</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,46 +6013,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721173</v>
+        <v>721572</v>
       </c>
       <c r="R50" t="n">
-        <v>6380248</v>
+        <v>6380434</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6113,10 +6104,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127265507</v>
+        <v>127265472</v>
       </c>
       <c r="B51" t="n">
-        <v>98361</v>
+        <v>98470</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,21 +6115,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6157,13 +6148,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721307</v>
+        <v>721232</v>
       </c>
       <c r="R51" t="n">
-        <v>6380360</v>
+        <v>6380313</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6224,10 +6215,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127265593</v>
+        <v>127265628</v>
       </c>
       <c r="B52" t="n">
-        <v>98466</v>
+        <v>98365</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,37 +6226,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721572</v>
+        <v>721173</v>
       </c>
       <c r="R52" t="n">
-        <v>6380434</v>
+        <v>6380248</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127265472</v>
+        <v>127265507</v>
       </c>
       <c r="B53" t="n">
-        <v>98466</v>
+        <v>98365</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6370,13 +6370,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721232</v>
+        <v>721307</v>
       </c>
       <c r="R53" t="n">
-        <v>6380313</v>
+        <v>6380360</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6437,45 +6437,64 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B54" t="n">
-        <v>106038</v>
+        <v>43232</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R54" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6539,64 +6558,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B55" t="n">
-        <v>43228</v>
+        <v>106044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R55" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6660,54 +6660,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265484</v>
+        <v>127265471</v>
       </c>
       <c r="B56" t="n">
-        <v>98361</v>
+        <v>106044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R56" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -6771,54 +6762,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265494</v>
+        <v>127265481</v>
       </c>
       <c r="B57" t="n">
-        <v>98465</v>
+        <v>109273</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721247</v>
+        <v>721220</v>
       </c>
       <c r="R57" t="n">
-        <v>6380342</v>
+        <v>6380355</v>
       </c>
       <c r="S57" t="n">
         <v>7</v>
@@ -6885,7 +6867,7 @@
         <v>127265622</v>
       </c>
       <c r="B58" t="n">
-        <v>103896</v>
+        <v>103902</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6993,45 +6975,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265481</v>
+        <v>127265494</v>
       </c>
       <c r="B59" t="n">
-        <v>109267</v>
+        <v>98469</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721220</v>
+        <v>721247</v>
       </c>
       <c r="R59" t="n">
-        <v>6380355</v>
+        <v>6380342</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7095,45 +7086,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265471</v>
+        <v>127265484</v>
       </c>
       <c r="B60" t="n">
-        <v>106038</v>
+        <v>98365</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721232</v>
+        <v>721220</v>
       </c>
       <c r="R60" t="n">
-        <v>6380313</v>
+        <v>6380355</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7197,54 +7197,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265474</v>
+        <v>127265505</v>
       </c>
       <c r="B61" t="n">
-        <v>98361</v>
+        <v>106044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721232</v>
+        <v>721284</v>
       </c>
       <c r="R61" t="n">
-        <v>6380313</v>
+        <v>6380359</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7308,57 +7299,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265504</v>
+        <v>127265488</v>
       </c>
       <c r="B62" t="n">
-        <v>98361</v>
+        <v>106044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721272</v>
+        <v>721231</v>
       </c>
       <c r="R62" t="n">
-        <v>6380356</v>
+        <v>6380342</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7419,37 +7401,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265546</v>
+        <v>127265533</v>
       </c>
       <c r="B63" t="n">
-        <v>98361</v>
+        <v>99198</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7463,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721560</v>
+        <v>721484</v>
       </c>
       <c r="R63" t="n">
-        <v>6380582</v>
+        <v>6380450</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7512,7 +7494,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7530,10 +7512,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265495</v>
+        <v>127265474</v>
       </c>
       <c r="B64" t="n">
-        <v>98421</v>
+        <v>98365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7541,26 +7523,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7574,10 +7556,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721247</v>
+        <v>721232</v>
       </c>
       <c r="R64" t="n">
-        <v>6380342</v>
+        <v>6380313</v>
       </c>
       <c r="S64" t="n">
         <v>7</v>
@@ -7641,10 +7623,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265617</v>
+        <v>127265504</v>
       </c>
       <c r="B65" t="n">
-        <v>98465</v>
+        <v>98365</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7652,26 +7634,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7679,24 +7661,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721357</v>
+        <v>721272</v>
       </c>
       <c r="R65" t="n">
-        <v>6380338</v>
+        <v>6380356</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7757,10 +7734,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265517</v>
+        <v>127265546</v>
       </c>
       <c r="B66" t="n">
-        <v>98421</v>
+        <v>98365</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7768,26 +7745,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7801,10 +7778,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721330</v>
+        <v>721560</v>
       </c>
       <c r="R66" t="n">
-        <v>6380365</v>
+        <v>6380582</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7850,7 +7827,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7868,45 +7845,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265505</v>
+        <v>127265495</v>
       </c>
       <c r="B67" t="n">
-        <v>106038</v>
+        <v>98425</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721284</v>
+        <v>721247</v>
       </c>
       <c r="R67" t="n">
-        <v>6380359</v>
+        <v>6380342</v>
       </c>
       <c r="S67" t="n">
         <v>7</v>
@@ -7970,48 +7956,62 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265488</v>
+        <v>127265617</v>
       </c>
       <c r="B68" t="n">
-        <v>106038</v>
+        <v>98469</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721231</v>
+        <v>721357</v>
       </c>
       <c r="R68" t="n">
-        <v>6380342</v>
+        <v>6380338</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8072,37 +8072,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265533</v>
+        <v>127265517</v>
       </c>
       <c r="B69" t="n">
-        <v>99194</v>
+        <v>98425</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721484</v>
+        <v>721330</v>
       </c>
       <c r="R69" t="n">
-        <v>6380450</v>
+        <v>6380365</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8183,10 +8183,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127265476</v>
+        <v>127265525</v>
       </c>
       <c r="B70" t="n">
-        <v>98361</v>
+        <v>98425</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,26 +8194,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8223,17 +8223,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>721209</v>
+        <v>721433</v>
       </c>
       <c r="R70" t="n">
-        <v>6380333</v>
+        <v>6380417</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8263,11 +8263,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8299,10 +8294,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127265525</v>
+        <v>127265476</v>
       </c>
       <c r="B71" t="n">
-        <v>98421</v>
+        <v>98365</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8310,26 +8305,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8339,17 +8334,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>721433</v>
+        <v>721209</v>
       </c>
       <c r="R71" t="n">
-        <v>6380417</v>
+        <v>6380333</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8379,6 +8374,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265528</v>
+        <v>127265586</v>
       </c>
       <c r="B72" t="n">
-        <v>98361</v>
+        <v>98470</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721460</v>
+        <v>721591</v>
       </c>
       <c r="R72" t="n">
-        <v>6380438</v>
+        <v>6380497</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8521,54 +8521,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265586</v>
+        <v>127265526</v>
       </c>
       <c r="B73" t="n">
-        <v>98466</v>
+        <v>109273</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721591</v>
+        <v>721433</v>
       </c>
       <c r="R73" t="n">
-        <v>6380497</v>
+        <v>6380417</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8601,6 +8592,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8632,45 +8628,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127265526</v>
+        <v>127265528</v>
       </c>
       <c r="B74" t="n">
-        <v>109267</v>
+        <v>98365</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>721433</v>
+        <v>721460</v>
       </c>
       <c r="R74" t="n">
-        <v>6380417</v>
+        <v>6380438</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8703,11 +8708,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8742,7 +8742,7 @@
         <v>127265535</v>
       </c>
       <c r="B75" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>127265588</v>
       </c>
       <c r="B76" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>127265508</v>
       </c>
       <c r="B77" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>127265513</v>
       </c>
       <c r="B78" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>127296632</v>
       </c>
       <c r="B79" t="n">
-        <v>43228</v>
+        <v>43232</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9291,57 +9291,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265489</v>
+        <v>127265493</v>
       </c>
       <c r="B80" t="n">
-        <v>98361</v>
+        <v>106044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721231</v>
+        <v>721247</v>
       </c>
       <c r="R80" t="n">
         <v>6380342</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9402,10 +9393,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265493</v>
+        <v>127265491</v>
       </c>
       <c r="B81" t="n">
-        <v>106038</v>
+        <v>106044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9437,10 +9428,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721247</v>
+        <v>721239</v>
       </c>
       <c r="R81" t="n">
-        <v>6380342</v>
+        <v>6380330</v>
       </c>
       <c r="S81" t="n">
         <v>7</v>
@@ -9507,7 +9498,7 @@
         <v>127265605</v>
       </c>
       <c r="B82" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,48 +9597,57 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127265491</v>
+        <v>127265489</v>
       </c>
       <c r="B83" t="n">
-        <v>106038</v>
+        <v>98365</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721239</v>
+        <v>721231</v>
       </c>
       <c r="R83" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9708,57 +9708,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265499</v>
+        <v>127265549</v>
       </c>
       <c r="B84" t="n">
-        <v>98361</v>
+        <v>106044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721247</v>
+        <v>721590</v>
       </c>
       <c r="R84" t="n">
-        <v>6380342</v>
+        <v>6380571</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9801,7 +9792,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9819,10 +9810,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265549</v>
+        <v>127265511</v>
       </c>
       <c r="B85" t="n">
-        <v>106038</v>
+        <v>106044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9850,17 +9841,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721590</v>
+        <v>721315</v>
       </c>
       <c r="R85" t="n">
-        <v>6380571</v>
+        <v>6380362</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9903,7 +9894,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9921,48 +9912,57 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265511</v>
+        <v>127265572</v>
       </c>
       <c r="B86" t="n">
-        <v>106038</v>
+        <v>98425</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R86" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10023,10 +10023,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127265572</v>
+        <v>127265499</v>
       </c>
       <c r="B87" t="n">
-        <v>98421</v>
+        <v>98365</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10034,26 +10034,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10063,17 +10063,17 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>721594</v>
+        <v>721247</v>
       </c>
       <c r="R87" t="n">
-        <v>6380563</v>
+        <v>6380342</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>127265483</v>
       </c>
       <c r="B88" t="n">
-        <v>106038</v>
+        <v>106044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>127265519</v>
       </c>
       <c r="B89" t="n">
-        <v>98361</v>
+        <v>98365</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>127265500</v>
       </c>
       <c r="B90" t="n">
-        <v>98361</v>
+        <v>98365</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>127265506</v>
       </c>
       <c r="B91" t="n">
-        <v>98361</v>
+        <v>98365</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,7 +2099,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265492</v>
+        <v>127265497</v>
       </c>
       <c r="B14" t="n">
         <v>98470</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R14" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S14" t="n">
         <v>7</v>
@@ -2210,45 +2210,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265600</v>
+        <v>127265518</v>
       </c>
       <c r="B15" t="n">
-        <v>109273</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721547</v>
+        <v>721330</v>
       </c>
       <c r="R15" t="n">
-        <v>6380409</v>
+        <v>6380365</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,7 +2321,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265518</v>
+        <v>127265492</v>
       </c>
       <c r="B16" t="n">
         <v>98470</v>
@@ -2352,17 +2361,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721330</v>
+        <v>721239</v>
       </c>
       <c r="R16" t="n">
-        <v>6380365</v>
+        <v>6380330</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2423,10 +2432,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265497</v>
+        <v>127265587</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>105484</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,26 +2443,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2463,17 +2472,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721247</v>
+        <v>721591</v>
       </c>
       <c r="R17" t="n">
-        <v>6380342</v>
+        <v>6380497</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2534,57 +2543,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265479</v>
+        <v>127265532</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>106044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721212</v>
+        <v>721484</v>
       </c>
       <c r="R18" t="n">
-        <v>6380346</v>
+        <v>6380450</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2645,54 +2645,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265530</v>
+        <v>127265540</v>
       </c>
       <c r="B19" t="n">
-        <v>98483</v>
+        <v>106044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223621</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721463</v>
+        <v>721546</v>
       </c>
       <c r="R19" t="n">
-        <v>6380440</v>
+        <v>6380552</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,7 +2729,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2756,27 +2747,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265532</v>
+        <v>127265600</v>
       </c>
       <c r="B20" t="n">
-        <v>106044</v>
+        <v>109273</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2787,14 +2778,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721484</v>
+        <v>721547</v>
       </c>
       <c r="R20" t="n">
-        <v>6380450</v>
+        <v>6380409</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2858,10 +2849,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265587</v>
+        <v>127265479</v>
       </c>
       <c r="B21" t="n">
-        <v>105484</v>
+        <v>98365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,26 +2860,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>223591</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2898,17 +2889,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721591</v>
+        <v>721212</v>
       </c>
       <c r="R21" t="n">
-        <v>6380497</v>
+        <v>6380346</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2969,45 +2960,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265540</v>
+        <v>127265530</v>
       </c>
       <c r="B22" t="n">
-        <v>106044</v>
+        <v>98483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>223621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721546</v>
+        <v>721463</v>
       </c>
       <c r="R22" t="n">
-        <v>6380552</v>
+        <v>6380440</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3071,48 +3071,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265496</v>
+        <v>127265610</v>
       </c>
       <c r="B23" t="n">
-        <v>109273</v>
+        <v>98365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R23" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3173,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127265610</v>
+        <v>127265590</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>98483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,21 +3193,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3217,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721466</v>
+        <v>721580</v>
       </c>
       <c r="R24" t="n">
-        <v>6380394</v>
+        <v>6380472</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,6 +3264,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3266,7 +3280,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3284,57 +3298,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265590</v>
+        <v>127265496</v>
       </c>
       <c r="B25" t="n">
-        <v>98483</v>
+        <v>109273</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721580</v>
+        <v>721247</v>
       </c>
       <c r="R25" t="n">
-        <v>6380472</v>
+        <v>6380342</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3366,11 +3371,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3400,45 +3400,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265503</v>
+        <v>127265473</v>
       </c>
       <c r="B26" t="n">
-        <v>106044</v>
+        <v>98425</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721272</v>
+        <v>721232</v>
       </c>
       <c r="R26" t="n">
-        <v>6380356</v>
+        <v>6380313</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3613,10 +3622,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265473</v>
+        <v>127265624</v>
       </c>
       <c r="B28" t="n">
-        <v>98425</v>
+        <v>98365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,26 +3633,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3653,17 +3662,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721232</v>
+        <v>721199</v>
       </c>
       <c r="R28" t="n">
-        <v>6380313</v>
+        <v>6380248</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3724,57 +3733,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265624</v>
+        <v>127265503</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>106044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721199</v>
+        <v>721272</v>
       </c>
       <c r="R29" t="n">
-        <v>6380248</v>
+        <v>6380356</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265598</v>
+        <v>127265606</v>
       </c>
       <c r="B31" t="n">
         <v>98470</v>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721557</v>
+        <v>721475</v>
       </c>
       <c r="R31" t="n">
-        <v>6380422</v>
+        <v>6380396</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4062,7 +4062,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265606</v>
+        <v>127265598</v>
       </c>
       <c r="B32" t="n">
         <v>98470</v>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721475</v>
+        <v>721557</v>
       </c>
       <c r="R32" t="n">
-        <v>6380396</v>
+        <v>6380422</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4275,48 +4275,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127265594</v>
+        <v>127296661</v>
       </c>
       <c r="B34" t="n">
-        <v>109273</v>
+        <v>58338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721572</v>
+        <v>721560</v>
       </c>
       <c r="R34" t="n">
-        <v>6380434</v>
+        <v>6380582</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4348,11 +4357,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4364,7 +4368,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4493,57 +4497,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296661</v>
+        <v>127265594</v>
       </c>
       <c r="B36" t="n">
-        <v>58338</v>
+        <v>109273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721560</v>
+        <v>721572</v>
       </c>
       <c r="R36" t="n">
-        <v>6380582</v>
+        <v>6380434</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4575,6 +4570,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5030,48 +5030,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127265579</v>
+        <v>127265623</v>
       </c>
       <c r="B41" t="n">
-        <v>106044</v>
+        <v>98425</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721577</v>
+        <v>721199</v>
       </c>
       <c r="R41" t="n">
-        <v>6380550</v>
+        <v>6380248</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5132,7 +5141,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265545</v>
+        <v>127265579</v>
       </c>
       <c r="B42" t="n">
         <v>106044</v>
@@ -5163,14 +5172,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721560</v>
+        <v>721577</v>
       </c>
       <c r="R42" t="n">
-        <v>6380582</v>
+        <v>6380550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5216,7 +5225,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5234,57 +5243,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127265623</v>
+        <v>127265545</v>
       </c>
       <c r="B43" t="n">
-        <v>98425</v>
+        <v>106044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721199</v>
+        <v>721560</v>
       </c>
       <c r="R43" t="n">
-        <v>6380248</v>
+        <v>6380582</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5345,48 +5345,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265534</v>
+        <v>127265515</v>
       </c>
       <c r="B44" t="n">
-        <v>109273</v>
+        <v>98425</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721493</v>
+        <v>721315</v>
       </c>
       <c r="R44" t="n">
-        <v>6380446</v>
+        <v>6380362</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5447,10 +5456,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265515</v>
+        <v>127265571</v>
       </c>
       <c r="B45" t="n">
-        <v>98425</v>
+        <v>98365</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5458,26 +5467,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5487,17 +5496,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R45" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5558,54 +5567,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265571</v>
+        <v>127265534</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>109273</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721594</v>
+        <v>721493</v>
       </c>
       <c r="R46" t="n">
-        <v>6380563</v>
+        <v>6380446</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127265626</v>
+        <v>127265478</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>98425</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,26 +5680,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721183</v>
+        <v>721212</v>
       </c>
       <c r="R47" t="n">
-        <v>6380248</v>
+        <v>6380346</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127265597</v>
+        <v>127265626</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5824,13 +5824,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721557</v>
+        <v>721183</v>
       </c>
       <c r="R48" t="n">
-        <v>6380422</v>
+        <v>6380248</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127265478</v>
+        <v>127265597</v>
       </c>
       <c r="B49" t="n">
-        <v>98425</v>
+        <v>98365</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,26 +5902,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721212</v>
+        <v>721557</v>
       </c>
       <c r="R49" t="n">
-        <v>6380346</v>
+        <v>6380422</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127265593</v>
+        <v>127265628</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>98365</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,37 +6013,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721572</v>
+        <v>721173</v>
       </c>
       <c r="R50" t="n">
-        <v>6380434</v>
+        <v>6380248</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6104,10 +6113,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127265472</v>
+        <v>127265507</v>
       </c>
       <c r="B51" t="n">
-        <v>98470</v>
+        <v>98365</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,21 +6124,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6148,13 +6157,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721232</v>
+        <v>721307</v>
       </c>
       <c r="R51" t="n">
-        <v>6380313</v>
+        <v>6380360</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6215,10 +6224,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127265628</v>
+        <v>127265593</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6226,46 +6235,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721173</v>
+        <v>721572</v>
       </c>
       <c r="R52" t="n">
-        <v>6380248</v>
+        <v>6380434</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127265507</v>
+        <v>127265472</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6370,13 +6370,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721307</v>
+        <v>721232</v>
       </c>
       <c r="R53" t="n">
-        <v>6380360</v>
+        <v>6380313</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6660,45 +6660,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265471</v>
+        <v>127265484</v>
       </c>
       <c r="B56" t="n">
-        <v>106044</v>
+        <v>98365</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721232</v>
+        <v>721220</v>
       </c>
       <c r="R56" t="n">
-        <v>6380313</v>
+        <v>6380355</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -6762,45 +6771,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265481</v>
+        <v>127265494</v>
       </c>
       <c r="B57" t="n">
-        <v>109273</v>
+        <v>98469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721220</v>
+        <v>721247</v>
       </c>
       <c r="R57" t="n">
-        <v>6380355</v>
+        <v>6380342</v>
       </c>
       <c r="S57" t="n">
         <v>7</v>
@@ -6975,54 +6993,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265494</v>
+        <v>127265481</v>
       </c>
       <c r="B59" t="n">
-        <v>98469</v>
+        <v>109273</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721247</v>
+        <v>721220</v>
       </c>
       <c r="R59" t="n">
-        <v>6380342</v>
+        <v>6380355</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7086,54 +7095,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265484</v>
+        <v>127265471</v>
       </c>
       <c r="B60" t="n">
-        <v>98365</v>
+        <v>106044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R60" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7197,45 +7197,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265505</v>
+        <v>127265495</v>
       </c>
       <c r="B61" t="n">
-        <v>106044</v>
+        <v>98425</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721284</v>
+        <v>721247</v>
       </c>
       <c r="R61" t="n">
-        <v>6380359</v>
+        <v>6380342</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7299,48 +7308,62 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265488</v>
+        <v>127265617</v>
       </c>
       <c r="B62" t="n">
-        <v>106044</v>
+        <v>98469</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721231</v>
+        <v>721357</v>
       </c>
       <c r="R62" t="n">
-        <v>6380342</v>
+        <v>6380338</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7401,37 +7424,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265533</v>
+        <v>127265517</v>
       </c>
       <c r="B63" t="n">
-        <v>99198</v>
+        <v>98425</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7445,10 +7468,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721484</v>
+        <v>721330</v>
       </c>
       <c r="R63" t="n">
-        <v>6380450</v>
+        <v>6380365</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7512,37 +7535,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265474</v>
+        <v>127265533</v>
       </c>
       <c r="B64" t="n">
-        <v>98365</v>
+        <v>99198</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7552,17 +7575,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721232</v>
+        <v>721484</v>
       </c>
       <c r="R64" t="n">
-        <v>6380313</v>
+        <v>6380450</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7623,7 +7646,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265504</v>
+        <v>127265474</v>
       </c>
       <c r="B65" t="n">
         <v>98365</v>
@@ -7653,7 +7676,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7667,10 +7690,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721272</v>
+        <v>721232</v>
       </c>
       <c r="R65" t="n">
-        <v>6380356</v>
+        <v>6380313</v>
       </c>
       <c r="S65" t="n">
         <v>7</v>
@@ -7734,7 +7757,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265546</v>
+        <v>127265504</v>
       </c>
       <c r="B66" t="n">
         <v>98365</v>
@@ -7764,7 +7787,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7774,17 +7797,17 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721560</v>
+        <v>721272</v>
       </c>
       <c r="R66" t="n">
-        <v>6380582</v>
+        <v>6380356</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7827,7 +7850,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7845,10 +7868,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265495</v>
+        <v>127265546</v>
       </c>
       <c r="B67" t="n">
-        <v>98425</v>
+        <v>98365</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7856,26 +7879,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7885,17 +7908,17 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721247</v>
+        <v>721560</v>
       </c>
       <c r="R67" t="n">
-        <v>6380342</v>
+        <v>6380582</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7938,7 +7961,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7956,62 +7979,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265617</v>
+        <v>127265505</v>
       </c>
       <c r="B68" t="n">
-        <v>98469</v>
+        <v>106044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721357</v>
+        <v>721284</v>
       </c>
       <c r="R68" t="n">
-        <v>6380338</v>
+        <v>6380359</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8072,57 +8081,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265517</v>
+        <v>127265488</v>
       </c>
       <c r="B69" t="n">
-        <v>98425</v>
+        <v>106044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721330</v>
+        <v>721231</v>
       </c>
       <c r="R69" t="n">
-        <v>6380365</v>
+        <v>6380342</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8183,10 +8183,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127265525</v>
+        <v>127265476</v>
       </c>
       <c r="B70" t="n">
-        <v>98425</v>
+        <v>98365</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,26 +8194,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8223,17 +8223,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>721433</v>
+        <v>721209</v>
       </c>
       <c r="R70" t="n">
-        <v>6380417</v>
+        <v>6380333</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8263,6 +8263,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8294,10 +8299,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127265476</v>
+        <v>127265525</v>
       </c>
       <c r="B71" t="n">
-        <v>98365</v>
+        <v>98425</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8305,26 +8310,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8334,17 +8339,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>721209</v>
+        <v>721433</v>
       </c>
       <c r="R71" t="n">
-        <v>6380333</v>
+        <v>6380417</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8374,11 +8379,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8410,54 +8410,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265586</v>
+        <v>127265526</v>
       </c>
       <c r="B72" t="n">
-        <v>98470</v>
+        <v>109273</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721591</v>
+        <v>721433</v>
       </c>
       <c r="R72" t="n">
-        <v>6380497</v>
+        <v>6380417</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8490,6 +8481,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8521,45 +8517,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265526</v>
+        <v>127265586</v>
       </c>
       <c r="B73" t="n">
-        <v>109273</v>
+        <v>98470</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721433</v>
+        <v>721591</v>
       </c>
       <c r="R73" t="n">
-        <v>6380417</v>
+        <v>6380497</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8592,11 +8597,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9393,27 +9393,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265491</v>
+        <v>127265605</v>
       </c>
       <c r="B81" t="n">
-        <v>106044</v>
+        <v>109273</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9424,17 +9424,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721239</v>
+        <v>721466</v>
       </c>
       <c r="R81" t="n">
-        <v>6380330</v>
+        <v>6380394</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9495,27 +9495,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265605</v>
+        <v>127265491</v>
       </c>
       <c r="B82" t="n">
-        <v>109273</v>
+        <v>106044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9526,17 +9526,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721466</v>
+        <v>721239</v>
       </c>
       <c r="R82" t="n">
-        <v>6380394</v>
+        <v>6380330</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9708,45 +9708,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265549</v>
+        <v>127265572</v>
       </c>
       <c r="B84" t="n">
-        <v>106044</v>
+        <v>98425</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721590</v>
+        <v>721594</v>
       </c>
       <c r="R84" t="n">
-        <v>6380571</v>
+        <v>6380563</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9792,7 +9801,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9810,48 +9819,57 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265511</v>
+        <v>127265499</v>
       </c>
       <c r="B85" t="n">
-        <v>106044</v>
+        <v>98365</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721315</v>
+        <v>721247</v>
       </c>
       <c r="R85" t="n">
-        <v>6380362</v>
+        <v>6380342</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9912,54 +9930,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265572</v>
+        <v>127265549</v>
       </c>
       <c r="B86" t="n">
-        <v>98425</v>
+        <v>106044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721594</v>
+        <v>721590</v>
       </c>
       <c r="R86" t="n">
-        <v>6380563</v>
+        <v>6380571</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10005,7 +10014,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10023,57 +10032,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127265499</v>
+        <v>127265511</v>
       </c>
       <c r="B87" t="n">
-        <v>98365</v>
+        <v>106044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>721247</v>
+        <v>721315</v>
       </c>
       <c r="R87" t="n">
-        <v>6380342</v>
+        <v>6380362</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10134,48 +10134,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127265483</v>
+        <v>127265519</v>
       </c>
       <c r="B88" t="n">
-        <v>106044</v>
+        <v>98365</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>721220</v>
+        <v>721330</v>
       </c>
       <c r="R88" t="n">
-        <v>6380355</v>
+        <v>6380365</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265519</v>
+        <v>127265500</v>
       </c>
       <c r="B89" t="n">
         <v>98365</v>
@@ -10264,20 +10264,29 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721330</v>
+        <v>721263</v>
       </c>
       <c r="R89" t="n">
-        <v>6380365</v>
+        <v>6380356</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10338,7 +10347,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265500</v>
+        <v>127265506</v>
       </c>
       <c r="B90" t="n">
         <v>98365</v>
@@ -10368,7 +10377,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10382,10 +10391,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721263</v>
+        <v>721284</v>
       </c>
       <c r="R90" t="n">
-        <v>6380356</v>
+        <v>6380359</v>
       </c>
       <c r="S90" t="n">
         <v>7</v>
@@ -10449,54 +10458,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127265506</v>
+        <v>127265483</v>
       </c>
       <c r="B91" t="n">
-        <v>98365</v>
+        <v>106044</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>721284</v>
+        <v>721220</v>
       </c>
       <c r="R91" t="n">
-        <v>6380359</v>
+        <v>6380355</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265497</v>
+        <v>127265479</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,26 +2110,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721247</v>
+        <v>721212</v>
       </c>
       <c r="R14" t="n">
-        <v>6380342</v>
+        <v>6380346</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265518</v>
+        <v>127265530</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>98483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721330</v>
+        <v>721463</v>
       </c>
       <c r="R15" t="n">
-        <v>6380365</v>
+        <v>6380440</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,7 +2321,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265492</v>
+        <v>127265497</v>
       </c>
       <c r="B16" t="n">
         <v>98470</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R16" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S16" t="n">
         <v>7</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265587</v>
+        <v>127265518</v>
       </c>
       <c r="B17" t="n">
-        <v>105484</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2472,14 +2472,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721591</v>
+        <v>721330</v>
       </c>
       <c r="R17" t="n">
-        <v>6380497</v>
+        <v>6380365</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2543,48 +2543,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265532</v>
+        <v>127265492</v>
       </c>
       <c r="B18" t="n">
-        <v>106044</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721484</v>
+        <v>721239</v>
       </c>
       <c r="R18" t="n">
-        <v>6380450</v>
+        <v>6380330</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2645,45 +2654,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265540</v>
+        <v>127265587</v>
       </c>
       <c r="B19" t="n">
-        <v>106044</v>
+        <v>105484</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721546</v>
+        <v>721591</v>
       </c>
       <c r="R19" t="n">
-        <v>6380552</v>
+        <v>6380497</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2747,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2747,27 +2765,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265600</v>
+        <v>127265532</v>
       </c>
       <c r="B20" t="n">
-        <v>109273</v>
+        <v>106044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2778,14 +2796,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721547</v>
+        <v>721484</v>
       </c>
       <c r="R20" t="n">
-        <v>6380409</v>
+        <v>6380450</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2849,57 +2867,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265479</v>
+        <v>127265540</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>106044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721212</v>
+        <v>721546</v>
       </c>
       <c r="R21" t="n">
-        <v>6380346</v>
+        <v>6380552</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2942,7 +2951,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2960,54 +2969,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265530</v>
+        <v>127265600</v>
       </c>
       <c r="B22" t="n">
-        <v>98483</v>
+        <v>109273</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721463</v>
+        <v>721547</v>
       </c>
       <c r="R22" t="n">
-        <v>6380440</v>
+        <v>6380409</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3400,10 +3400,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265473</v>
+        <v>127265624</v>
       </c>
       <c r="B26" t="n">
-        <v>98425</v>
+        <v>98365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3411,26 +3411,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721232</v>
+        <v>721199</v>
       </c>
       <c r="R26" t="n">
-        <v>6380313</v>
+        <v>6380248</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,57 +3511,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265475</v>
+        <v>127265503</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>106044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721209</v>
+        <v>721272</v>
       </c>
       <c r="R27" t="n">
-        <v>6380333</v>
+        <v>6380356</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3622,10 +3613,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265624</v>
+        <v>127265473</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>98425</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,26 +3624,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3662,17 +3653,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721199</v>
+        <v>721232</v>
       </c>
       <c r="R28" t="n">
-        <v>6380248</v>
+        <v>6380313</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3733,48 +3724,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265503</v>
+        <v>127265475</v>
       </c>
       <c r="B29" t="n">
-        <v>106044</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721272</v>
+        <v>721209</v>
       </c>
       <c r="R29" t="n">
-        <v>6380356</v>
+        <v>6380333</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4386,54 +4386,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265584</v>
+        <v>127265594</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>109273</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721601</v>
+        <v>721572</v>
       </c>
       <c r="R35" t="n">
-        <v>6380518</v>
+        <v>6380434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,6 +4457,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,45 +4493,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265594</v>
+        <v>127265584</v>
       </c>
       <c r="B36" t="n">
-        <v>109273</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721572</v>
+        <v>721601</v>
       </c>
       <c r="R36" t="n">
-        <v>6380434</v>
+        <v>6380518</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,11 +4573,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5345,57 +5345,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265515</v>
+        <v>127265534</v>
       </c>
       <c r="B44" t="n">
-        <v>98425</v>
+        <v>109273</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721315</v>
+        <v>721493</v>
       </c>
       <c r="R44" t="n">
-        <v>6380362</v>
+        <v>6380446</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5567,48 +5558,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265534</v>
+        <v>127265515</v>
       </c>
       <c r="B46" t="n">
-        <v>109273</v>
+        <v>98425</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721493</v>
+        <v>721315</v>
       </c>
       <c r="R46" t="n">
-        <v>6380446</v>
+        <v>6380362</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127265628</v>
+        <v>127265593</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,46 +6013,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721173</v>
+        <v>721572</v>
       </c>
       <c r="R50" t="n">
-        <v>6380248</v>
+        <v>6380434</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6113,10 +6104,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127265507</v>
+        <v>127265472</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>98470</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,21 +6115,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6157,13 +6148,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721307</v>
+        <v>721232</v>
       </c>
       <c r="R51" t="n">
-        <v>6380360</v>
+        <v>6380313</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6224,10 +6215,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127265593</v>
+        <v>127265628</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>98365</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,37 +6226,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721572</v>
+        <v>721173</v>
       </c>
       <c r="R52" t="n">
-        <v>6380434</v>
+        <v>6380248</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127265472</v>
+        <v>127265507</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>98365</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6370,13 +6370,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721232</v>
+        <v>721307</v>
       </c>
       <c r="R53" t="n">
-        <v>6380313</v>
+        <v>6380360</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6437,64 +6437,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B54" t="n">
-        <v>43232</v>
+        <v>106044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R54" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,45 +6539,64 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B55" t="n">
-        <v>106044</v>
+        <v>43232</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R55" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7197,54 +7197,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265495</v>
+        <v>127265505</v>
       </c>
       <c r="B61" t="n">
-        <v>98425</v>
+        <v>106044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721247</v>
+        <v>721284</v>
       </c>
       <c r="R61" t="n">
-        <v>6380342</v>
+        <v>6380359</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7308,62 +7299,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265617</v>
+        <v>127265488</v>
       </c>
       <c r="B62" t="n">
-        <v>98469</v>
+        <v>106044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721357</v>
+        <v>721231</v>
       </c>
       <c r="R62" t="n">
-        <v>6380338</v>
+        <v>6380342</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7424,7 +7401,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265517</v>
+        <v>127265495</v>
       </c>
       <c r="B63" t="n">
         <v>98425</v>
@@ -7454,7 +7431,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7464,17 +7441,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721330</v>
+        <v>721247</v>
       </c>
       <c r="R63" t="n">
-        <v>6380365</v>
+        <v>6380342</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7535,37 +7512,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265533</v>
+        <v>127265617</v>
       </c>
       <c r="B64" t="n">
-        <v>99198</v>
+        <v>98469</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222361</v>
+        <v>219862</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7573,19 +7550,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721484</v>
+        <v>721357</v>
       </c>
       <c r="R64" t="n">
-        <v>6380450</v>
+        <v>6380338</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7646,10 +7628,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265474</v>
+        <v>127265517</v>
       </c>
       <c r="B65" t="n">
-        <v>98365</v>
+        <v>98425</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7657,26 +7639,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7686,17 +7668,17 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721232</v>
+        <v>721330</v>
       </c>
       <c r="R65" t="n">
-        <v>6380313</v>
+        <v>6380365</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7757,37 +7739,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265504</v>
+        <v>127265533</v>
       </c>
       <c r="B66" t="n">
-        <v>98365</v>
+        <v>99198</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7797,17 +7779,17 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721272</v>
+        <v>721484</v>
       </c>
       <c r="R66" t="n">
-        <v>6380356</v>
+        <v>6380450</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7868,7 +7850,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265546</v>
+        <v>127265474</v>
       </c>
       <c r="B67" t="n">
         <v>98365</v>
@@ -7898,7 +7880,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7908,17 +7890,17 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721560</v>
+        <v>721232</v>
       </c>
       <c r="R67" t="n">
-        <v>6380582</v>
+        <v>6380313</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7961,7 +7943,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7979,45 +7961,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265505</v>
+        <v>127265504</v>
       </c>
       <c r="B68" t="n">
-        <v>106044</v>
+        <v>98365</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721284</v>
+        <v>721272</v>
       </c>
       <c r="R68" t="n">
-        <v>6380359</v>
+        <v>6380356</v>
       </c>
       <c r="S68" t="n">
         <v>7</v>
@@ -8081,48 +8072,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265488</v>
+        <v>127265546</v>
       </c>
       <c r="B69" t="n">
-        <v>106044</v>
+        <v>98365</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721231</v>
+        <v>721560</v>
       </c>
       <c r="R69" t="n">
-        <v>6380342</v>
+        <v>6380582</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8739,54 +8739,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B75" t="n">
-        <v>98470</v>
+        <v>109273</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R75" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8850,45 +8841,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B76" t="n">
-        <v>109273</v>
+        <v>98470</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R76" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8952,57 +8952,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127265508</v>
+        <v>127265513</v>
       </c>
       <c r="B77" t="n">
-        <v>98425</v>
+        <v>109273</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721307</v>
+        <v>721315</v>
       </c>
       <c r="R77" t="n">
-        <v>6380360</v>
+        <v>6380362</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9063,48 +9054,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127265513</v>
+        <v>127265508</v>
       </c>
       <c r="B78" t="n">
-        <v>109273</v>
+        <v>98425</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721315</v>
+        <v>721307</v>
       </c>
       <c r="R78" t="n">
-        <v>6380362</v>
+        <v>6380360</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -4386,45 +4386,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265594</v>
+        <v>127265584</v>
       </c>
       <c r="B35" t="n">
-        <v>109273</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721572</v>
+        <v>721601</v>
       </c>
       <c r="R35" t="n">
-        <v>6380434</v>
+        <v>6380518</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4457,11 +4466,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,54 +4497,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265584</v>
+        <v>127265594</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>109273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721601</v>
+        <v>721572</v>
       </c>
       <c r="R36" t="n">
-        <v>6380518</v>
+        <v>6380434</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4573,6 +4568,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4604,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127265612</v>
+        <v>127265541</v>
       </c>
       <c r="B37" t="n">
-        <v>98484</v>
+        <v>98365</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,43 +4615,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721424</v>
+        <v>721546</v>
       </c>
       <c r="R37" t="n">
-        <v>6380372</v>
+        <v>6380552</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4697,7 +4688,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4715,7 +4706,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265541</v>
+        <v>127265566</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4746,14 +4737,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721546</v>
+        <v>721615</v>
       </c>
       <c r="R38" t="n">
-        <v>6380552</v>
+        <v>6380615</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4790,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4817,7 +4808,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265566</v>
+        <v>127265582</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -4845,17 +4836,26 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721615</v>
+        <v>721601</v>
       </c>
       <c r="R39" t="n">
-        <v>6380615</v>
+        <v>6380518</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265582</v>
+        <v>127265612</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>98484</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,21 +4930,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721601</v>
+        <v>721424</v>
       </c>
       <c r="R40" t="n">
-        <v>6380518</v>
+        <v>6380372</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -9165,67 +9165,57 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127296632</v>
+        <v>127265489</v>
       </c>
       <c r="B79" t="n">
-        <v>43232</v>
+        <v>98365</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>101242</v>
+        <v>223591</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>721578</v>
+        <v>721231</v>
       </c>
       <c r="R79" t="n">
-        <v>6380530</v>
+        <v>6380342</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9257,11 +9247,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Lundstarr rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9273,7 +9258,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9597,57 +9582,67 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127265489</v>
+        <v>127296632</v>
       </c>
       <c r="B83" t="n">
-        <v>98365</v>
+        <v>43232</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721231</v>
+        <v>721578</v>
       </c>
       <c r="R83" t="n">
-        <v>6380342</v>
+        <v>6380530</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9679,6 +9674,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lundstarr rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2102,7 +2102,7 @@
         <v>127265479</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>127265530</v>
       </c>
       <c r="B15" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265497</v>
+        <v>127265587</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>105486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,26 +2332,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721247</v>
+        <v>721591</v>
       </c>
       <c r="R16" t="n">
-        <v>6380342</v>
+        <v>6380497</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265518</v>
+        <v>127265492</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,17 +2472,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721330</v>
+        <v>721239</v>
       </c>
       <c r="R17" t="n">
-        <v>6380365</v>
+        <v>6380330</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2543,57 +2543,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265492</v>
+        <v>127265600</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>109275</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721239</v>
+        <v>721547</v>
       </c>
       <c r="R18" t="n">
-        <v>6380330</v>
+        <v>6380409</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2654,10 +2645,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265587</v>
+        <v>127265518</v>
       </c>
       <c r="B19" t="n">
-        <v>105484</v>
+        <v>98471</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,21 +2656,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2694,14 +2685,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721591</v>
+        <v>721330</v>
       </c>
       <c r="R19" t="n">
-        <v>6380497</v>
+        <v>6380365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2768,7 +2759,7 @@
         <v>127265532</v>
       </c>
       <c r="B20" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2861,7 @@
         <v>127265540</v>
       </c>
       <c r="B21" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2969,48 +2960,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265600</v>
+        <v>127265497</v>
       </c>
       <c r="B22" t="n">
-        <v>109273</v>
+        <v>98471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721547</v>
+        <v>721247</v>
       </c>
       <c r="R22" t="n">
-        <v>6380409</v>
+        <v>6380342</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>127265610</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>127265590</v>
       </c>
       <c r="B24" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>127265496</v>
       </c>
       <c r="B25" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265624</v>
+        <v>127265475</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>98471</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3411,21 +3411,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3440,14 +3440,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721199</v>
+        <v>721209</v>
       </c>
       <c r="R26" t="n">
-        <v>6380248</v>
+        <v>6380333</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3514,7 +3514,7 @@
         <v>127265503</v>
       </c>
       <c r="B27" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265473</v>
+        <v>127265624</v>
       </c>
       <c r="B28" t="n">
-        <v>98425</v>
+        <v>98366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,26 +3624,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3653,17 +3653,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721232</v>
+        <v>721199</v>
       </c>
       <c r="R28" t="n">
-        <v>6380313</v>
+        <v>6380248</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265475</v>
+        <v>127265473</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>98426</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3735,26 +3735,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3768,13 +3768,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721209</v>
+        <v>721232</v>
       </c>
       <c r="R29" t="n">
-        <v>6380333</v>
+        <v>6380313</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>127265548</v>
       </c>
       <c r="B30" t="n">
-        <v>99664</v>
+        <v>99665</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>127265606</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4062,57 +4062,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265598</v>
+        <v>127265486</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>109275</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721557</v>
+        <v>721231</v>
       </c>
       <c r="R32" t="n">
-        <v>6380422</v>
+        <v>6380342</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4155,7 +4146,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4173,48 +4164,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265486</v>
+        <v>127265598</v>
       </c>
       <c r="B33" t="n">
-        <v>109273</v>
+        <v>98471</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721231</v>
+        <v>721557</v>
       </c>
       <c r="R33" t="n">
-        <v>6380342</v>
+        <v>6380422</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4386,54 +4386,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265584</v>
+        <v>127265594</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>109275</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721601</v>
+        <v>721572</v>
       </c>
       <c r="R35" t="n">
-        <v>6380518</v>
+        <v>6380434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,6 +4457,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,45 +4493,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265594</v>
+        <v>127265584</v>
       </c>
       <c r="B36" t="n">
-        <v>109273</v>
+        <v>98471</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721572</v>
+        <v>721601</v>
       </c>
       <c r="R36" t="n">
-        <v>6380434</v>
+        <v>6380518</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,11 +4573,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,7 +4607,7 @@
         <v>127265541</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>127265566</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>127265582</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>127265612</v>
       </c>
       <c r="B40" t="n">
-        <v>98484</v>
+        <v>98485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>127265623</v>
       </c>
       <c r="B41" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>127265579</v>
       </c>
       <c r="B42" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>127265545</v>
       </c>
       <c r="B43" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>127265534</v>
       </c>
       <c r="B44" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265571</v>
+        <v>127265515</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>98426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5458,26 +5458,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5487,17 +5487,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721594</v>
+        <v>721315</v>
       </c>
       <c r="R45" t="n">
-        <v>6380563</v>
+        <v>6380362</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265515</v>
+        <v>127265571</v>
       </c>
       <c r="B46" t="n">
-        <v>98425</v>
+        <v>98366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5569,26 +5569,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5598,17 +5598,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R46" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127265478</v>
+        <v>127265626</v>
       </c>
       <c r="B47" t="n">
-        <v>98425</v>
+        <v>98366</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,26 +5680,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721212</v>
+        <v>721183</v>
       </c>
       <c r="R47" t="n">
-        <v>6380346</v>
+        <v>6380248</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127265626</v>
+        <v>127265597</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5824,13 +5824,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721183</v>
+        <v>721557</v>
       </c>
       <c r="R48" t="n">
-        <v>6380248</v>
+        <v>6380422</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127265597</v>
+        <v>127265478</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>98426</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,26 +5902,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721557</v>
+        <v>721212</v>
       </c>
       <c r="R49" t="n">
-        <v>6380422</v>
+        <v>6380346</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6005,7 +6005,7 @@
         <v>127265593</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>127265472</v>
       </c>
       <c r="B51" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>127265628</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>127265507</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6437,45 +6437,64 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B54" t="n">
-        <v>106044</v>
+        <v>43232</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R54" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6539,64 +6558,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B55" t="n">
-        <v>43232</v>
+        <v>106046</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R55" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6660,44 +6660,35 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265484</v>
+        <v>127265481</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
+        <v>109275</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
@@ -6771,32 +6762,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265494</v>
+        <v>127265622</v>
       </c>
       <c r="B57" t="n">
-        <v>98469</v>
+        <v>103904</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219862</v>
+        <v>220164</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6811,17 +6802,17 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721247</v>
+        <v>721252</v>
       </c>
       <c r="R57" t="n">
-        <v>6380342</v>
+        <v>6380274</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6882,32 +6873,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265622</v>
+        <v>127265494</v>
       </c>
       <c r="B58" t="n">
-        <v>103902</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220164</v>
+        <v>219862</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6922,17 +6913,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721252</v>
+        <v>721247</v>
       </c>
       <c r="R58" t="n">
-        <v>6380274</v>
+        <v>6380342</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6993,27 +6984,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265481</v>
+        <v>127265471</v>
       </c>
       <c r="B59" t="n">
-        <v>109273</v>
+        <v>106046</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7028,10 +7019,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R59" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7095,45 +7086,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265471</v>
+        <v>127265484</v>
       </c>
       <c r="B60" t="n">
-        <v>106044</v>
+        <v>98366</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721232</v>
+        <v>721220</v>
       </c>
       <c r="R60" t="n">
-        <v>6380313</v>
+        <v>6380355</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7200,7 +7200,7 @@
         <v>127265505</v>
       </c>
       <c r="B61" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>127265488</v>
       </c>
       <c r="B62" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7401,10 +7401,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265495</v>
+        <v>127265474</v>
       </c>
       <c r="B63" t="n">
-        <v>98425</v>
+        <v>98366</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7412,26 +7412,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721247</v>
+        <v>721232</v>
       </c>
       <c r="R63" t="n">
-        <v>6380342</v>
+        <v>6380313</v>
       </c>
       <c r="S63" t="n">
         <v>7</v>
@@ -7512,10 +7512,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265617</v>
+        <v>127265504</v>
       </c>
       <c r="B64" t="n">
-        <v>98469</v>
+        <v>98366</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7523,26 +7523,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7550,24 +7550,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721357</v>
+        <v>721272</v>
       </c>
       <c r="R64" t="n">
-        <v>6380338</v>
+        <v>6380356</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7628,37 +7623,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265517</v>
+        <v>127265533</v>
       </c>
       <c r="B65" t="n">
-        <v>98425</v>
+        <v>99199</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>222361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7672,10 +7667,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721330</v>
+        <v>721484</v>
       </c>
       <c r="R65" t="n">
-        <v>6380365</v>
+        <v>6380450</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7739,37 +7734,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265533</v>
+        <v>127265546</v>
       </c>
       <c r="B66" t="n">
-        <v>99198</v>
+        <v>98366</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222361</v>
+        <v>223591</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7783,10 +7778,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721484</v>
+        <v>721560</v>
       </c>
       <c r="R66" t="n">
-        <v>6380450</v>
+        <v>6380582</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7832,7 +7827,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7850,10 +7845,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265474</v>
+        <v>127265617</v>
       </c>
       <c r="B67" t="n">
-        <v>98365</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7861,26 +7856,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7888,19 +7883,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721232</v>
+        <v>721357</v>
       </c>
       <c r="R67" t="n">
-        <v>6380313</v>
+        <v>6380338</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7961,10 +7961,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265504</v>
+        <v>127265495</v>
       </c>
       <c r="B68" t="n">
-        <v>98365</v>
+        <v>98426</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7972,26 +7972,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721272</v>
+        <v>721247</v>
       </c>
       <c r="R68" t="n">
-        <v>6380356</v>
+        <v>6380342</v>
       </c>
       <c r="S68" t="n">
         <v>7</v>
@@ -8072,10 +8072,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265546</v>
+        <v>127265517</v>
       </c>
       <c r="B69" t="n">
-        <v>98365</v>
+        <v>98426</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8083,26 +8083,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721560</v>
+        <v>721330</v>
       </c>
       <c r="R69" t="n">
-        <v>6380582</v>
+        <v>6380365</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8186,7 +8186,7 @@
         <v>127265476</v>
       </c>
       <c r="B70" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>127265525</v>
       </c>
       <c r="B71" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,45 +8410,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265526</v>
+        <v>127265586</v>
       </c>
       <c r="B72" t="n">
-        <v>109273</v>
+        <v>98471</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721433</v>
+        <v>721591</v>
       </c>
       <c r="R72" t="n">
-        <v>6380417</v>
+        <v>6380497</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8481,11 +8490,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8517,54 +8521,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265586</v>
+        <v>127265526</v>
       </c>
       <c r="B73" t="n">
-        <v>98470</v>
+        <v>109275</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721591</v>
+        <v>721433</v>
       </c>
       <c r="R73" t="n">
-        <v>6380497</v>
+        <v>6380417</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8597,6 +8592,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8631,7 +8631,7 @@
         <v>127265528</v>
       </c>
       <c r="B74" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8739,45 +8739,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B75" t="n">
-        <v>109273</v>
+        <v>98471</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R75" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8841,54 +8850,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B76" t="n">
-        <v>98470</v>
+        <v>109275</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R76" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8952,48 +8952,57 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127265513</v>
+        <v>127265508</v>
       </c>
       <c r="B77" t="n">
-        <v>109273</v>
+        <v>98426</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721315</v>
+        <v>721307</v>
       </c>
       <c r="R77" t="n">
-        <v>6380362</v>
+        <v>6380360</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9054,57 +9063,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127265508</v>
+        <v>127265513</v>
       </c>
       <c r="B78" t="n">
-        <v>98425</v>
+        <v>109275</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721307</v>
+        <v>721315</v>
       </c>
       <c r="R78" t="n">
-        <v>6380360</v>
+        <v>6380362</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9165,57 +9165,67 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127265489</v>
+        <v>127296632</v>
       </c>
       <c r="B79" t="n">
-        <v>98365</v>
+        <v>43232</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>721231</v>
+        <v>721578</v>
       </c>
       <c r="R79" t="n">
-        <v>6380342</v>
+        <v>6380530</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9247,6 +9257,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Lundstarr rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9258,7 +9273,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9276,10 +9291,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265493</v>
+        <v>127265491</v>
       </c>
       <c r="B80" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9311,10 +9326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721247</v>
+        <v>721239</v>
       </c>
       <c r="R80" t="n">
-        <v>6380342</v>
+        <v>6380330</v>
       </c>
       <c r="S80" t="n">
         <v>7</v>
@@ -9378,27 +9393,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265605</v>
+        <v>127265493</v>
       </c>
       <c r="B81" t="n">
-        <v>109273</v>
+        <v>106046</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9409,17 +9424,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721466</v>
+        <v>721247</v>
       </c>
       <c r="R81" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9480,27 +9495,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265491</v>
+        <v>127265605</v>
       </c>
       <c r="B82" t="n">
-        <v>106044</v>
+        <v>109275</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9511,17 +9526,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721239</v>
+        <v>721466</v>
       </c>
       <c r="R82" t="n">
-        <v>6380330</v>
+        <v>6380394</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9582,67 +9597,57 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127296632</v>
+        <v>127265489</v>
       </c>
       <c r="B83" t="n">
-        <v>43232</v>
+        <v>98366</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101242</v>
+        <v>223591</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721578</v>
+        <v>721231</v>
       </c>
       <c r="R83" t="n">
-        <v>6380530</v>
+        <v>6380342</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9674,11 +9679,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Lundstarr rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9708,57 +9708,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265572</v>
+        <v>127265511</v>
       </c>
       <c r="B84" t="n">
-        <v>98425</v>
+        <v>106046</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721594</v>
+        <v>721315</v>
       </c>
       <c r="R84" t="n">
-        <v>6380563</v>
+        <v>6380362</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9819,57 +9810,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265499</v>
+        <v>127265549</v>
       </c>
       <c r="B85" t="n">
-        <v>98365</v>
+        <v>106046</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721247</v>
+        <v>721590</v>
       </c>
       <c r="R85" t="n">
-        <v>6380342</v>
+        <v>6380571</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9912,7 +9894,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9930,48 +9912,57 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265549</v>
+        <v>127265499</v>
       </c>
       <c r="B86" t="n">
-        <v>106044</v>
+        <v>98366</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721590</v>
+        <v>721247</v>
       </c>
       <c r="R86" t="n">
-        <v>6380571</v>
+        <v>6380342</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10014,7 +10005,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10032,48 +10023,57 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127265511</v>
+        <v>127265572</v>
       </c>
       <c r="B87" t="n">
-        <v>106044</v>
+        <v>98426</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R87" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10134,48 +10134,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127265519</v>
+        <v>127265483</v>
       </c>
       <c r="B88" t="n">
-        <v>98365</v>
+        <v>106046</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>721330</v>
+        <v>721220</v>
       </c>
       <c r="R88" t="n">
-        <v>6380365</v>
+        <v>6380355</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265500</v>
+        <v>127265519</v>
       </c>
       <c r="B89" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10264,29 +10264,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721263</v>
+        <v>721330</v>
       </c>
       <c r="R89" t="n">
-        <v>6380356</v>
+        <v>6380365</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10347,10 +10338,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265506</v>
+        <v>127265500</v>
       </c>
       <c r="B90" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10377,7 +10368,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10391,10 +10382,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721284</v>
+        <v>721263</v>
       </c>
       <c r="R90" t="n">
-        <v>6380359</v>
+        <v>6380356</v>
       </c>
       <c r="S90" t="n">
         <v>7</v>
@@ -10458,45 +10449,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127265483</v>
+        <v>127265506</v>
       </c>
       <c r="B91" t="n">
-        <v>106044</v>
+        <v>98366</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>721220</v>
+        <v>721284</v>
       </c>
       <c r="R91" t="n">
-        <v>6380355</v>
+        <v>6380359</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -3951,7 +3951,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265606</v>
+        <v>127265598</v>
       </c>
       <c r="B31" t="n">
         <v>98471</v>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721475</v>
+        <v>721557</v>
       </c>
       <c r="R31" t="n">
-        <v>6380396</v>
+        <v>6380422</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4062,48 +4062,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265486</v>
+        <v>127265606</v>
       </c>
       <c r="B32" t="n">
-        <v>109275</v>
+        <v>98471</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721231</v>
+        <v>721475</v>
       </c>
       <c r="R32" t="n">
-        <v>6380342</v>
+        <v>6380396</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4164,57 +4173,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265598</v>
+        <v>127265486</v>
       </c>
       <c r="B33" t="n">
-        <v>98471</v>
+        <v>109275</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721557</v>
+        <v>721231</v>
       </c>
       <c r="R33" t="n">
-        <v>6380422</v>
+        <v>6380342</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -9165,67 +9165,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127296632</v>
+        <v>127265491</v>
       </c>
       <c r="B79" t="n">
-        <v>43232</v>
+        <v>106046</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>721578</v>
+        <v>721239</v>
       </c>
       <c r="R79" t="n">
-        <v>6380530</v>
+        <v>6380330</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9257,11 +9238,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Lundstarr rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9273,7 +9249,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9291,7 +9267,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265491</v>
+        <v>127265493</v>
       </c>
       <c r="B80" t="n">
         <v>106046</v>
@@ -9326,10 +9302,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R80" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S80" t="n">
         <v>7</v>
@@ -9393,27 +9369,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265493</v>
+        <v>127265605</v>
       </c>
       <c r="B81" t="n">
-        <v>106046</v>
+        <v>109275</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9424,17 +9400,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R81" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9495,48 +9471,57 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265605</v>
+        <v>127265489</v>
       </c>
       <c r="B82" t="n">
-        <v>109275</v>
+        <v>98366</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721466</v>
+        <v>721231</v>
       </c>
       <c r="R82" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9597,57 +9582,67 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127265489</v>
+        <v>127296632</v>
       </c>
       <c r="B83" t="n">
-        <v>98366</v>
+        <v>43232</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721231</v>
+        <v>721578</v>
       </c>
       <c r="R83" t="n">
-        <v>6380342</v>
+        <v>6380530</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9679,6 +9674,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lundstarr rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9708,48 +9708,57 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265511</v>
+        <v>127265572</v>
       </c>
       <c r="B84" t="n">
-        <v>106046</v>
+        <v>98426</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R84" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9810,7 +9819,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265549</v>
+        <v>127265511</v>
       </c>
       <c r="B85" t="n">
         <v>106046</v>
@@ -9841,17 +9850,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721590</v>
+        <v>721315</v>
       </c>
       <c r="R85" t="n">
-        <v>6380571</v>
+        <v>6380362</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9894,7 +9903,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9912,57 +9921,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265499</v>
+        <v>127265549</v>
       </c>
       <c r="B86" t="n">
-        <v>98366</v>
+        <v>106046</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721247</v>
+        <v>721590</v>
       </c>
       <c r="R86" t="n">
-        <v>6380342</v>
+        <v>6380571</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10023,10 +10023,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127265572</v>
+        <v>127265499</v>
       </c>
       <c r="B87" t="n">
-        <v>98426</v>
+        <v>98366</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10034,26 +10034,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10063,17 +10063,17 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>721594</v>
+        <v>721247</v>
       </c>
       <c r="R87" t="n">
-        <v>6380563</v>
+        <v>6380342</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,57 +2099,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265479</v>
+        <v>127265532</v>
       </c>
       <c r="B14" t="n">
-        <v>98366</v>
+        <v>106048</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721212</v>
+        <v>721484</v>
       </c>
       <c r="R14" t="n">
-        <v>6380346</v>
+        <v>6380450</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265530</v>
+        <v>127265587</v>
       </c>
       <c r="B15" t="n">
-        <v>98484</v>
+        <v>105488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,21 +2212,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223621</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2250,14 +2241,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721463</v>
+        <v>721591</v>
       </c>
       <c r="R15" t="n">
-        <v>6380440</v>
+        <v>6380497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,54 +2312,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265587</v>
+        <v>127265600</v>
       </c>
       <c r="B16" t="n">
-        <v>105486</v>
+        <v>109277</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721591</v>
+        <v>721547</v>
       </c>
       <c r="R16" t="n">
-        <v>6380497</v>
+        <v>6380409</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2432,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265492</v>
+        <v>127265497</v>
       </c>
       <c r="B17" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,7 +2444,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2476,10 +2458,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R17" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
@@ -2543,45 +2525,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265600</v>
+        <v>127265518</v>
       </c>
       <c r="B18" t="n">
-        <v>109275</v>
+        <v>98473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721547</v>
+        <v>721330</v>
       </c>
       <c r="R18" t="n">
-        <v>6380409</v>
+        <v>6380365</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2645,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265518</v>
+        <v>127265492</v>
       </c>
       <c r="B19" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,17 +2676,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721330</v>
+        <v>721239</v>
       </c>
       <c r="R19" t="n">
-        <v>6380365</v>
+        <v>6380330</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2756,48 +2747,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265532</v>
+        <v>127265479</v>
       </c>
       <c r="B20" t="n">
-        <v>106046</v>
+        <v>98368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721484</v>
+        <v>721212</v>
       </c>
       <c r="R20" t="n">
-        <v>6380450</v>
+        <v>6380346</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2858,45 +2858,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265540</v>
+        <v>127265530</v>
       </c>
       <c r="B21" t="n">
-        <v>106046</v>
+        <v>98486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220785</v>
+        <v>223621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721546</v>
+        <v>721463</v>
       </c>
       <c r="R21" t="n">
-        <v>6380552</v>
+        <v>6380440</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2942,7 +2951,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2960,57 +2969,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265497</v>
+        <v>127265540</v>
       </c>
       <c r="B22" t="n">
-        <v>98471</v>
+        <v>106048</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721247</v>
+        <v>721546</v>
       </c>
       <c r="R22" t="n">
-        <v>6380342</v>
+        <v>6380552</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
         <v>127265610</v>
       </c>
       <c r="B23" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>127265590</v>
       </c>
       <c r="B24" t="n">
-        <v>98484</v>
+        <v>98486</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>127265496</v>
       </c>
       <c r="B25" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>127265475</v>
       </c>
       <c r="B26" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,45 +3511,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265503</v>
+        <v>127265473</v>
       </c>
       <c r="B27" t="n">
-        <v>106046</v>
+        <v>98428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721272</v>
+        <v>721232</v>
       </c>
       <c r="R27" t="n">
-        <v>6380356</v>
+        <v>6380313</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3613,57 +3622,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265624</v>
+        <v>127265503</v>
       </c>
       <c r="B28" t="n">
-        <v>98366</v>
+        <v>106048</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721199</v>
+        <v>721272</v>
       </c>
       <c r="R28" t="n">
-        <v>6380248</v>
+        <v>6380356</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265473</v>
+        <v>127265624</v>
       </c>
       <c r="B29" t="n">
-        <v>98426</v>
+        <v>98368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3735,26 +3735,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3764,17 +3764,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721232</v>
+        <v>721199</v>
       </c>
       <c r="R29" t="n">
-        <v>6380313</v>
+        <v>6380248</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>127265548</v>
       </c>
       <c r="B30" t="n">
-        <v>99665</v>
+        <v>99667</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,57 +3951,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265598</v>
+        <v>127265486</v>
       </c>
       <c r="B31" t="n">
-        <v>98471</v>
+        <v>109277</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721557</v>
+        <v>721231</v>
       </c>
       <c r="R31" t="n">
-        <v>6380422</v>
+        <v>6380342</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4044,7 +4035,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4065,7 +4056,7 @@
         <v>127265606</v>
       </c>
       <c r="B32" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,48 +4164,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265486</v>
+        <v>127265598</v>
       </c>
       <c r="B33" t="n">
-        <v>109275</v>
+        <v>98473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721231</v>
+        <v>721557</v>
       </c>
       <c r="R33" t="n">
-        <v>6380342</v>
+        <v>6380422</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
         <v>127296661</v>
       </c>
       <c r="B34" t="n">
-        <v>58338</v>
+        <v>58340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4386,45 +4386,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265594</v>
+        <v>127265584</v>
       </c>
       <c r="B35" t="n">
-        <v>109275</v>
+        <v>98473</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721572</v>
+        <v>721601</v>
       </c>
       <c r="R35" t="n">
-        <v>6380434</v>
+        <v>6380518</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4457,11 +4466,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,54 +4497,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265584</v>
+        <v>127265594</v>
       </c>
       <c r="B36" t="n">
-        <v>98471</v>
+        <v>109277</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721601</v>
+        <v>721572</v>
       </c>
       <c r="R36" t="n">
-        <v>6380518</v>
+        <v>6380434</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4573,6 +4568,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,7 +4607,7 @@
         <v>127265541</v>
       </c>
       <c r="B37" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>127265566</v>
       </c>
       <c r="B38" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>127265582</v>
       </c>
       <c r="B39" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>127265612</v>
       </c>
       <c r="B40" t="n">
-        <v>98485</v>
+        <v>98487</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5030,57 +5030,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127265623</v>
+        <v>127265579</v>
       </c>
       <c r="B41" t="n">
-        <v>98426</v>
+        <v>106048</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721199</v>
+        <v>721577</v>
       </c>
       <c r="R41" t="n">
-        <v>6380248</v>
+        <v>6380550</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5141,10 +5132,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265579</v>
+        <v>127265545</v>
       </c>
       <c r="B42" t="n">
-        <v>106046</v>
+        <v>106048</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5172,14 +5163,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721577</v>
+        <v>721560</v>
       </c>
       <c r="R42" t="n">
-        <v>6380550</v>
+        <v>6380582</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5225,7 +5216,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5243,48 +5234,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127265545</v>
+        <v>127265623</v>
       </c>
       <c r="B43" t="n">
-        <v>106046</v>
+        <v>98428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721560</v>
+        <v>721199</v>
       </c>
       <c r="R43" t="n">
-        <v>6380582</v>
+        <v>6380248</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5345,45 +5345,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265534</v>
+        <v>127265571</v>
       </c>
       <c r="B44" t="n">
-        <v>109275</v>
+        <v>98368</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721493</v>
+        <v>721594</v>
       </c>
       <c r="R44" t="n">
-        <v>6380446</v>
+        <v>6380563</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5450,7 +5459,7 @@
         <v>127265515</v>
       </c>
       <c r="B45" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5558,54 +5567,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265571</v>
+        <v>127265534</v>
       </c>
       <c r="B46" t="n">
-        <v>98366</v>
+        <v>109277</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721594</v>
+        <v>721493</v>
       </c>
       <c r="R46" t="n">
-        <v>6380563</v>
+        <v>6380446</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127265626</v>
+        <v>127265478</v>
       </c>
       <c r="B47" t="n">
-        <v>98366</v>
+        <v>98428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,26 +5680,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721183</v>
+        <v>721212</v>
       </c>
       <c r="R47" t="n">
-        <v>6380248</v>
+        <v>6380346</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127265597</v>
+        <v>127265626</v>
       </c>
       <c r="B48" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5824,13 +5824,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721557</v>
+        <v>721183</v>
       </c>
       <c r="R48" t="n">
-        <v>6380422</v>
+        <v>6380248</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127265478</v>
+        <v>127265597</v>
       </c>
       <c r="B49" t="n">
-        <v>98426</v>
+        <v>98368</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,26 +5902,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721212</v>
+        <v>721557</v>
       </c>
       <c r="R49" t="n">
-        <v>6380346</v>
+        <v>6380422</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6005,7 +6005,7 @@
         <v>127265593</v>
       </c>
       <c r="B50" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>127265472</v>
       </c>
       <c r="B51" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>127265628</v>
       </c>
       <c r="B52" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>127265507</v>
       </c>
       <c r="B53" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6437,64 +6437,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B54" t="n">
-        <v>43232</v>
+        <v>106048</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R54" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,45 +6539,64 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B55" t="n">
-        <v>106046</v>
+        <v>43234</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R55" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6660,35 +6660,44 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265481</v>
+        <v>127265484</v>
       </c>
       <c r="B56" t="n">
-        <v>109275</v>
+        <v>98368</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
@@ -6765,7 +6774,7 @@
         <v>127265622</v>
       </c>
       <c r="B57" t="n">
-        <v>103904</v>
+        <v>103906</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6873,54 +6882,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265494</v>
+        <v>127265471</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>106048</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721247</v>
+        <v>721232</v>
       </c>
       <c r="R58" t="n">
-        <v>6380342</v>
+        <v>6380313</v>
       </c>
       <c r="S58" t="n">
         <v>7</v>
@@ -6984,45 +6984,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265471</v>
+        <v>127265494</v>
       </c>
       <c r="B59" t="n">
-        <v>106046</v>
+        <v>98472</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721232</v>
+        <v>721247</v>
       </c>
       <c r="R59" t="n">
-        <v>6380313</v>
+        <v>6380342</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7086,44 +7095,35 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265484</v>
+        <v>127265481</v>
       </c>
       <c r="B60" t="n">
-        <v>98366</v>
+        <v>109277</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
@@ -7197,45 +7197,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265505</v>
+        <v>127265474</v>
       </c>
       <c r="B61" t="n">
-        <v>106046</v>
+        <v>98368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721284</v>
+        <v>721232</v>
       </c>
       <c r="R61" t="n">
-        <v>6380359</v>
+        <v>6380313</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7299,48 +7308,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265488</v>
+        <v>127265504</v>
       </c>
       <c r="B62" t="n">
-        <v>106046</v>
+        <v>98368</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721231</v>
+        <v>721272</v>
       </c>
       <c r="R62" t="n">
-        <v>6380342</v>
+        <v>6380356</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7401,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265474</v>
+        <v>127265546</v>
       </c>
       <c r="B63" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7431,7 +7449,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7441,17 +7459,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721232</v>
+        <v>721560</v>
       </c>
       <c r="R63" t="n">
-        <v>6380313</v>
+        <v>6380582</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7494,7 +7512,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7512,10 +7530,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265504</v>
+        <v>127265617</v>
       </c>
       <c r="B64" t="n">
-        <v>98366</v>
+        <v>98472</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7523,26 +7541,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7550,19 +7568,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721272</v>
+        <v>721357</v>
       </c>
       <c r="R64" t="n">
-        <v>6380356</v>
+        <v>6380338</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7623,37 +7646,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265533</v>
+        <v>127265517</v>
       </c>
       <c r="B65" t="n">
-        <v>99199</v>
+        <v>98428</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7667,10 +7690,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721484</v>
+        <v>721330</v>
       </c>
       <c r="R65" t="n">
-        <v>6380450</v>
+        <v>6380365</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7734,57 +7757,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265546</v>
+        <v>127265505</v>
       </c>
       <c r="B66" t="n">
-        <v>98366</v>
+        <v>106048</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721560</v>
+        <v>721284</v>
       </c>
       <c r="R66" t="n">
-        <v>6380582</v>
+        <v>6380359</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7827,7 +7841,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7845,62 +7859,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265617</v>
+        <v>127265488</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>106048</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721357</v>
+        <v>721231</v>
       </c>
       <c r="R67" t="n">
-        <v>6380338</v>
+        <v>6380342</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>127265495</v>
       </c>
       <c r="B68" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8072,37 +8072,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265517</v>
+        <v>127265533</v>
       </c>
       <c r="B69" t="n">
-        <v>98426</v>
+        <v>99201</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>222361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721330</v>
+        <v>721484</v>
       </c>
       <c r="R69" t="n">
-        <v>6380365</v>
+        <v>6380450</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8186,7 +8186,7 @@
         <v>127265476</v>
       </c>
       <c r="B70" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>127265525</v>
       </c>
       <c r="B71" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265586</v>
+        <v>127265528</v>
       </c>
       <c r="B72" t="n">
-        <v>98471</v>
+        <v>98368</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721591</v>
+        <v>721460</v>
       </c>
       <c r="R72" t="n">
-        <v>6380497</v>
+        <v>6380438</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8521,45 +8521,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265526</v>
+        <v>127265586</v>
       </c>
       <c r="B73" t="n">
-        <v>109275</v>
+        <v>98473</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721433</v>
+        <v>721591</v>
       </c>
       <c r="R73" t="n">
-        <v>6380417</v>
+        <v>6380497</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8592,11 +8601,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8628,54 +8632,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127265528</v>
+        <v>127265526</v>
       </c>
       <c r="B74" t="n">
-        <v>98366</v>
+        <v>109277</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>721460</v>
+        <v>721433</v>
       </c>
       <c r="R74" t="n">
-        <v>6380438</v>
+        <v>6380417</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8708,6 +8703,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8739,54 +8739,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B75" t="n">
-        <v>98471</v>
+        <v>109277</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R75" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8850,45 +8841,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B76" t="n">
-        <v>109275</v>
+        <v>98473</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R76" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8952,57 +8952,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127265508</v>
+        <v>127265513</v>
       </c>
       <c r="B77" t="n">
-        <v>98426</v>
+        <v>109277</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721307</v>
+        <v>721315</v>
       </c>
       <c r="R77" t="n">
-        <v>6380360</v>
+        <v>6380362</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9063,48 +9054,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127265513</v>
+        <v>127265508</v>
       </c>
       <c r="B78" t="n">
-        <v>109275</v>
+        <v>98428</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721315</v>
+        <v>721307</v>
       </c>
       <c r="R78" t="n">
-        <v>6380362</v>
+        <v>6380360</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9165,48 +9165,67 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127265491</v>
+        <v>127296632</v>
       </c>
       <c r="B79" t="n">
-        <v>106046</v>
+        <v>43234</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>721239</v>
+        <v>721578</v>
       </c>
       <c r="R79" t="n">
-        <v>6380330</v>
+        <v>6380530</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9238,6 +9257,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Lundstarr rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9249,7 +9273,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9267,10 +9291,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265493</v>
+        <v>127265491</v>
       </c>
       <c r="B80" t="n">
-        <v>106046</v>
+        <v>106048</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9302,10 +9326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721247</v>
+        <v>721239</v>
       </c>
       <c r="R80" t="n">
-        <v>6380342</v>
+        <v>6380330</v>
       </c>
       <c r="S80" t="n">
         <v>7</v>
@@ -9369,48 +9393,57 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265605</v>
+        <v>127265489</v>
       </c>
       <c r="B81" t="n">
-        <v>109275</v>
+        <v>98368</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721466</v>
+        <v>721231</v>
       </c>
       <c r="R81" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9471,57 +9504,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265489</v>
+        <v>127265493</v>
       </c>
       <c r="B82" t="n">
-        <v>98366</v>
+        <v>106048</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721231</v>
+        <v>721247</v>
       </c>
       <c r="R82" t="n">
         <v>6380342</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9582,10 +9606,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127296632</v>
+        <v>127265605</v>
       </c>
       <c r="B83" t="n">
-        <v>43232</v>
+        <v>109277</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9593,53 +9617,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721578</v>
+        <v>721466</v>
       </c>
       <c r="R83" t="n">
-        <v>6380530</v>
+        <v>6380394</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9674,11 +9679,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Lundstarr rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265572</v>
+        <v>127265499</v>
       </c>
       <c r="B84" t="n">
-        <v>98426</v>
+        <v>98368</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9719,26 +9719,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9748,17 +9748,17 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721594</v>
+        <v>721247</v>
       </c>
       <c r="R84" t="n">
-        <v>6380563</v>
+        <v>6380342</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9819,48 +9819,57 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265511</v>
+        <v>127265572</v>
       </c>
       <c r="B85" t="n">
-        <v>106046</v>
+        <v>98428</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R85" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9924,7 +9933,7 @@
         <v>127265549</v>
       </c>
       <c r="B86" t="n">
-        <v>106046</v>
+        <v>106048</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10023,57 +10032,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127265499</v>
+        <v>127265511</v>
       </c>
       <c r="B87" t="n">
-        <v>98366</v>
+        <v>106048</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>721247</v>
+        <v>721315</v>
       </c>
       <c r="R87" t="n">
-        <v>6380342</v>
+        <v>6380362</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10134,48 +10134,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127265483</v>
+        <v>127265519</v>
       </c>
       <c r="B88" t="n">
-        <v>106046</v>
+        <v>98368</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>721220</v>
+        <v>721330</v>
       </c>
       <c r="R88" t="n">
-        <v>6380355</v>
+        <v>6380365</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265519</v>
+        <v>127265500</v>
       </c>
       <c r="B89" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10264,20 +10264,29 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721330</v>
+        <v>721263</v>
       </c>
       <c r="R89" t="n">
-        <v>6380365</v>
+        <v>6380356</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10338,10 +10347,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265500</v>
+        <v>127265506</v>
       </c>
       <c r="B90" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10368,7 +10377,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10382,10 +10391,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721263</v>
+        <v>721284</v>
       </c>
       <c r="R90" t="n">
-        <v>6380356</v>
+        <v>6380359</v>
       </c>
       <c r="S90" t="n">
         <v>7</v>
@@ -10449,54 +10458,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127265506</v>
+        <v>127265483</v>
       </c>
       <c r="B91" t="n">
-        <v>98366</v>
+        <v>106048</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>721284</v>
+        <v>721220</v>
       </c>
       <c r="R91" t="n">
-        <v>6380359</v>
+        <v>6380355</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,48 +2099,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265532</v>
+        <v>127265497</v>
       </c>
       <c r="B14" t="n">
-        <v>106048</v>
+        <v>98473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721484</v>
+        <v>721247</v>
       </c>
       <c r="R14" t="n">
-        <v>6380450</v>
+        <v>6380342</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265587</v>
+        <v>127265518</v>
       </c>
       <c r="B15" t="n">
-        <v>105488</v>
+        <v>98473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,21 +2221,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2241,14 +2250,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721591</v>
+        <v>721330</v>
       </c>
       <c r="R15" t="n">
-        <v>6380497</v>
+        <v>6380365</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,48 +2321,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265600</v>
+        <v>127265492</v>
       </c>
       <c r="B16" t="n">
-        <v>109277</v>
+        <v>98473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721547</v>
+        <v>721239</v>
       </c>
       <c r="R16" t="n">
-        <v>6380409</v>
+        <v>6380330</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2414,57 +2432,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265497</v>
+        <v>127265600</v>
       </c>
       <c r="B17" t="n">
-        <v>98473</v>
+        <v>109277</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721247</v>
+        <v>721547</v>
       </c>
       <c r="R17" t="n">
-        <v>6380342</v>
+        <v>6380409</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2525,54 +2534,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265518</v>
+        <v>127265532</v>
       </c>
       <c r="B18" t="n">
-        <v>98473</v>
+        <v>106048</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721330</v>
+        <v>721484</v>
       </c>
       <c r="R18" t="n">
-        <v>6380365</v>
+        <v>6380450</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2636,57 +2636,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265492</v>
+        <v>127265540</v>
       </c>
       <c r="B19" t="n">
-        <v>98473</v>
+        <v>106048</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721239</v>
+        <v>721546</v>
       </c>
       <c r="R19" t="n">
-        <v>6380330</v>
+        <v>6380552</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2729,7 +2720,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2969,45 +2960,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265540</v>
+        <v>127265587</v>
       </c>
       <c r="B22" t="n">
-        <v>106048</v>
+        <v>105488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721546</v>
+        <v>721591</v>
       </c>
       <c r="R22" t="n">
-        <v>6380552</v>
+        <v>6380497</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3071,57 +3071,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265610</v>
+        <v>127265496</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>109277</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721466</v>
+        <v>721247</v>
       </c>
       <c r="R23" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3182,10 +3173,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127265590</v>
+        <v>127265610</v>
       </c>
       <c r="B24" t="n">
-        <v>98486</v>
+        <v>98368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,21 +3184,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223621</v>
+        <v>223591</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3226,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721580</v>
+        <v>721466</v>
       </c>
       <c r="R24" t="n">
-        <v>6380472</v>
+        <v>6380394</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3264,11 +3255,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3280,7 +3266,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3298,48 +3284,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265496</v>
+        <v>127265590</v>
       </c>
       <c r="B25" t="n">
-        <v>109277</v>
+        <v>98486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721247</v>
+        <v>721580</v>
       </c>
       <c r="R25" t="n">
-        <v>6380342</v>
+        <v>6380472</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3371,6 +3366,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265475</v>
+        <v>127265473</v>
       </c>
       <c r="B26" t="n">
-        <v>98473</v>
+        <v>98428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3411,26 +3411,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721209</v>
+        <v>721232</v>
       </c>
       <c r="R26" t="n">
-        <v>6380333</v>
+        <v>6380313</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265473</v>
+        <v>127265475</v>
       </c>
       <c r="B27" t="n">
-        <v>98428</v>
+        <v>98473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,26 +3522,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3555,13 +3555,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721232</v>
+        <v>721209</v>
       </c>
       <c r="R27" t="n">
-        <v>6380313</v>
+        <v>6380333</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3835,54 +3835,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265548</v>
+        <v>127265486</v>
       </c>
       <c r="B30" t="n">
-        <v>99667</v>
+        <v>109277</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>174</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721578</v>
+        <v>721231</v>
       </c>
       <c r="R30" t="n">
-        <v>6380576</v>
+        <v>6380342</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3917,11 +3908,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3933,7 +3919,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3951,48 +3937,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265486</v>
+        <v>127265598</v>
       </c>
       <c r="B31" t="n">
-        <v>109277</v>
+        <v>98473</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721231</v>
+        <v>721557</v>
       </c>
       <c r="R31" t="n">
-        <v>6380342</v>
+        <v>6380422</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4035,7 +4030,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4164,10 +4159,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265598</v>
+        <v>127265548</v>
       </c>
       <c r="B33" t="n">
-        <v>98473</v>
+        <v>99667</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,31 +4170,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>174</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,13 +4203,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721557</v>
+        <v>721578</v>
       </c>
       <c r="R33" t="n">
-        <v>6380422</v>
+        <v>6380576</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4246,6 +4241,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127265541</v>
+        <v>127265612</v>
       </c>
       <c r="B37" t="n">
-        <v>98368</v>
+        <v>98487</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,34 +4615,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721546</v>
+        <v>721424</v>
       </c>
       <c r="R37" t="n">
-        <v>6380552</v>
+        <v>6380372</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,7 +4697,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4706,7 +4715,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265566</v>
+        <v>127265541</v>
       </c>
       <c r="B38" t="n">
         <v>98368</v>
@@ -4737,14 +4746,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721615</v>
+        <v>721546</v>
       </c>
       <c r="R38" t="n">
-        <v>6380615</v>
+        <v>6380552</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,7 +4799,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4808,7 +4817,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265582</v>
+        <v>127265566</v>
       </c>
       <c r="B39" t="n">
         <v>98368</v>
@@ -4836,26 +4845,17 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721601</v>
+        <v>721615</v>
       </c>
       <c r="R39" t="n">
-        <v>6380518</v>
+        <v>6380615</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265612</v>
+        <v>127265582</v>
       </c>
       <c r="B40" t="n">
-        <v>98487</v>
+        <v>98368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,21 +4930,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721424</v>
+        <v>721601</v>
       </c>
       <c r="R40" t="n">
-        <v>6380372</v>
+        <v>6380518</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5030,48 +5030,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127265579</v>
+        <v>127265623</v>
       </c>
       <c r="B41" t="n">
-        <v>106048</v>
+        <v>98428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721577</v>
+        <v>721199</v>
       </c>
       <c r="R41" t="n">
-        <v>6380550</v>
+        <v>6380248</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5132,7 +5141,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265545</v>
+        <v>127265579</v>
       </c>
       <c r="B42" t="n">
         <v>106048</v>
@@ -5163,14 +5172,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721560</v>
+        <v>721577</v>
       </c>
       <c r="R42" t="n">
-        <v>6380582</v>
+        <v>6380550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5216,7 +5225,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5234,57 +5243,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127265623</v>
+        <v>127265545</v>
       </c>
       <c r="B43" t="n">
-        <v>98428</v>
+        <v>106048</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721199</v>
+        <v>721560</v>
       </c>
       <c r="R43" t="n">
-        <v>6380248</v>
+        <v>6380582</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265571</v>
+        <v>127265515</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>98428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5356,26 +5356,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5385,17 +5385,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721594</v>
+        <v>721315</v>
       </c>
       <c r="R44" t="n">
-        <v>6380563</v>
+        <v>6380362</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5456,57 +5456,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265515</v>
+        <v>127265534</v>
       </c>
       <c r="B45" t="n">
-        <v>98428</v>
+        <v>109277</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721315</v>
+        <v>721493</v>
       </c>
       <c r="R45" t="n">
-        <v>6380362</v>
+        <v>6380446</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5567,45 +5558,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265534</v>
+        <v>127265571</v>
       </c>
       <c r="B46" t="n">
-        <v>109277</v>
+        <v>98368</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721493</v>
+        <v>721594</v>
       </c>
       <c r="R46" t="n">
-        <v>6380446</v>
+        <v>6380563</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6437,45 +6437,64 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B54" t="n">
-        <v>106048</v>
+        <v>43234</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R54" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6539,64 +6558,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B55" t="n">
-        <v>43234</v>
+        <v>106048</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R55" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265484</v>
+        <v>127265494</v>
       </c>
       <c r="B56" t="n">
-        <v>98368</v>
+        <v>98472</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6671,26 +6671,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721220</v>
+        <v>721247</v>
       </c>
       <c r="R56" t="n">
-        <v>6380355</v>
+        <v>6380342</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -6771,10 +6771,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265622</v>
+        <v>127265481</v>
       </c>
       <c r="B57" t="n">
-        <v>103906</v>
+        <v>109277</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,46 +6782,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721252</v>
+        <v>721220</v>
       </c>
       <c r="R57" t="n">
-        <v>6380274</v>
+        <v>6380355</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6984,10 +6975,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265494</v>
+        <v>127265484</v>
       </c>
       <c r="B59" t="n">
-        <v>98472</v>
+        <v>98368</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6995,26 +6986,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7028,10 +7019,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721247</v>
+        <v>721220</v>
       </c>
       <c r="R59" t="n">
-        <v>6380342</v>
+        <v>6380355</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7095,10 +7086,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265481</v>
+        <v>127265622</v>
       </c>
       <c r="B60" t="n">
-        <v>109277</v>
+        <v>103906</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7106,37 +7097,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721220</v>
+        <v>721252</v>
       </c>
       <c r="R60" t="n">
-        <v>6380355</v>
+        <v>6380274</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7197,54 +7197,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265474</v>
+        <v>127265505</v>
       </c>
       <c r="B61" t="n">
-        <v>98368</v>
+        <v>106048</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721232</v>
+        <v>721284</v>
       </c>
       <c r="R61" t="n">
-        <v>6380313</v>
+        <v>6380359</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7308,57 +7299,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265504</v>
+        <v>127265488</v>
       </c>
       <c r="B62" t="n">
-        <v>98368</v>
+        <v>106048</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721272</v>
+        <v>721231</v>
       </c>
       <c r="R62" t="n">
-        <v>6380356</v>
+        <v>6380342</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7419,37 +7401,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265546</v>
+        <v>127265533</v>
       </c>
       <c r="B63" t="n">
-        <v>98368</v>
+        <v>99201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7463,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721560</v>
+        <v>721484</v>
       </c>
       <c r="R63" t="n">
-        <v>6380582</v>
+        <v>6380450</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7512,7 +7494,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7530,10 +7512,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265617</v>
+        <v>127265495</v>
       </c>
       <c r="B64" t="n">
-        <v>98472</v>
+        <v>98428</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7541,26 +7523,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7568,24 +7550,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721357</v>
+        <v>721247</v>
       </c>
       <c r="R64" t="n">
-        <v>6380338</v>
+        <v>6380342</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7646,10 +7623,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265517</v>
+        <v>127265617</v>
       </c>
       <c r="B65" t="n">
-        <v>98428</v>
+        <v>98472</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7657,26 +7634,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7684,19 +7661,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721330</v>
+        <v>721357</v>
       </c>
       <c r="R65" t="n">
-        <v>6380365</v>
+        <v>6380338</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7757,48 +7739,57 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265505</v>
+        <v>127265517</v>
       </c>
       <c r="B66" t="n">
-        <v>106048</v>
+        <v>98428</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721284</v>
+        <v>721330</v>
       </c>
       <c r="R66" t="n">
-        <v>6380359</v>
+        <v>6380365</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7859,48 +7850,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265488</v>
+        <v>127265474</v>
       </c>
       <c r="B67" t="n">
-        <v>106048</v>
+        <v>98368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721231</v>
+        <v>721232</v>
       </c>
       <c r="R67" t="n">
-        <v>6380342</v>
+        <v>6380313</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7961,10 +7961,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265495</v>
+        <v>127265504</v>
       </c>
       <c r="B68" t="n">
-        <v>98428</v>
+        <v>98368</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7972,26 +7972,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721247</v>
+        <v>721272</v>
       </c>
       <c r="R68" t="n">
-        <v>6380342</v>
+        <v>6380356</v>
       </c>
       <c r="S68" t="n">
         <v>7</v>
@@ -8072,37 +8072,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265533</v>
+        <v>127265546</v>
       </c>
       <c r="B69" t="n">
-        <v>99201</v>
+        <v>98368</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222361</v>
+        <v>223591</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721484</v>
+        <v>721560</v>
       </c>
       <c r="R69" t="n">
-        <v>6380450</v>
+        <v>6380582</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127265476</v>
+        <v>127265525</v>
       </c>
       <c r="B70" t="n">
-        <v>98368</v>
+        <v>98428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,26 +8194,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8223,17 +8223,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>721209</v>
+        <v>721433</v>
       </c>
       <c r="R70" t="n">
-        <v>6380333</v>
+        <v>6380417</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8263,11 +8263,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8299,10 +8294,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127265525</v>
+        <v>127265476</v>
       </c>
       <c r="B71" t="n">
-        <v>98428</v>
+        <v>98368</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8310,26 +8305,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8339,17 +8334,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>721433</v>
+        <v>721209</v>
       </c>
       <c r="R71" t="n">
-        <v>6380417</v>
+        <v>6380333</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8379,6 +8374,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8739,45 +8739,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B75" t="n">
-        <v>109277</v>
+        <v>98473</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R75" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8841,54 +8850,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B76" t="n">
-        <v>98473</v>
+        <v>109277</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R76" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8952,48 +8952,57 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127265513</v>
+        <v>127265508</v>
       </c>
       <c r="B77" t="n">
-        <v>109277</v>
+        <v>98428</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721315</v>
+        <v>721307</v>
       </c>
       <c r="R77" t="n">
-        <v>6380362</v>
+        <v>6380360</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9054,57 +9063,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127265508</v>
+        <v>127265513</v>
       </c>
       <c r="B78" t="n">
-        <v>98428</v>
+        <v>109277</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721307</v>
+        <v>721315</v>
       </c>
       <c r="R78" t="n">
-        <v>6380360</v>
+        <v>6380362</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265491</v>
+        <v>127265493</v>
       </c>
       <c r="B80" t="n">
         <v>106048</v>
@@ -9326,10 +9326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R80" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S80" t="n">
         <v>7</v>
@@ -9393,57 +9393,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265489</v>
+        <v>127265491</v>
       </c>
       <c r="B81" t="n">
-        <v>98368</v>
+        <v>106048</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721231</v>
+        <v>721239</v>
       </c>
       <c r="R81" t="n">
-        <v>6380342</v>
+        <v>6380330</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9504,27 +9495,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265493</v>
+        <v>127265605</v>
       </c>
       <c r="B82" t="n">
-        <v>106048</v>
+        <v>109277</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9535,17 +9526,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R82" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9606,48 +9597,57 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127265605</v>
+        <v>127265489</v>
       </c>
       <c r="B83" t="n">
-        <v>109277</v>
+        <v>98368</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721466</v>
+        <v>721231</v>
       </c>
       <c r="R83" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265499</v>
+        <v>127265572</v>
       </c>
       <c r="B84" t="n">
-        <v>98368</v>
+        <v>98428</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9719,26 +9719,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9748,17 +9748,17 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721247</v>
+        <v>721594</v>
       </c>
       <c r="R84" t="n">
-        <v>6380342</v>
+        <v>6380563</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9819,54 +9819,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265572</v>
+        <v>127265549</v>
       </c>
       <c r="B85" t="n">
-        <v>98428</v>
+        <v>106048</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721594</v>
+        <v>721590</v>
       </c>
       <c r="R85" t="n">
-        <v>6380563</v>
+        <v>6380571</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9912,7 +9903,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9930,7 +9921,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265549</v>
+        <v>127265511</v>
       </c>
       <c r="B86" t="n">
         <v>106048</v>
@@ -9961,17 +9952,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721590</v>
+        <v>721315</v>
       </c>
       <c r="R86" t="n">
-        <v>6380571</v>
+        <v>6380362</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10014,7 +10005,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10032,48 +10023,57 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127265511</v>
+        <v>127265499</v>
       </c>
       <c r="B87" t="n">
-        <v>106048</v>
+        <v>98368</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>721315</v>
+        <v>721247</v>
       </c>
       <c r="R87" t="n">
-        <v>6380362</v>
+        <v>6380342</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10134,48 +10134,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127265519</v>
+        <v>127265483</v>
       </c>
       <c r="B88" t="n">
-        <v>98368</v>
+        <v>106048</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>721330</v>
+        <v>721220</v>
       </c>
       <c r="R88" t="n">
-        <v>6380365</v>
+        <v>6380355</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265500</v>
+        <v>127265519</v>
       </c>
       <c r="B89" t="n">
         <v>98368</v>
@@ -10264,29 +10264,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721263</v>
+        <v>721330</v>
       </c>
       <c r="R89" t="n">
-        <v>6380356</v>
+        <v>6380365</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10347,7 +10338,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265506</v>
+        <v>127265500</v>
       </c>
       <c r="B90" t="n">
         <v>98368</v>
@@ -10377,7 +10368,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10391,10 +10382,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721284</v>
+        <v>721263</v>
       </c>
       <c r="R90" t="n">
-        <v>6380359</v>
+        <v>6380356</v>
       </c>
       <c r="S90" t="n">
         <v>7</v>
@@ -10458,45 +10449,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127265483</v>
+        <v>127265506</v>
       </c>
       <c r="B91" t="n">
-        <v>106048</v>
+        <v>98368</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>721220</v>
+        <v>721284</v>
       </c>
       <c r="R91" t="n">
-        <v>6380355</v>
+        <v>6380359</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2432,45 +2432,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265600</v>
+        <v>127265587</v>
       </c>
       <c r="B17" t="n">
-        <v>109277</v>
+        <v>105488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721547</v>
+        <v>721591</v>
       </c>
       <c r="R17" t="n">
-        <v>6380409</v>
+        <v>6380497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2543,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265532</v>
+        <v>127265540</v>
       </c>
       <c r="B18" t="n">
         <v>106048</v>
@@ -2569,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721484</v>
+        <v>721546</v>
       </c>
       <c r="R18" t="n">
-        <v>6380450</v>
+        <v>6380552</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,7 +2627,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2636,48 +2645,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265540</v>
+        <v>127265479</v>
       </c>
       <c r="B19" t="n">
-        <v>106048</v>
+        <v>98368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721546</v>
+        <v>721212</v>
       </c>
       <c r="R19" t="n">
-        <v>6380552</v>
+        <v>6380346</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2720,7 +2738,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2738,10 +2756,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265479</v>
+        <v>127265530</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,26 +2767,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2778,17 +2796,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721212</v>
+        <v>721463</v>
       </c>
       <c r="R20" t="n">
-        <v>6380346</v>
+        <v>6380440</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2849,54 +2867,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265530</v>
+        <v>127265600</v>
       </c>
       <c r="B21" t="n">
-        <v>98486</v>
+        <v>109277</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721463</v>
+        <v>721547</v>
       </c>
       <c r="R21" t="n">
-        <v>6380440</v>
+        <v>6380409</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,54 +2969,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265587</v>
+        <v>127265532</v>
       </c>
       <c r="B22" t="n">
-        <v>105488</v>
+        <v>106048</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721591</v>
+        <v>721484</v>
       </c>
       <c r="R22" t="n">
-        <v>6380497</v>
+        <v>6380450</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,48 +3071,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265496</v>
+        <v>127265610</v>
       </c>
       <c r="B23" t="n">
-        <v>109277</v>
+        <v>98368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R23" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3173,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127265610</v>
+        <v>127265590</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98486</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,21 +3193,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3217,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721466</v>
+        <v>721580</v>
       </c>
       <c r="R24" t="n">
-        <v>6380394</v>
+        <v>6380472</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,6 +3264,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3266,7 +3280,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3284,57 +3298,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265590</v>
+        <v>127265496</v>
       </c>
       <c r="B25" t="n">
-        <v>98486</v>
+        <v>109277</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721580</v>
+        <v>721247</v>
       </c>
       <c r="R25" t="n">
-        <v>6380472</v>
+        <v>6380342</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3366,11 +3371,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3835,45 +3835,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265486</v>
+        <v>127265548</v>
       </c>
       <c r="B30" t="n">
-        <v>109277</v>
+        <v>99667</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>174</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721231</v>
+        <v>721578</v>
       </c>
       <c r="R30" t="n">
-        <v>6380342</v>
+        <v>6380576</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3908,6 +3917,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3919,7 +3933,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4159,54 +4173,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265548</v>
+        <v>127265486</v>
       </c>
       <c r="B33" t="n">
-        <v>99667</v>
+        <v>109277</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>174</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721578</v>
+        <v>721231</v>
       </c>
       <c r="R33" t="n">
-        <v>6380576</v>
+        <v>6380342</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4241,11 +4246,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -6771,10 +6771,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265481</v>
+        <v>127265622</v>
       </c>
       <c r="B57" t="n">
-        <v>109277</v>
+        <v>103906</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,37 +6782,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721220</v>
+        <v>721252</v>
       </c>
       <c r="R57" t="n">
-        <v>6380355</v>
+        <v>6380274</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6873,27 +6882,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265471</v>
+        <v>127265481</v>
       </c>
       <c r="B58" t="n">
-        <v>106048</v>
+        <v>109277</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6908,10 +6917,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721232</v>
+        <v>721220</v>
       </c>
       <c r="R58" t="n">
-        <v>6380313</v>
+        <v>6380355</v>
       </c>
       <c r="S58" t="n">
         <v>7</v>
@@ -6975,54 +6984,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265484</v>
+        <v>127265471</v>
       </c>
       <c r="B59" t="n">
-        <v>98368</v>
+        <v>106048</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R59" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7086,37 +7086,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265622</v>
+        <v>127265484</v>
       </c>
       <c r="B60" t="n">
-        <v>103906</v>
+        <v>98368</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220164</v>
+        <v>223591</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7126,17 +7126,17 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721252</v>
+        <v>721220</v>
       </c>
       <c r="R60" t="n">
-        <v>6380274</v>
+        <v>6380355</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7197,45 +7197,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265505</v>
+        <v>127265495</v>
       </c>
       <c r="B61" t="n">
-        <v>106048</v>
+        <v>98428</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721284</v>
+        <v>721247</v>
       </c>
       <c r="R61" t="n">
-        <v>6380359</v>
+        <v>6380342</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7299,48 +7308,62 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265488</v>
+        <v>127265617</v>
       </c>
       <c r="B62" t="n">
-        <v>106048</v>
+        <v>98472</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721231</v>
+        <v>721357</v>
       </c>
       <c r="R62" t="n">
-        <v>6380342</v>
+        <v>6380338</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7401,37 +7424,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265533</v>
+        <v>127265517</v>
       </c>
       <c r="B63" t="n">
-        <v>99201</v>
+        <v>98428</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7445,10 +7468,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721484</v>
+        <v>721330</v>
       </c>
       <c r="R63" t="n">
-        <v>6380450</v>
+        <v>6380365</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7512,54 +7535,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265495</v>
+        <v>127265505</v>
       </c>
       <c r="B64" t="n">
-        <v>98428</v>
+        <v>106048</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721247</v>
+        <v>721284</v>
       </c>
       <c r="R64" t="n">
-        <v>6380342</v>
+        <v>6380359</v>
       </c>
       <c r="S64" t="n">
         <v>7</v>
@@ -7623,62 +7637,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265617</v>
+        <v>127265488</v>
       </c>
       <c r="B65" t="n">
-        <v>98472</v>
+        <v>106048</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721357</v>
+        <v>721231</v>
       </c>
       <c r="R65" t="n">
-        <v>6380338</v>
+        <v>6380342</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7739,10 +7739,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265517</v>
+        <v>127265474</v>
       </c>
       <c r="B66" t="n">
-        <v>98428</v>
+        <v>98368</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7750,26 +7750,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7779,17 +7779,17 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721330</v>
+        <v>721232</v>
       </c>
       <c r="R66" t="n">
-        <v>6380365</v>
+        <v>6380313</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265474</v>
+        <v>127265504</v>
       </c>
       <c r="B67" t="n">
         <v>98368</v>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721232</v>
+        <v>721272</v>
       </c>
       <c r="R67" t="n">
-        <v>6380313</v>
+        <v>6380356</v>
       </c>
       <c r="S67" t="n">
         <v>7</v>
@@ -7961,7 +7961,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265504</v>
+        <v>127265546</v>
       </c>
       <c r="B68" t="n">
         <v>98368</v>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8001,17 +8001,17 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721272</v>
+        <v>721560</v>
       </c>
       <c r="R68" t="n">
-        <v>6380356</v>
+        <v>6380582</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8072,37 +8072,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265546</v>
+        <v>127265533</v>
       </c>
       <c r="B69" t="n">
-        <v>98368</v>
+        <v>99201</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721560</v>
+        <v>721484</v>
       </c>
       <c r="R69" t="n">
-        <v>6380582</v>
+        <v>6380450</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265528</v>
+        <v>127265586</v>
       </c>
       <c r="B72" t="n">
-        <v>98368</v>
+        <v>98473</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721460</v>
+        <v>721591</v>
       </c>
       <c r="R72" t="n">
-        <v>6380438</v>
+        <v>6380497</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8521,54 +8521,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265586</v>
+        <v>127265526</v>
       </c>
       <c r="B73" t="n">
-        <v>98473</v>
+        <v>109277</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721591</v>
+        <v>721433</v>
       </c>
       <c r="R73" t="n">
-        <v>6380497</v>
+        <v>6380417</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8601,6 +8592,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8632,45 +8628,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127265526</v>
+        <v>127265528</v>
       </c>
       <c r="B74" t="n">
-        <v>109277</v>
+        <v>98368</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>721433</v>
+        <v>721460</v>
       </c>
       <c r="R74" t="n">
-        <v>6380417</v>
+        <v>6380438</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8703,11 +8708,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265497</v>
+        <v>127265587</v>
       </c>
       <c r="B14" t="n">
-        <v>98473</v>
+        <v>105488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,26 +2110,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2139,17 +2139,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721247</v>
+        <v>721591</v>
       </c>
       <c r="R14" t="n">
-        <v>6380342</v>
+        <v>6380497</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265518</v>
+        <v>127265479</v>
       </c>
       <c r="B15" t="n">
-        <v>98473</v>
+        <v>98368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,26 +2221,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2250,17 +2250,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721330</v>
+        <v>721212</v>
       </c>
       <c r="R15" t="n">
-        <v>6380365</v>
+        <v>6380346</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265492</v>
+        <v>127265530</v>
       </c>
       <c r="B16" t="n">
-        <v>98473</v>
+        <v>98486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721239</v>
+        <v>721463</v>
       </c>
       <c r="R16" t="n">
-        <v>6380330</v>
+        <v>6380440</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2432,54 +2432,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265587</v>
+        <v>127265600</v>
       </c>
       <c r="B17" t="n">
-        <v>105488</v>
+        <v>109277</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721591</v>
+        <v>721547</v>
       </c>
       <c r="R17" t="n">
-        <v>6380497</v>
+        <v>6380409</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2543,7 +2534,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265540</v>
+        <v>127265532</v>
       </c>
       <c r="B18" t="n">
         <v>106048</v>
@@ -2578,10 +2569,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721546</v>
+        <v>721484</v>
       </c>
       <c r="R18" t="n">
-        <v>6380552</v>
+        <v>6380450</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2627,7 +2618,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2645,57 +2636,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265479</v>
+        <v>127265540</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>106048</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721212</v>
+        <v>721546</v>
       </c>
       <c r="R19" t="n">
-        <v>6380346</v>
+        <v>6380552</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2738,7 +2720,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2756,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265530</v>
+        <v>127265497</v>
       </c>
       <c r="B20" t="n">
-        <v>98486</v>
+        <v>98473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2767,26 +2749,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2796,17 +2778,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721463</v>
+        <v>721247</v>
       </c>
       <c r="R20" t="n">
-        <v>6380440</v>
+        <v>6380342</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2867,45 +2849,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265600</v>
+        <v>127265518</v>
       </c>
       <c r="B21" t="n">
-        <v>109277</v>
+        <v>98473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721547</v>
+        <v>721330</v>
       </c>
       <c r="R21" t="n">
-        <v>6380409</v>
+        <v>6380365</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,48 +2960,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265532</v>
+        <v>127265492</v>
       </c>
       <c r="B22" t="n">
-        <v>106048</v>
+        <v>98473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721484</v>
+        <v>721239</v>
       </c>
       <c r="R22" t="n">
-        <v>6380450</v>
+        <v>6380330</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3071,57 +3071,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265610</v>
+        <v>127265496</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>109277</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721466</v>
+        <v>721247</v>
       </c>
       <c r="R23" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3298,48 +3289,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265496</v>
+        <v>127265610</v>
       </c>
       <c r="B25" t="n">
-        <v>109277</v>
+        <v>98368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R25" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3400,54 +3400,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265473</v>
+        <v>127265503</v>
       </c>
       <c r="B26" t="n">
-        <v>98428</v>
+        <v>106048</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721232</v>
+        <v>721272</v>
       </c>
       <c r="R26" t="n">
-        <v>6380313</v>
+        <v>6380356</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3511,10 +3502,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265475</v>
+        <v>127265624</v>
       </c>
       <c r="B27" t="n">
-        <v>98473</v>
+        <v>98368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,21 +3513,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3551,14 +3542,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721209</v>
+        <v>721199</v>
       </c>
       <c r="R27" t="n">
-        <v>6380333</v>
+        <v>6380248</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3622,45 +3613,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265503</v>
+        <v>127265473</v>
       </c>
       <c r="B28" t="n">
-        <v>106048</v>
+        <v>98428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721272</v>
+        <v>721232</v>
       </c>
       <c r="R28" t="n">
-        <v>6380356</v>
+        <v>6380313</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265624</v>
+        <v>127265475</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>98473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3735,21 +3735,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721199</v>
+        <v>721209</v>
       </c>
       <c r="R29" t="n">
-        <v>6380248</v>
+        <v>6380333</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3951,57 +3951,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265598</v>
+        <v>127265486</v>
       </c>
       <c r="B31" t="n">
-        <v>98473</v>
+        <v>109277</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721557</v>
+        <v>721231</v>
       </c>
       <c r="R31" t="n">
-        <v>6380422</v>
+        <v>6380342</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4044,7 +4035,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4062,7 +4053,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265606</v>
+        <v>127265598</v>
       </c>
       <c r="B32" t="n">
         <v>98473</v>
@@ -4092,7 +4083,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4106,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721475</v>
+        <v>721557</v>
       </c>
       <c r="R32" t="n">
-        <v>6380396</v>
+        <v>6380422</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4155,7 +4146,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4173,48 +4164,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265486</v>
+        <v>127265606</v>
       </c>
       <c r="B33" t="n">
-        <v>109277</v>
+        <v>98473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721231</v>
+        <v>721475</v>
       </c>
       <c r="R33" t="n">
-        <v>6380342</v>
+        <v>6380396</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4386,54 +4386,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265584</v>
+        <v>127265594</v>
       </c>
       <c r="B35" t="n">
-        <v>98473</v>
+        <v>109277</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721601</v>
+        <v>721572</v>
       </c>
       <c r="R35" t="n">
-        <v>6380518</v>
+        <v>6380434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,6 +4457,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,45 +4493,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265594</v>
+        <v>127265584</v>
       </c>
       <c r="B36" t="n">
-        <v>109277</v>
+        <v>98473</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721572</v>
+        <v>721601</v>
       </c>
       <c r="R36" t="n">
-        <v>6380434</v>
+        <v>6380518</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,11 +4573,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,7 +4715,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265541</v>
+        <v>127265566</v>
       </c>
       <c r="B38" t="n">
         <v>98368</v>
@@ -4746,14 +4746,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721546</v>
+        <v>721615</v>
       </c>
       <c r="R38" t="n">
-        <v>6380552</v>
+        <v>6380615</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265566</v>
+        <v>127265582</v>
       </c>
       <c r="B39" t="n">
         <v>98368</v>
@@ -4845,17 +4845,26 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721615</v>
+        <v>721601</v>
       </c>
       <c r="R39" t="n">
-        <v>6380615</v>
+        <v>6380518</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4901,7 +4910,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4919,7 +4928,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265582</v>
+        <v>127265541</v>
       </c>
       <c r="B40" t="n">
         <v>98368</v>
@@ -4947,26 +4956,17 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721601</v>
+        <v>721546</v>
       </c>
       <c r="R40" t="n">
-        <v>6380518</v>
+        <v>6380552</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6660,54 +6660,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265494</v>
+        <v>127265481</v>
       </c>
       <c r="B56" t="n">
-        <v>98472</v>
+        <v>109277</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721247</v>
+        <v>721220</v>
       </c>
       <c r="R56" t="n">
-        <v>6380342</v>
+        <v>6380355</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -6882,27 +6873,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265481</v>
+        <v>127265471</v>
       </c>
       <c r="B58" t="n">
-        <v>109277</v>
+        <v>106048</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6917,10 +6908,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R58" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S58" t="n">
         <v>7</v>
@@ -6984,45 +6975,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265471</v>
+        <v>127265494</v>
       </c>
       <c r="B59" t="n">
-        <v>106048</v>
+        <v>98472</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721232</v>
+        <v>721247</v>
       </c>
       <c r="R59" t="n">
-        <v>6380313</v>
+        <v>6380342</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7197,54 +7197,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265495</v>
+        <v>127265505</v>
       </c>
       <c r="B61" t="n">
-        <v>98428</v>
+        <v>106048</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721247</v>
+        <v>721284</v>
       </c>
       <c r="R61" t="n">
-        <v>6380342</v>
+        <v>6380359</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7308,62 +7299,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265617</v>
+        <v>127265488</v>
       </c>
       <c r="B62" t="n">
-        <v>98472</v>
+        <v>106048</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721357</v>
+        <v>721231</v>
       </c>
       <c r="R62" t="n">
-        <v>6380338</v>
+        <v>6380342</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7424,10 +7401,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265517</v>
+        <v>127265504</v>
       </c>
       <c r="B63" t="n">
-        <v>98428</v>
+        <v>98368</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7435,26 +7412,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7464,17 +7441,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721330</v>
+        <v>721272</v>
       </c>
       <c r="R63" t="n">
-        <v>6380365</v>
+        <v>6380356</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7535,45 +7512,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265505</v>
+        <v>127265474</v>
       </c>
       <c r="B64" t="n">
-        <v>106048</v>
+        <v>98368</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721284</v>
+        <v>721232</v>
       </c>
       <c r="R64" t="n">
-        <v>6380359</v>
+        <v>6380313</v>
       </c>
       <c r="S64" t="n">
         <v>7</v>
@@ -7637,48 +7623,57 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265488</v>
+        <v>127265546</v>
       </c>
       <c r="B65" t="n">
-        <v>106048</v>
+        <v>98368</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721231</v>
+        <v>721560</v>
       </c>
       <c r="R65" t="n">
-        <v>6380342</v>
+        <v>6380582</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7721,7 +7716,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7739,37 +7734,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265474</v>
+        <v>127265533</v>
       </c>
       <c r="B66" t="n">
-        <v>98368</v>
+        <v>99201</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7779,17 +7774,17 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721232</v>
+        <v>721484</v>
       </c>
       <c r="R66" t="n">
-        <v>6380313</v>
+        <v>6380450</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7850,10 +7845,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265504</v>
+        <v>127265495</v>
       </c>
       <c r="B67" t="n">
-        <v>98368</v>
+        <v>98428</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7861,26 +7856,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7894,10 +7889,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721272</v>
+        <v>721247</v>
       </c>
       <c r="R67" t="n">
-        <v>6380356</v>
+        <v>6380342</v>
       </c>
       <c r="S67" t="n">
         <v>7</v>
@@ -7961,10 +7956,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265546</v>
+        <v>127265617</v>
       </c>
       <c r="B68" t="n">
-        <v>98368</v>
+        <v>98472</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7972,21 +7967,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7999,19 +7994,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721560</v>
+        <v>721357</v>
       </c>
       <c r="R68" t="n">
-        <v>6380582</v>
+        <v>6380338</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8072,37 +8072,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265533</v>
+        <v>127265517</v>
       </c>
       <c r="B69" t="n">
-        <v>99201</v>
+        <v>98428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721484</v>
+        <v>721330</v>
       </c>
       <c r="R69" t="n">
-        <v>6380450</v>
+        <v>6380365</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265586</v>
+        <v>127265528</v>
       </c>
       <c r="B72" t="n">
-        <v>98473</v>
+        <v>98368</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721591</v>
+        <v>721460</v>
       </c>
       <c r="R72" t="n">
-        <v>6380497</v>
+        <v>6380438</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8628,10 +8628,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127265528</v>
+        <v>127265586</v>
       </c>
       <c r="B74" t="n">
-        <v>98368</v>
+        <v>98473</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8639,21 +8639,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8668,14 +8668,14 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>721460</v>
+        <v>721591</v>
       </c>
       <c r="R74" t="n">
-        <v>6380438</v>
+        <v>6380497</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8739,54 +8739,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B75" t="n">
-        <v>98473</v>
+        <v>109277</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R75" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8850,45 +8841,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B76" t="n">
-        <v>109277</v>
+        <v>98473</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R76" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265493</v>
+        <v>127265491</v>
       </c>
       <c r="B80" t="n">
         <v>106048</v>
@@ -9326,10 +9326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721247</v>
+        <v>721239</v>
       </c>
       <c r="R80" t="n">
-        <v>6380342</v>
+        <v>6380330</v>
       </c>
       <c r="S80" t="n">
         <v>7</v>
@@ -9393,7 +9393,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265491</v>
+        <v>127265493</v>
       </c>
       <c r="B81" t="n">
         <v>106048</v>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R81" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S81" t="n">
         <v>7</v>
@@ -9708,57 +9708,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265572</v>
+        <v>127265511</v>
       </c>
       <c r="B84" t="n">
-        <v>98428</v>
+        <v>106048</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721594</v>
+        <v>721315</v>
       </c>
       <c r="R84" t="n">
-        <v>6380563</v>
+        <v>6380362</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9921,48 +9912,57 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265511</v>
+        <v>127265572</v>
       </c>
       <c r="B86" t="n">
-        <v>106048</v>
+        <v>98428</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R86" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265519</v>
+        <v>127265500</v>
       </c>
       <c r="B89" t="n">
         <v>98368</v>
@@ -10264,20 +10264,29 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721330</v>
+        <v>721263</v>
       </c>
       <c r="R89" t="n">
-        <v>6380365</v>
+        <v>6380356</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10338,7 +10347,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265500</v>
+        <v>127265519</v>
       </c>
       <c r="B90" t="n">
         <v>98368</v>
@@ -10366,29 +10375,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721263</v>
+        <v>721330</v>
       </c>
       <c r="R90" t="n">
-        <v>6380356</v>
+        <v>6380365</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265587</v>
+        <v>127265479</v>
       </c>
       <c r="B14" t="n">
-        <v>105488</v>
+        <v>98374</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,26 +2110,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2139,17 +2139,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721591</v>
+        <v>721212</v>
       </c>
       <c r="R14" t="n">
-        <v>6380497</v>
+        <v>6380346</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265479</v>
+        <v>127265530</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>98492</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,26 +2221,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2250,17 +2250,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721212</v>
+        <v>721463</v>
       </c>
       <c r="R15" t="n">
-        <v>6380346</v>
+        <v>6380440</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2321,54 +2321,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265530</v>
+        <v>127265600</v>
       </c>
       <c r="B16" t="n">
-        <v>98486</v>
+        <v>109283</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721463</v>
+        <v>721547</v>
       </c>
       <c r="R16" t="n">
-        <v>6380440</v>
+        <v>6380409</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2432,45 +2423,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265600</v>
+        <v>127265587</v>
       </c>
       <c r="B17" t="n">
-        <v>109277</v>
+        <v>105494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721547</v>
+        <v>721591</v>
       </c>
       <c r="R17" t="n">
-        <v>6380409</v>
+        <v>6380497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,48 +2534,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265532</v>
+        <v>127265497</v>
       </c>
       <c r="B18" t="n">
-        <v>106048</v>
+        <v>98479</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721484</v>
+        <v>721247</v>
       </c>
       <c r="R18" t="n">
-        <v>6380450</v>
+        <v>6380342</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2636,45 +2645,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265540</v>
+        <v>127265518</v>
       </c>
       <c r="B19" t="n">
-        <v>106048</v>
+        <v>98479</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721546</v>
+        <v>721330</v>
       </c>
       <c r="R19" t="n">
-        <v>6380552</v>
+        <v>6380365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,7 +2738,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2738,10 +2756,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265497</v>
+        <v>127265492</v>
       </c>
       <c r="B20" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2768,7 +2786,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2782,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721247</v>
+        <v>721239</v>
       </c>
       <c r="R20" t="n">
-        <v>6380342</v>
+        <v>6380330</v>
       </c>
       <c r="S20" t="n">
         <v>7</v>
@@ -2849,54 +2867,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265518</v>
+        <v>127265532</v>
       </c>
       <c r="B21" t="n">
-        <v>98473</v>
+        <v>106054</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721330</v>
+        <v>721484</v>
       </c>
       <c r="R21" t="n">
-        <v>6380365</v>
+        <v>6380450</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,57 +2969,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265492</v>
+        <v>127265540</v>
       </c>
       <c r="B22" t="n">
-        <v>98473</v>
+        <v>106054</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721239</v>
+        <v>721546</v>
       </c>
       <c r="R22" t="n">
-        <v>6380330</v>
+        <v>6380552</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
         <v>127265496</v>
       </c>
       <c r="B23" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127265590</v>
+        <v>127265610</v>
       </c>
       <c r="B24" t="n">
-        <v>98486</v>
+        <v>98374</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,21 +3184,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223621</v>
+        <v>223591</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721580</v>
+        <v>721466</v>
       </c>
       <c r="R24" t="n">
-        <v>6380472</v>
+        <v>6380394</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,11 +3255,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3271,7 +3266,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3289,10 +3284,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265610</v>
+        <v>127265590</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>98492</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3300,21 +3295,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3333,10 +3328,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721466</v>
+        <v>721580</v>
       </c>
       <c r="R25" t="n">
-        <v>6380394</v>
+        <v>6380472</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,6 +3366,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3400,45 +3400,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265503</v>
+        <v>127265473</v>
       </c>
       <c r="B26" t="n">
-        <v>106048</v>
+        <v>98434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721272</v>
+        <v>721232</v>
       </c>
       <c r="R26" t="n">
-        <v>6380356</v>
+        <v>6380313</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3502,10 +3511,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265624</v>
+        <v>127265475</v>
       </c>
       <c r="B27" t="n">
-        <v>98368</v>
+        <v>98479</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3513,21 +3522,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3542,14 +3551,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721199</v>
+        <v>721209</v>
       </c>
       <c r="R27" t="n">
-        <v>6380248</v>
+        <v>6380333</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3613,54 +3622,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265473</v>
+        <v>127265503</v>
       </c>
       <c r="B28" t="n">
-        <v>98428</v>
+        <v>106054</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721232</v>
+        <v>721272</v>
       </c>
       <c r="R28" t="n">
-        <v>6380313</v>
+        <v>6380356</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265475</v>
+        <v>127265624</v>
       </c>
       <c r="B29" t="n">
-        <v>98473</v>
+        <v>98374</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3735,21 +3735,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721209</v>
+        <v>721199</v>
       </c>
       <c r="R29" t="n">
-        <v>6380333</v>
+        <v>6380248</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3838,7 +3838,7 @@
         <v>127265548</v>
       </c>
       <c r="B30" t="n">
-        <v>99667</v>
+        <v>99673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>127265486</v>
       </c>
       <c r="B31" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>127265598</v>
       </c>
       <c r="B32" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>127265606</v>
       </c>
       <c r="B33" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>127265594</v>
       </c>
       <c r="B35" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>127265584</v>
       </c>
       <c r="B36" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>127265612</v>
       </c>
       <c r="B37" t="n">
-        <v>98487</v>
+        <v>98493</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265566</v>
+        <v>127265541</v>
       </c>
       <c r="B38" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4746,14 +4746,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721615</v>
+        <v>721546</v>
       </c>
       <c r="R38" t="n">
-        <v>6380615</v>
+        <v>6380552</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265582</v>
+        <v>127265566</v>
       </c>
       <c r="B39" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4845,26 +4845,17 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721601</v>
+        <v>721615</v>
       </c>
       <c r="R39" t="n">
-        <v>6380518</v>
+        <v>6380615</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4910,7 +4901,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4928,10 +4919,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265541</v>
+        <v>127265582</v>
       </c>
       <c r="B40" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4956,17 +4947,26 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721546</v>
+        <v>721601</v>
       </c>
       <c r="R40" t="n">
-        <v>6380552</v>
+        <v>6380518</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5033,7 +5033,7 @@
         <v>127265623</v>
       </c>
       <c r="B41" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>127265579</v>
       </c>
       <c r="B42" t="n">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>127265545</v>
       </c>
       <c r="B43" t="n">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>127265515</v>
       </c>
       <c r="B44" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>127265534</v>
       </c>
       <c r="B45" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>127265571</v>
       </c>
       <c r="B46" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>127265478</v>
       </c>
       <c r="B47" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>127265626</v>
       </c>
       <c r="B48" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>127265597</v>
       </c>
       <c r="B49" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>127265593</v>
       </c>
       <c r="B50" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>127265472</v>
       </c>
       <c r="B51" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>127265628</v>
       </c>
       <c r="B52" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>127265507</v>
       </c>
       <c r="B53" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>127265583</v>
       </c>
       <c r="B55" t="n">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>127265481</v>
       </c>
       <c r="B56" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>127265622</v>
       </c>
       <c r="B57" t="n">
-        <v>103906</v>
+        <v>103912</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>127265471</v>
       </c>
       <c r="B58" t="n">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>127265494</v>
       </c>
       <c r="B59" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>127265484</v>
       </c>
       <c r="B60" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7197,45 +7197,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265505</v>
+        <v>127265495</v>
       </c>
       <c r="B61" t="n">
-        <v>106048</v>
+        <v>98434</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721284</v>
+        <v>721247</v>
       </c>
       <c r="R61" t="n">
-        <v>6380359</v>
+        <v>6380342</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7299,48 +7308,62 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265488</v>
+        <v>127265617</v>
       </c>
       <c r="B62" t="n">
-        <v>106048</v>
+        <v>98478</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721231</v>
+        <v>721357</v>
       </c>
       <c r="R62" t="n">
-        <v>6380342</v>
+        <v>6380338</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7401,10 +7424,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265504</v>
+        <v>127265517</v>
       </c>
       <c r="B63" t="n">
-        <v>98368</v>
+        <v>98434</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7412,26 +7435,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7441,17 +7464,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721272</v>
+        <v>721330</v>
       </c>
       <c r="R63" t="n">
-        <v>6380356</v>
+        <v>6380365</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7512,37 +7535,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265474</v>
+        <v>127265533</v>
       </c>
       <c r="B64" t="n">
-        <v>98368</v>
+        <v>99207</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7552,17 +7575,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721232</v>
+        <v>721484</v>
       </c>
       <c r="R64" t="n">
-        <v>6380313</v>
+        <v>6380450</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7623,57 +7646,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265546</v>
+        <v>127265505</v>
       </c>
       <c r="B65" t="n">
-        <v>98368</v>
+        <v>106054</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721560</v>
+        <v>721284</v>
       </c>
       <c r="R65" t="n">
-        <v>6380582</v>
+        <v>6380359</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7716,7 +7730,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7734,27 +7748,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265533</v>
+        <v>127265488</v>
       </c>
       <c r="B66" t="n">
-        <v>99201</v>
+        <v>106054</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222361</v>
+        <v>220785</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7762,29 +7776,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721484</v>
+        <v>721231</v>
       </c>
       <c r="R66" t="n">
-        <v>6380450</v>
+        <v>6380342</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7845,10 +7850,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265495</v>
+        <v>127265474</v>
       </c>
       <c r="B67" t="n">
-        <v>98428</v>
+        <v>98374</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7856,26 +7861,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7889,10 +7894,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721247</v>
+        <v>721232</v>
       </c>
       <c r="R67" t="n">
-        <v>6380342</v>
+        <v>6380313</v>
       </c>
       <c r="S67" t="n">
         <v>7</v>
@@ -7956,10 +7961,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265617</v>
+        <v>127265504</v>
       </c>
       <c r="B68" t="n">
-        <v>98472</v>
+        <v>98374</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7967,26 +7972,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7994,24 +7999,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721357</v>
+        <v>721272</v>
       </c>
       <c r="R68" t="n">
-        <v>6380338</v>
+        <v>6380356</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8072,10 +8072,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265517</v>
+        <v>127265546</v>
       </c>
       <c r="B69" t="n">
-        <v>98428</v>
+        <v>98374</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8083,26 +8083,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721330</v>
+        <v>721560</v>
       </c>
       <c r="R69" t="n">
-        <v>6380365</v>
+        <v>6380582</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8186,7 +8186,7 @@
         <v>127265525</v>
       </c>
       <c r="B70" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>127265476</v>
       </c>
       <c r="B71" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,54 +8410,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265528</v>
+        <v>127265526</v>
       </c>
       <c r="B72" t="n">
-        <v>98368</v>
+        <v>109283</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721460</v>
+        <v>721433</v>
       </c>
       <c r="R72" t="n">
-        <v>6380438</v>
+        <v>6380417</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8490,6 +8481,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8521,45 +8517,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265526</v>
+        <v>127265586</v>
       </c>
       <c r="B73" t="n">
-        <v>109277</v>
+        <v>98479</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721433</v>
+        <v>721591</v>
       </c>
       <c r="R73" t="n">
-        <v>6380417</v>
+        <v>6380497</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8592,11 +8597,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8628,10 +8628,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127265586</v>
+        <v>127265528</v>
       </c>
       <c r="B74" t="n">
-        <v>98473</v>
+        <v>98374</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8639,21 +8639,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8668,14 +8668,14 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>721591</v>
+        <v>721460</v>
       </c>
       <c r="R74" t="n">
-        <v>6380497</v>
+        <v>6380438</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
         <v>127265588</v>
       </c>
       <c r="B75" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>127265535</v>
       </c>
       <c r="B76" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8952,57 +8952,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127265508</v>
+        <v>127265513</v>
       </c>
       <c r="B77" t="n">
-        <v>98428</v>
+        <v>109283</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721307</v>
+        <v>721315</v>
       </c>
       <c r="R77" t="n">
-        <v>6380360</v>
+        <v>6380362</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9063,48 +9054,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127265513</v>
+        <v>127265508</v>
       </c>
       <c r="B78" t="n">
-        <v>109277</v>
+        <v>98434</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721315</v>
+        <v>721307</v>
       </c>
       <c r="R78" t="n">
-        <v>6380362</v>
+        <v>6380360</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9291,10 +9291,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265491</v>
+        <v>127265493</v>
       </c>
       <c r="B80" t="n">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9326,10 +9326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R80" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S80" t="n">
         <v>7</v>
@@ -9393,10 +9393,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265493</v>
+        <v>127265491</v>
       </c>
       <c r="B81" t="n">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721247</v>
+        <v>721239</v>
       </c>
       <c r="R81" t="n">
-        <v>6380342</v>
+        <v>6380330</v>
       </c>
       <c r="S81" t="n">
         <v>7</v>
@@ -9495,48 +9495,57 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265605</v>
+        <v>127265489</v>
       </c>
       <c r="B82" t="n">
-        <v>109277</v>
+        <v>98374</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721466</v>
+        <v>721231</v>
       </c>
       <c r="R82" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9597,57 +9606,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127265489</v>
+        <v>127265605</v>
       </c>
       <c r="B83" t="n">
-        <v>98368</v>
+        <v>109283</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721231</v>
+        <v>721466</v>
       </c>
       <c r="R83" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9708,48 +9708,57 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265511</v>
+        <v>127265572</v>
       </c>
       <c r="B84" t="n">
-        <v>106048</v>
+        <v>98434</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R84" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9813,7 +9822,7 @@
         <v>127265549</v>
       </c>
       <c r="B85" t="n">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9912,57 +9921,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265572</v>
+        <v>127265511</v>
       </c>
       <c r="B86" t="n">
-        <v>98428</v>
+        <v>106054</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721594</v>
+        <v>721315</v>
       </c>
       <c r="R86" t="n">
-        <v>6380563</v>
+        <v>6380362</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>127265499</v>
       </c>
       <c r="B87" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>127265483</v>
       </c>
       <c r="B88" t="n">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265500</v>
+        <v>127265519</v>
       </c>
       <c r="B89" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10264,29 +10264,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721263</v>
+        <v>721330</v>
       </c>
       <c r="R89" t="n">
-        <v>6380356</v>
+        <v>6380365</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10347,10 +10338,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265519</v>
+        <v>127265500</v>
       </c>
       <c r="B90" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10375,20 +10366,29 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721330</v>
+        <v>721263</v>
       </c>
       <c r="R90" t="n">
-        <v>6380365</v>
+        <v>6380356</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>127265506</v>
       </c>
       <c r="B91" t="n">
-        <v>98368</v>
+        <v>98374</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,57 +2099,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265479</v>
+        <v>127265532</v>
       </c>
       <c r="B14" t="n">
-        <v>98374</v>
+        <v>106057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721212</v>
+        <v>721484</v>
       </c>
       <c r="R14" t="n">
-        <v>6380346</v>
+        <v>6380450</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265530</v>
+        <v>127265587</v>
       </c>
       <c r="B15" t="n">
-        <v>98492</v>
+        <v>105497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,21 +2212,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223621</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2250,14 +2241,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721463</v>
+        <v>721591</v>
       </c>
       <c r="R15" t="n">
-        <v>6380440</v>
+        <v>6380497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,27 +2312,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265600</v>
+        <v>127265540</v>
       </c>
       <c r="B16" t="n">
-        <v>109283</v>
+        <v>106057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2352,14 +2343,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721547</v>
+        <v>721546</v>
       </c>
       <c r="R16" t="n">
-        <v>6380409</v>
+        <v>6380552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,7 +2396,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2423,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265587</v>
+        <v>127265492</v>
       </c>
       <c r="B17" t="n">
-        <v>105494</v>
+        <v>98482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,21 +2425,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2463,17 +2454,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721591</v>
+        <v>721239</v>
       </c>
       <c r="R17" t="n">
-        <v>6380497</v>
+        <v>6380330</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2534,57 +2525,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265497</v>
+        <v>127265600</v>
       </c>
       <c r="B18" t="n">
-        <v>98479</v>
+        <v>109286</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721247</v>
+        <v>721547</v>
       </c>
       <c r="R18" t="n">
-        <v>6380342</v>
+        <v>6380409</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2630,7 @@
         <v>127265518</v>
       </c>
       <c r="B19" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265492</v>
+        <v>127265497</v>
       </c>
       <c r="B20" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2786,7 +2768,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2800,10 +2782,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R20" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S20" t="n">
         <v>7</v>
@@ -2867,48 +2849,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265532</v>
+        <v>127265479</v>
       </c>
       <c r="B21" t="n">
-        <v>106054</v>
+        <v>98377</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721484</v>
+        <v>721212</v>
       </c>
       <c r="R21" t="n">
-        <v>6380450</v>
+        <v>6380346</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2969,45 +2960,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265540</v>
+        <v>127265530</v>
       </c>
       <c r="B22" t="n">
-        <v>106054</v>
+        <v>98495</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>223621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721546</v>
+        <v>721463</v>
       </c>
       <c r="R22" t="n">
-        <v>6380552</v>
+        <v>6380440</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
         <v>127265496</v>
       </c>
       <c r="B23" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>127265610</v>
       </c>
       <c r="B24" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>127265590</v>
       </c>
       <c r="B25" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265473</v>
+        <v>127265475</v>
       </c>
       <c r="B26" t="n">
-        <v>98434</v>
+        <v>98482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3411,26 +3411,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721232</v>
+        <v>721209</v>
       </c>
       <c r="R26" t="n">
-        <v>6380313</v>
+        <v>6380333</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265475</v>
+        <v>127265473</v>
       </c>
       <c r="B27" t="n">
-        <v>98479</v>
+        <v>98437</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,26 +3522,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3555,13 +3555,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721209</v>
+        <v>721232</v>
       </c>
       <c r="R27" t="n">
-        <v>6380333</v>
+        <v>6380313</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3622,48 +3622,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265503</v>
+        <v>127265624</v>
       </c>
       <c r="B28" t="n">
-        <v>106054</v>
+        <v>98377</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721272</v>
+        <v>721199</v>
       </c>
       <c r="R28" t="n">
-        <v>6380356</v>
+        <v>6380248</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3724,57 +3733,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265624</v>
+        <v>127265503</v>
       </c>
       <c r="B29" t="n">
-        <v>98374</v>
+        <v>106057</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721199</v>
+        <v>721272</v>
       </c>
       <c r="R29" t="n">
-        <v>6380248</v>
+        <v>6380356</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>127265548</v>
       </c>
       <c r="B30" t="n">
-        <v>99673</v>
+        <v>99676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,48 +3951,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265486</v>
+        <v>127265598</v>
       </c>
       <c r="B31" t="n">
-        <v>109283</v>
+        <v>98482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721231</v>
+        <v>721557</v>
       </c>
       <c r="R31" t="n">
-        <v>6380342</v>
+        <v>6380422</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4035,7 +4044,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4053,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265598</v>
+        <v>127265606</v>
       </c>
       <c r="B32" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4083,7 +4092,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4097,10 +4106,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721557</v>
+        <v>721475</v>
       </c>
       <c r="R32" t="n">
-        <v>6380422</v>
+        <v>6380396</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4146,7 +4155,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4164,57 +4173,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265606</v>
+        <v>127265486</v>
       </c>
       <c r="B33" t="n">
-        <v>98479</v>
+        <v>109286</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721475</v>
+        <v>721231</v>
       </c>
       <c r="R33" t="n">
-        <v>6380396</v>
+        <v>6380342</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4275,57 +4275,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127296661</v>
+        <v>127265594</v>
       </c>
       <c r="B34" t="n">
-        <v>58340</v>
+        <v>109286</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721560</v>
+        <v>721572</v>
       </c>
       <c r="R34" t="n">
-        <v>6380582</v>
+        <v>6380434</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4357,6 +4348,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4368,7 +4364,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4386,45 +4382,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265594</v>
+        <v>127265584</v>
       </c>
       <c r="B35" t="n">
-        <v>109283</v>
+        <v>98482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721572</v>
+        <v>721601</v>
       </c>
       <c r="R35" t="n">
-        <v>6380434</v>
+        <v>6380518</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4457,11 +4462,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,10 +4493,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265584</v>
+        <v>127296661</v>
       </c>
       <c r="B36" t="n">
-        <v>98479</v>
+        <v>58343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4504,46 +4504,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721601</v>
+        <v>721560</v>
       </c>
       <c r="R36" t="n">
-        <v>6380518</v>
+        <v>6380582</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127265612</v>
+        <v>127265541</v>
       </c>
       <c r="B37" t="n">
-        <v>98493</v>
+        <v>98377</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,43 +4615,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721424</v>
+        <v>721546</v>
       </c>
       <c r="R37" t="n">
-        <v>6380372</v>
+        <v>6380552</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4697,7 +4688,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4715,10 +4706,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265541</v>
+        <v>127265566</v>
       </c>
       <c r="B38" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4746,14 +4737,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721546</v>
+        <v>721615</v>
       </c>
       <c r="R38" t="n">
-        <v>6380552</v>
+        <v>6380615</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4790,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4817,10 +4808,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265566</v>
+        <v>127265582</v>
       </c>
       <c r="B39" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4845,17 +4836,26 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721615</v>
+        <v>721601</v>
       </c>
       <c r="R39" t="n">
-        <v>6380615</v>
+        <v>6380518</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265582</v>
+        <v>127265612</v>
       </c>
       <c r="B40" t="n">
-        <v>98374</v>
+        <v>98496</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,21 +4930,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721601</v>
+        <v>721424</v>
       </c>
       <c r="R40" t="n">
-        <v>6380518</v>
+        <v>6380372</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5030,57 +5030,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127265623</v>
+        <v>127265579</v>
       </c>
       <c r="B41" t="n">
-        <v>98434</v>
+        <v>106057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721199</v>
+        <v>721577</v>
       </c>
       <c r="R41" t="n">
-        <v>6380248</v>
+        <v>6380550</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5141,10 +5132,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265579</v>
+        <v>127265545</v>
       </c>
       <c r="B42" t="n">
-        <v>106054</v>
+        <v>106057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5172,14 +5163,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721577</v>
+        <v>721560</v>
       </c>
       <c r="R42" t="n">
-        <v>6380550</v>
+        <v>6380582</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5225,7 +5216,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5243,48 +5234,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127265545</v>
+        <v>127265623</v>
       </c>
       <c r="B43" t="n">
-        <v>106054</v>
+        <v>98437</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721560</v>
+        <v>721199</v>
       </c>
       <c r="R43" t="n">
-        <v>6380582</v>
+        <v>6380248</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5345,57 +5345,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265515</v>
+        <v>127265534</v>
       </c>
       <c r="B44" t="n">
-        <v>98434</v>
+        <v>109286</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721315</v>
+        <v>721493</v>
       </c>
       <c r="R44" t="n">
-        <v>6380362</v>
+        <v>6380446</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5456,48 +5447,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265534</v>
+        <v>127265515</v>
       </c>
       <c r="B45" t="n">
-        <v>109283</v>
+        <v>98437</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721493</v>
+        <v>721315</v>
       </c>
       <c r="R45" t="n">
-        <v>6380446</v>
+        <v>6380362</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>127265571</v>
       </c>
       <c r="B46" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>127265478</v>
       </c>
       <c r="B47" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>127265626</v>
       </c>
       <c r="B48" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>127265597</v>
       </c>
       <c r="B49" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>127265593</v>
       </c>
       <c r="B50" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>127265472</v>
       </c>
       <c r="B51" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>127265628</v>
       </c>
       <c r="B52" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>127265507</v>
       </c>
       <c r="B53" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6437,64 +6437,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B54" t="n">
-        <v>43234</v>
+        <v>106057</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R54" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,45 +6539,64 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B55" t="n">
-        <v>106054</v>
+        <v>43235</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R55" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6663,7 +6663,7 @@
         <v>127265481</v>
       </c>
       <c r="B56" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>127265622</v>
       </c>
       <c r="B57" t="n">
-        <v>103912</v>
+        <v>103915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6873,45 +6873,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265471</v>
+        <v>127265494</v>
       </c>
       <c r="B58" t="n">
-        <v>106054</v>
+        <v>98481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721232</v>
+        <v>721247</v>
       </c>
       <c r="R58" t="n">
-        <v>6380313</v>
+        <v>6380342</v>
       </c>
       <c r="S58" t="n">
         <v>7</v>
@@ -6975,10 +6984,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265494</v>
+        <v>127265484</v>
       </c>
       <c r="B59" t="n">
-        <v>98478</v>
+        <v>98377</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6986,26 +6995,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7019,10 +7028,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721247</v>
+        <v>721220</v>
       </c>
       <c r="R59" t="n">
-        <v>6380342</v>
+        <v>6380355</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7086,54 +7095,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265484</v>
+        <v>127265471</v>
       </c>
       <c r="B60" t="n">
-        <v>98374</v>
+        <v>106057</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R60" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7197,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265495</v>
+        <v>127265517</v>
       </c>
       <c r="B61" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721247</v>
+        <v>721330</v>
       </c>
       <c r="R61" t="n">
-        <v>6380342</v>
+        <v>6380365</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7308,10 +7308,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265617</v>
+        <v>127265474</v>
       </c>
       <c r="B62" t="n">
-        <v>98478</v>
+        <v>98377</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7319,26 +7319,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7346,24 +7346,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721357</v>
+        <v>721232</v>
       </c>
       <c r="R62" t="n">
-        <v>6380338</v>
+        <v>6380313</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7424,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265517</v>
+        <v>127265504</v>
       </c>
       <c r="B63" t="n">
-        <v>98434</v>
+        <v>98377</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7435,26 +7430,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7464,17 +7459,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721330</v>
+        <v>721272</v>
       </c>
       <c r="R63" t="n">
-        <v>6380365</v>
+        <v>6380356</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7535,37 +7530,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265533</v>
+        <v>127265546</v>
       </c>
       <c r="B64" t="n">
-        <v>99207</v>
+        <v>98377</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222361</v>
+        <v>223591</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7579,10 +7574,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721484</v>
+        <v>721560</v>
       </c>
       <c r="R64" t="n">
-        <v>6380450</v>
+        <v>6380582</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7628,7 +7623,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7649,7 +7644,7 @@
         <v>127265505</v>
       </c>
       <c r="B65" t="n">
-        <v>106054</v>
+        <v>106057</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7751,7 +7746,7 @@
         <v>127265488</v>
       </c>
       <c r="B66" t="n">
-        <v>106054</v>
+        <v>106057</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7850,10 +7845,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265474</v>
+        <v>127265495</v>
       </c>
       <c r="B67" t="n">
-        <v>98374</v>
+        <v>98437</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7861,26 +7856,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7894,10 +7889,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721232</v>
+        <v>721247</v>
       </c>
       <c r="R67" t="n">
-        <v>6380313</v>
+        <v>6380342</v>
       </c>
       <c r="S67" t="n">
         <v>7</v>
@@ -7961,10 +7956,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265504</v>
+        <v>127265617</v>
       </c>
       <c r="B68" t="n">
-        <v>98374</v>
+        <v>98481</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7972,26 +7967,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7999,19 +7994,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721272</v>
+        <v>721357</v>
       </c>
       <c r="R68" t="n">
-        <v>6380356</v>
+        <v>6380338</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8072,37 +8072,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265546</v>
+        <v>127265533</v>
       </c>
       <c r="B69" t="n">
-        <v>98374</v>
+        <v>99210</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721560</v>
+        <v>721484</v>
       </c>
       <c r="R69" t="n">
-        <v>6380582</v>
+        <v>6380450</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8186,7 +8186,7 @@
         <v>127265525</v>
       </c>
       <c r="B70" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>127265476</v>
       </c>
       <c r="B71" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,45 +8410,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265526</v>
+        <v>127265586</v>
       </c>
       <c r="B72" t="n">
-        <v>109283</v>
+        <v>98482</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721433</v>
+        <v>721591</v>
       </c>
       <c r="R72" t="n">
-        <v>6380417</v>
+        <v>6380497</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8481,11 +8490,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8517,54 +8521,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265586</v>
+        <v>127265526</v>
       </c>
       <c r="B73" t="n">
-        <v>98479</v>
+        <v>109286</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721591</v>
+        <v>721433</v>
       </c>
       <c r="R73" t="n">
-        <v>6380497</v>
+        <v>6380417</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8597,6 +8592,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8631,7 +8631,7 @@
         <v>127265528</v>
       </c>
       <c r="B74" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8739,45 +8739,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B75" t="n">
-        <v>109283</v>
+        <v>98482</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R75" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8841,54 +8850,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B76" t="n">
-        <v>98479</v>
+        <v>109286</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R76" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8952,48 +8952,57 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127265513</v>
+        <v>127265508</v>
       </c>
       <c r="B77" t="n">
-        <v>109283</v>
+        <v>98437</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721315</v>
+        <v>721307</v>
       </c>
       <c r="R77" t="n">
-        <v>6380362</v>
+        <v>6380360</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9054,57 +9063,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127265508</v>
+        <v>127265513</v>
       </c>
       <c r="B78" t="n">
-        <v>98434</v>
+        <v>109286</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721307</v>
+        <v>721315</v>
       </c>
       <c r="R78" t="n">
-        <v>6380360</v>
+        <v>6380362</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9165,10 +9165,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127296632</v>
+        <v>127265605</v>
       </c>
       <c r="B79" t="n">
-        <v>43234</v>
+        <v>109286</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9176,53 +9176,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>721578</v>
+        <v>721466</v>
       </c>
       <c r="R79" t="n">
-        <v>6380530</v>
+        <v>6380394</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9257,11 +9238,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Lundstarr rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9273,7 +9249,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9294,7 +9270,7 @@
         <v>127265493</v>
       </c>
       <c r="B80" t="n">
-        <v>106054</v>
+        <v>106057</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9396,7 +9372,7 @@
         <v>127265491</v>
       </c>
       <c r="B81" t="n">
-        <v>106054</v>
+        <v>106057</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9495,57 +9471,67 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265489</v>
+        <v>127296632</v>
       </c>
       <c r="B82" t="n">
-        <v>98374</v>
+        <v>43235</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721231</v>
+        <v>721578</v>
       </c>
       <c r="R82" t="n">
-        <v>6380342</v>
+        <v>6380530</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9577,6 +9563,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Lundstarr rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9588,7 +9579,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9606,48 +9597,57 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127265605</v>
+        <v>127265489</v>
       </c>
       <c r="B83" t="n">
-        <v>109283</v>
+        <v>98377</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721466</v>
+        <v>721231</v>
       </c>
       <c r="R83" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>127265572</v>
       </c>
       <c r="B84" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9819,48 +9819,57 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265549</v>
+        <v>127265499</v>
       </c>
       <c r="B85" t="n">
-        <v>106054</v>
+        <v>98377</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721590</v>
+        <v>721247</v>
       </c>
       <c r="R85" t="n">
-        <v>6380571</v>
+        <v>6380342</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9903,7 +9912,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9921,10 +9930,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265511</v>
+        <v>127265549</v>
       </c>
       <c r="B86" t="n">
-        <v>106054</v>
+        <v>106057</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9952,17 +9961,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721315</v>
+        <v>721590</v>
       </c>
       <c r="R86" t="n">
-        <v>6380362</v>
+        <v>6380571</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10005,7 +10014,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10023,57 +10032,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127265499</v>
+        <v>127265511</v>
       </c>
       <c r="B87" t="n">
-        <v>98374</v>
+        <v>106057</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>721247</v>
+        <v>721315</v>
       </c>
       <c r="R87" t="n">
-        <v>6380342</v>
+        <v>6380362</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10134,48 +10134,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127265483</v>
+        <v>127265519</v>
       </c>
       <c r="B88" t="n">
-        <v>106054</v>
+        <v>98377</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>721220</v>
+        <v>721330</v>
       </c>
       <c r="R88" t="n">
-        <v>6380355</v>
+        <v>6380365</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265519</v>
+        <v>127265500</v>
       </c>
       <c r="B89" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10264,20 +10264,29 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721330</v>
+        <v>721263</v>
       </c>
       <c r="R89" t="n">
-        <v>6380365</v>
+        <v>6380356</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10338,10 +10347,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265500</v>
+        <v>127265506</v>
       </c>
       <c r="B90" t="n">
-        <v>98374</v>
+        <v>98377</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10368,7 +10377,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10382,10 +10391,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721263</v>
+        <v>721284</v>
       </c>
       <c r="R90" t="n">
-        <v>6380356</v>
+        <v>6380359</v>
       </c>
       <c r="S90" t="n">
         <v>7</v>
@@ -10449,54 +10458,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127265506</v>
+        <v>127265483</v>
       </c>
       <c r="B91" t="n">
-        <v>98374</v>
+        <v>106057</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>721284</v>
+        <v>721220</v>
       </c>
       <c r="R91" t="n">
-        <v>6380359</v>
+        <v>6380355</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,45 +2099,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265532</v>
+        <v>127265587</v>
       </c>
       <c r="B14" t="n">
-        <v>106057</v>
+        <v>105505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721484</v>
+        <v>721591</v>
       </c>
       <c r="R14" t="n">
-        <v>6380450</v>
+        <v>6380497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2201,54 +2210,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265587</v>
+        <v>127265532</v>
       </c>
       <c r="B15" t="n">
-        <v>105497</v>
+        <v>106065</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220785</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721591</v>
+        <v>721484</v>
       </c>
       <c r="R15" t="n">
-        <v>6380497</v>
+        <v>6380450</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2315,7 +2315,7 @@
         <v>127265540</v>
       </c>
       <c r="B16" t="n">
-        <v>106057</v>
+        <v>106065</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,57 +2414,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265492</v>
+        <v>127265600</v>
       </c>
       <c r="B17" t="n">
-        <v>98482</v>
+        <v>109294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721239</v>
+        <v>721547</v>
       </c>
       <c r="R17" t="n">
-        <v>6380330</v>
+        <v>6380409</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2525,48 +2516,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265600</v>
+        <v>127265479</v>
       </c>
       <c r="B18" t="n">
-        <v>109286</v>
+        <v>98385</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721547</v>
+        <v>721212</v>
       </c>
       <c r="R18" t="n">
-        <v>6380409</v>
+        <v>6380346</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2627,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265518</v>
+        <v>127265530</v>
       </c>
       <c r="B19" t="n">
-        <v>98482</v>
+        <v>98503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,21 +2638,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721330</v>
+        <v>721463</v>
       </c>
       <c r="R19" t="n">
-        <v>6380365</v>
+        <v>6380440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2741,7 +2741,7 @@
         <v>127265497</v>
       </c>
       <c r="B20" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265479</v>
+        <v>127265518</v>
       </c>
       <c r="B21" t="n">
-        <v>98377</v>
+        <v>98490</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,26 +2860,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2889,17 +2889,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721212</v>
+        <v>721330</v>
       </c>
       <c r="R21" t="n">
-        <v>6380346</v>
+        <v>6380365</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265530</v>
+        <v>127265492</v>
       </c>
       <c r="B22" t="n">
-        <v>98495</v>
+        <v>98490</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,21 +2971,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3000,17 +3000,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721463</v>
+        <v>721239</v>
       </c>
       <c r="R22" t="n">
-        <v>6380440</v>
+        <v>6380330</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>127265496</v>
       </c>
       <c r="B23" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>127265610</v>
       </c>
       <c r="B24" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>127265590</v>
       </c>
       <c r="B25" t="n">
-        <v>98495</v>
+        <v>98503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,57 +3400,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265475</v>
+        <v>127265503</v>
       </c>
       <c r="B26" t="n">
-        <v>98482</v>
+        <v>106065</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721209</v>
+        <v>721272</v>
       </c>
       <c r="R26" t="n">
-        <v>6380333</v>
+        <v>6380356</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,10 +3502,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265473</v>
+        <v>127265624</v>
       </c>
       <c r="B27" t="n">
-        <v>98437</v>
+        <v>98385</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,26 +3513,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3551,17 +3542,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721232</v>
+        <v>721199</v>
       </c>
       <c r="R27" t="n">
-        <v>6380313</v>
+        <v>6380248</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3622,10 +3613,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265624</v>
+        <v>127265473</v>
       </c>
       <c r="B28" t="n">
-        <v>98377</v>
+        <v>98445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,26 +3624,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3662,17 +3653,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721199</v>
+        <v>721232</v>
       </c>
       <c r="R28" t="n">
-        <v>6380248</v>
+        <v>6380313</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3733,48 +3724,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265503</v>
+        <v>127265475</v>
       </c>
       <c r="B29" t="n">
-        <v>106057</v>
+        <v>98490</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721272</v>
+        <v>721209</v>
       </c>
       <c r="R29" t="n">
-        <v>6380356</v>
+        <v>6380333</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265548</v>
+        <v>127265598</v>
       </c>
       <c r="B30" t="n">
-        <v>99676</v>
+        <v>98490</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3846,31 +3846,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>174</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3879,13 +3879,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721578</v>
+        <v>721557</v>
       </c>
       <c r="R30" t="n">
-        <v>6380576</v>
+        <v>6380422</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,11 +3917,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3933,7 +3928,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3951,10 +3946,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265598</v>
+        <v>127265606</v>
       </c>
       <c r="B31" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3976,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3995,10 +3990,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721557</v>
+        <v>721475</v>
       </c>
       <c r="R31" t="n">
-        <v>6380422</v>
+        <v>6380396</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,7 +4039,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4062,10 +4057,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265606</v>
+        <v>127265548</v>
       </c>
       <c r="B32" t="n">
-        <v>98482</v>
+        <v>99684</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,31 +4068,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>174</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4106,13 +4101,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721475</v>
+        <v>721578</v>
       </c>
       <c r="R32" t="n">
-        <v>6380396</v>
+        <v>6380576</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4144,6 +4139,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
         <v>127265486</v>
       </c>
       <c r="B33" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,48 +4275,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127265594</v>
+        <v>127296661</v>
       </c>
       <c r="B34" t="n">
-        <v>109286</v>
+        <v>58349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721572</v>
+        <v>721560</v>
       </c>
       <c r="R34" t="n">
-        <v>6380434</v>
+        <v>6380582</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4348,11 +4357,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4364,7 +4368,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4382,54 +4386,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265584</v>
+        <v>127265594</v>
       </c>
       <c r="B35" t="n">
-        <v>98482</v>
+        <v>109294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721601</v>
+        <v>721572</v>
       </c>
       <c r="R35" t="n">
-        <v>6380518</v>
+        <v>6380434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4462,6 +4457,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,10 +4493,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296661</v>
+        <v>127265584</v>
       </c>
       <c r="B36" t="n">
-        <v>58343</v>
+        <v>98490</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4504,46 +4504,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721560</v>
+        <v>721601</v>
       </c>
       <c r="R36" t="n">
-        <v>6380582</v>
+        <v>6380518</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4607,7 +4607,7 @@
         <v>127265541</v>
       </c>
       <c r="B37" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4706,10 +4706,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265566</v>
+        <v>127265582</v>
       </c>
       <c r="B38" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,17 +4734,26 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721615</v>
+        <v>721601</v>
       </c>
       <c r="R38" t="n">
-        <v>6380615</v>
+        <v>6380518</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,7 +4799,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4808,10 +4817,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265582</v>
+        <v>127265566</v>
       </c>
       <c r="B39" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,26 +4845,17 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721601</v>
+        <v>721615</v>
       </c>
       <c r="R39" t="n">
-        <v>6380518</v>
+        <v>6380615</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4922,7 +4922,7 @@
         <v>127265612</v>
       </c>
       <c r="B40" t="n">
-        <v>98496</v>
+        <v>98504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>127265579</v>
       </c>
       <c r="B41" t="n">
-        <v>106057</v>
+        <v>106065</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>127265545</v>
       </c>
       <c r="B42" t="n">
-        <v>106057</v>
+        <v>106065</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>127265623</v>
       </c>
       <c r="B43" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>127265534</v>
       </c>
       <c r="B44" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265515</v>
+        <v>127265571</v>
       </c>
       <c r="B45" t="n">
-        <v>98437</v>
+        <v>98385</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5458,26 +5458,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5487,17 +5487,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R45" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265571</v>
+        <v>127265515</v>
       </c>
       <c r="B46" t="n">
-        <v>98377</v>
+        <v>98445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5569,26 +5569,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5598,17 +5598,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721594</v>
+        <v>721315</v>
       </c>
       <c r="R46" t="n">
-        <v>6380563</v>
+        <v>6380362</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127265478</v>
+        <v>127265626</v>
       </c>
       <c r="B47" t="n">
-        <v>98437</v>
+        <v>98385</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,26 +5680,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721212</v>
+        <v>721183</v>
       </c>
       <c r="R47" t="n">
-        <v>6380346</v>
+        <v>6380248</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127265626</v>
+        <v>127265597</v>
       </c>
       <c r="B48" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5824,13 +5824,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721183</v>
+        <v>721557</v>
       </c>
       <c r="R48" t="n">
-        <v>6380248</v>
+        <v>6380422</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127265597</v>
+        <v>127265478</v>
       </c>
       <c r="B49" t="n">
-        <v>98377</v>
+        <v>98445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,26 +5902,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721557</v>
+        <v>721212</v>
       </c>
       <c r="R49" t="n">
-        <v>6380422</v>
+        <v>6380346</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127265593</v>
+        <v>127265628</v>
       </c>
       <c r="B50" t="n">
-        <v>98482</v>
+        <v>98385</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,37 +6013,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721572</v>
+        <v>721173</v>
       </c>
       <c r="R50" t="n">
-        <v>6380434</v>
+        <v>6380248</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6104,10 +6113,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127265472</v>
+        <v>127265507</v>
       </c>
       <c r="B51" t="n">
-        <v>98482</v>
+        <v>98385</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,21 +6124,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6148,13 +6157,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721232</v>
+        <v>721307</v>
       </c>
       <c r="R51" t="n">
-        <v>6380313</v>
+        <v>6380360</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6215,10 +6224,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127265628</v>
+        <v>127265593</v>
       </c>
       <c r="B52" t="n">
-        <v>98377</v>
+        <v>98490</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6226,46 +6235,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721173</v>
+        <v>721572</v>
       </c>
       <c r="R52" t="n">
-        <v>6380248</v>
+        <v>6380434</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127265507</v>
+        <v>127265472</v>
       </c>
       <c r="B53" t="n">
-        <v>98377</v>
+        <v>98490</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6370,13 +6370,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721307</v>
+        <v>721232</v>
       </c>
       <c r="R53" t="n">
-        <v>6380360</v>
+        <v>6380313</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6437,45 +6437,64 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B54" t="n">
-        <v>106057</v>
+        <v>43235</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R54" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6539,64 +6558,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B55" t="n">
-        <v>43235</v>
+        <v>106065</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R55" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265481</v>
+        <v>127265622</v>
       </c>
       <c r="B56" t="n">
-        <v>109286</v>
+        <v>103923</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6671,37 +6671,46 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721220</v>
+        <v>721252</v>
       </c>
       <c r="R56" t="n">
-        <v>6380355</v>
+        <v>6380274</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6762,10 +6771,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265622</v>
+        <v>127265481</v>
       </c>
       <c r="B57" t="n">
-        <v>103915</v>
+        <v>109294</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6773,46 +6782,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721252</v>
+        <v>721220</v>
       </c>
       <c r="R57" t="n">
-        <v>6380274</v>
+        <v>6380355</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6873,54 +6873,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265494</v>
+        <v>127265471</v>
       </c>
       <c r="B58" t="n">
-        <v>98481</v>
+        <v>106065</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721247</v>
+        <v>721232</v>
       </c>
       <c r="R58" t="n">
-        <v>6380342</v>
+        <v>6380313</v>
       </c>
       <c r="S58" t="n">
         <v>7</v>
@@ -6987,7 +6978,7 @@
         <v>127265484</v>
       </c>
       <c r="B59" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7095,45 +7086,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265471</v>
+        <v>127265494</v>
       </c>
       <c r="B60" t="n">
-        <v>106057</v>
+        <v>98489</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721232</v>
+        <v>721247</v>
       </c>
       <c r="R60" t="n">
-        <v>6380313</v>
+        <v>6380342</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7197,57 +7197,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265517</v>
+        <v>127265505</v>
       </c>
       <c r="B61" t="n">
-        <v>98437</v>
+        <v>106065</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721330</v>
+        <v>721284</v>
       </c>
       <c r="R61" t="n">
-        <v>6380365</v>
+        <v>6380359</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7308,57 +7299,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265474</v>
+        <v>127265488</v>
       </c>
       <c r="B62" t="n">
-        <v>98377</v>
+        <v>106065</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721232</v>
+        <v>721231</v>
       </c>
       <c r="R62" t="n">
-        <v>6380313</v>
+        <v>6380342</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7419,37 +7401,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265504</v>
+        <v>127265533</v>
       </c>
       <c r="B63" t="n">
-        <v>98377</v>
+        <v>99218</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7459,17 +7441,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721272</v>
+        <v>721484</v>
       </c>
       <c r="R63" t="n">
-        <v>6380356</v>
+        <v>6380450</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7530,10 +7512,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265546</v>
+        <v>127265474</v>
       </c>
       <c r="B64" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7560,7 +7542,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7570,17 +7552,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721560</v>
+        <v>721232</v>
       </c>
       <c r="R64" t="n">
-        <v>6380582</v>
+        <v>6380313</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7623,7 +7605,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7641,45 +7623,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265505</v>
+        <v>127265504</v>
       </c>
       <c r="B65" t="n">
-        <v>106057</v>
+        <v>98385</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721284</v>
+        <v>721272</v>
       </c>
       <c r="R65" t="n">
-        <v>6380359</v>
+        <v>6380356</v>
       </c>
       <c r="S65" t="n">
         <v>7</v>
@@ -7743,48 +7734,57 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265488</v>
+        <v>127265546</v>
       </c>
       <c r="B66" t="n">
-        <v>106057</v>
+        <v>98385</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721231</v>
+        <v>721560</v>
       </c>
       <c r="R66" t="n">
-        <v>6380342</v>
+        <v>6380582</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7848,7 +7848,7 @@
         <v>127265495</v>
       </c>
       <c r="B67" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>127265617</v>
       </c>
       <c r="B68" t="n">
-        <v>98481</v>
+        <v>98489</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8072,37 +8072,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265533</v>
+        <v>127265517</v>
       </c>
       <c r="B69" t="n">
-        <v>99210</v>
+        <v>98445</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721484</v>
+        <v>721330</v>
       </c>
       <c r="R69" t="n">
-        <v>6380450</v>
+        <v>6380365</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8186,7 +8186,7 @@
         <v>127265525</v>
       </c>
       <c r="B70" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>127265476</v>
       </c>
       <c r="B71" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,54 +8410,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265586</v>
+        <v>127265526</v>
       </c>
       <c r="B72" t="n">
-        <v>98482</v>
+        <v>109294</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721591</v>
+        <v>721433</v>
       </c>
       <c r="R72" t="n">
-        <v>6380497</v>
+        <v>6380417</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8490,6 +8481,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8521,45 +8517,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265526</v>
+        <v>127265586</v>
       </c>
       <c r="B73" t="n">
-        <v>109286</v>
+        <v>98490</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721433</v>
+        <v>721591</v>
       </c>
       <c r="R73" t="n">
-        <v>6380417</v>
+        <v>6380497</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8592,11 +8597,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8631,7 +8631,7 @@
         <v>127265528</v>
       </c>
       <c r="B74" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8739,54 +8739,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B75" t="n">
-        <v>98482</v>
+        <v>109294</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R75" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8850,45 +8841,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B76" t="n">
-        <v>109286</v>
+        <v>98490</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R76" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8955,7 +8955,7 @@
         <v>127265508</v>
       </c>
       <c r="B77" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>127265513</v>
       </c>
       <c r="B78" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9165,10 +9165,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127265605</v>
+        <v>127296632</v>
       </c>
       <c r="B79" t="n">
-        <v>109286</v>
+        <v>43235</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9176,34 +9176,53 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>721466</v>
+        <v>721578</v>
       </c>
       <c r="R79" t="n">
-        <v>6380394</v>
+        <v>6380530</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9238,6 +9257,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Lundstarr rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9249,7 +9273,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9267,27 +9291,27 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265493</v>
+        <v>127265605</v>
       </c>
       <c r="B80" t="n">
-        <v>106057</v>
+        <v>109294</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9298,17 +9322,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R80" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9369,10 +9393,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265491</v>
+        <v>127265493</v>
       </c>
       <c r="B81" t="n">
-        <v>106057</v>
+        <v>106065</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9404,10 +9428,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R81" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S81" t="n">
         <v>7</v>
@@ -9471,67 +9495,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127296632</v>
+        <v>127265491</v>
       </c>
       <c r="B82" t="n">
-        <v>43235</v>
+        <v>106065</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721578</v>
+        <v>721239</v>
       </c>
       <c r="R82" t="n">
-        <v>6380530</v>
+        <v>6380330</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9563,11 +9568,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Lundstarr rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9600,7 +9600,7 @@
         <v>127265489</v>
       </c>
       <c r="B83" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9708,54 +9708,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265572</v>
+        <v>127265549</v>
       </c>
       <c r="B84" t="n">
-        <v>98437</v>
+        <v>106065</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721594</v>
+        <v>721590</v>
       </c>
       <c r="R84" t="n">
-        <v>6380563</v>
+        <v>6380571</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9801,7 +9792,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9819,57 +9810,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265499</v>
+        <v>127265511</v>
       </c>
       <c r="B85" t="n">
-        <v>98377</v>
+        <v>106065</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721247</v>
+        <v>721315</v>
       </c>
       <c r="R85" t="n">
-        <v>6380342</v>
+        <v>6380362</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9930,48 +9912,57 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265549</v>
+        <v>127265499</v>
       </c>
       <c r="B86" t="n">
-        <v>106057</v>
+        <v>98385</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721590</v>
+        <v>721247</v>
       </c>
       <c r="R86" t="n">
-        <v>6380571</v>
+        <v>6380342</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10014,7 +10005,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10032,48 +10023,57 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127265511</v>
+        <v>127265572</v>
       </c>
       <c r="B87" t="n">
-        <v>106057</v>
+        <v>98445</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R87" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10134,48 +10134,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127265519</v>
+        <v>127265483</v>
       </c>
       <c r="B88" t="n">
-        <v>98377</v>
+        <v>106065</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>721330</v>
+        <v>721220</v>
       </c>
       <c r="R88" t="n">
-        <v>6380365</v>
+        <v>6380355</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265500</v>
+        <v>127265519</v>
       </c>
       <c r="B89" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10264,29 +10264,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721263</v>
+        <v>721330</v>
       </c>
       <c r="R89" t="n">
-        <v>6380356</v>
+        <v>6380365</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10350,7 +10341,7 @@
         <v>127265506</v>
       </c>
       <c r="B90" t="n">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10458,45 +10449,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127265483</v>
+        <v>127265500</v>
       </c>
       <c r="B91" t="n">
-        <v>106057</v>
+        <v>98385</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>721220</v>
+        <v>721263</v>
       </c>
       <c r="R91" t="n">
-        <v>6380355</v>
+        <v>6380356</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265587</v>
+        <v>127265497</v>
       </c>
       <c r="B14" t="n">
-        <v>105505</v>
+        <v>98491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,26 +2110,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2139,17 +2139,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721591</v>
+        <v>721247</v>
       </c>
       <c r="R14" t="n">
-        <v>6380497</v>
+        <v>6380342</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,45 +2210,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265532</v>
+        <v>127265518</v>
       </c>
       <c r="B15" t="n">
-        <v>106065</v>
+        <v>98491</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721484</v>
+        <v>721330</v>
       </c>
       <c r="R15" t="n">
-        <v>6380450</v>
+        <v>6380365</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,48 +2321,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265540</v>
+        <v>127265492</v>
       </c>
       <c r="B16" t="n">
-        <v>106065</v>
+        <v>98491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721546</v>
+        <v>721239</v>
       </c>
       <c r="R16" t="n">
-        <v>6380552</v>
+        <v>6380330</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2396,7 +2414,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2414,48 +2432,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265600</v>
+        <v>127265479</v>
       </c>
       <c r="B17" t="n">
-        <v>109294</v>
+        <v>98386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721547</v>
+        <v>721212</v>
       </c>
       <c r="R17" t="n">
-        <v>6380409</v>
+        <v>6380346</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2516,10 +2543,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265479</v>
+        <v>127265530</v>
       </c>
       <c r="B18" t="n">
-        <v>98385</v>
+        <v>98504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,26 +2554,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2556,17 +2583,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721212</v>
+        <v>721463</v>
       </c>
       <c r="R18" t="n">
-        <v>6380346</v>
+        <v>6380440</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2627,54 +2654,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265530</v>
+        <v>127265532</v>
       </c>
       <c r="B19" t="n">
-        <v>98503</v>
+        <v>106066</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223621</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721463</v>
+        <v>721484</v>
       </c>
       <c r="R19" t="n">
-        <v>6380440</v>
+        <v>6380450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,57 +2756,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265497</v>
+        <v>127265540</v>
       </c>
       <c r="B20" t="n">
-        <v>98490</v>
+        <v>106066</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721247</v>
+        <v>721546</v>
       </c>
       <c r="R20" t="n">
-        <v>6380342</v>
+        <v>6380552</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2831,7 +2840,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2849,54 +2858,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265518</v>
+        <v>127265600</v>
       </c>
       <c r="B21" t="n">
-        <v>98490</v>
+        <v>109295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721330</v>
+        <v>721547</v>
       </c>
       <c r="R21" t="n">
-        <v>6380365</v>
+        <v>6380409</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265492</v>
+        <v>127265587</v>
       </c>
       <c r="B22" t="n">
-        <v>98490</v>
+        <v>105506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,21 +2971,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3000,17 +3000,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721239</v>
+        <v>721591</v>
       </c>
       <c r="R22" t="n">
-        <v>6380330</v>
+        <v>6380497</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3071,48 +3071,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265496</v>
+        <v>127265590</v>
       </c>
       <c r="B23" t="n">
-        <v>109294</v>
+        <v>98504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721247</v>
+        <v>721580</v>
       </c>
       <c r="R23" t="n">
-        <v>6380342</v>
+        <v>6380472</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3144,6 +3153,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3155,7 +3169,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3176,7 +3190,7 @@
         <v>127265610</v>
       </c>
       <c r="B24" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3284,57 +3298,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265590</v>
+        <v>127265496</v>
       </c>
       <c r="B25" t="n">
-        <v>98503</v>
+        <v>109295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721580</v>
+        <v>721247</v>
       </c>
       <c r="R25" t="n">
-        <v>6380472</v>
+        <v>6380342</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3366,11 +3371,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3400,48 +3400,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265503</v>
+        <v>127265624</v>
       </c>
       <c r="B26" t="n">
-        <v>106065</v>
+        <v>98386</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721272</v>
+        <v>721199</v>
       </c>
       <c r="R26" t="n">
-        <v>6380356</v>
+        <v>6380248</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3502,10 +3511,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265624</v>
+        <v>127265473</v>
       </c>
       <c r="B27" t="n">
-        <v>98385</v>
+        <v>98446</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3513,26 +3522,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3542,17 +3551,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721199</v>
+        <v>721232</v>
       </c>
       <c r="R27" t="n">
-        <v>6380248</v>
+        <v>6380313</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3613,10 +3622,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265473</v>
+        <v>127265475</v>
       </c>
       <c r="B28" t="n">
-        <v>98445</v>
+        <v>98491</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,26 +3633,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3657,13 +3666,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721232</v>
+        <v>721209</v>
       </c>
       <c r="R28" t="n">
-        <v>6380313</v>
+        <v>6380333</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3724,57 +3733,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265475</v>
+        <v>127265503</v>
       </c>
       <c r="B29" t="n">
-        <v>98490</v>
+        <v>106066</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721209</v>
+        <v>721272</v>
       </c>
       <c r="R29" t="n">
-        <v>6380333</v>
+        <v>6380356</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265598</v>
+        <v>127265548</v>
       </c>
       <c r="B30" t="n">
-        <v>98490</v>
+        <v>99685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3846,31 +3846,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>174</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3879,13 +3879,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721557</v>
+        <v>721578</v>
       </c>
       <c r="R30" t="n">
-        <v>6380422</v>
+        <v>6380576</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,6 +3917,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3928,7 +3933,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3946,10 +3951,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265606</v>
+        <v>127265598</v>
       </c>
       <c r="B31" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3976,7 +3981,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3990,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721475</v>
+        <v>721557</v>
       </c>
       <c r="R31" t="n">
-        <v>6380396</v>
+        <v>6380422</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4039,7 +4044,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4057,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265548</v>
+        <v>127265606</v>
       </c>
       <c r="B32" t="n">
-        <v>99684</v>
+        <v>98491</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,31 +4073,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>174</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4101,13 +4106,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721578</v>
+        <v>721475</v>
       </c>
       <c r="R32" t="n">
-        <v>6380576</v>
+        <v>6380396</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4139,11 +4144,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
         <v>127265486</v>
       </c>
       <c r="B33" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4386,45 +4386,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265594</v>
+        <v>127265584</v>
       </c>
       <c r="B35" t="n">
-        <v>109294</v>
+        <v>98491</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721572</v>
+        <v>721601</v>
       </c>
       <c r="R35" t="n">
-        <v>6380434</v>
+        <v>6380518</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4457,11 +4466,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,54 +4497,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265584</v>
+        <v>127265594</v>
       </c>
       <c r="B36" t="n">
-        <v>98490</v>
+        <v>109295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721601</v>
+        <v>721572</v>
       </c>
       <c r="R36" t="n">
-        <v>6380518</v>
+        <v>6380434</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4573,6 +4568,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4604,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127265541</v>
+        <v>127265612</v>
       </c>
       <c r="B37" t="n">
-        <v>98385</v>
+        <v>98505</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,34 +4615,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721546</v>
+        <v>721424</v>
       </c>
       <c r="R37" t="n">
-        <v>6380552</v>
+        <v>6380372</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,7 +4697,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4706,10 +4715,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265582</v>
+        <v>127265566</v>
       </c>
       <c r="B38" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,26 +4743,17 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721601</v>
+        <v>721615</v>
       </c>
       <c r="R38" t="n">
-        <v>6380518</v>
+        <v>6380615</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265566</v>
+        <v>127265582</v>
       </c>
       <c r="B39" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4845,17 +4845,26 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721615</v>
+        <v>721601</v>
       </c>
       <c r="R39" t="n">
-        <v>6380615</v>
+        <v>6380518</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4901,7 +4910,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4919,10 +4928,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265612</v>
+        <v>127265541</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>98386</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,43 +4939,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721424</v>
+        <v>721546</v>
       </c>
       <c r="R40" t="n">
-        <v>6380372</v>
+        <v>6380552</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5033,7 +5033,7 @@
         <v>127265579</v>
       </c>
       <c r="B41" t="n">
-        <v>106065</v>
+        <v>106066</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>127265545</v>
       </c>
       <c r="B42" t="n">
-        <v>106065</v>
+        <v>106066</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>127265623</v>
       </c>
       <c r="B43" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,48 +5345,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265534</v>
+        <v>127265515</v>
       </c>
       <c r="B44" t="n">
-        <v>109294</v>
+        <v>98446</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721493</v>
+        <v>721315</v>
       </c>
       <c r="R44" t="n">
-        <v>6380446</v>
+        <v>6380362</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5447,54 +5456,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265571</v>
+        <v>127265534</v>
       </c>
       <c r="B45" t="n">
-        <v>98385</v>
+        <v>109295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721594</v>
+        <v>721493</v>
       </c>
       <c r="R45" t="n">
-        <v>6380563</v>
+        <v>6380446</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265515</v>
+        <v>127265571</v>
       </c>
       <c r="B46" t="n">
-        <v>98445</v>
+        <v>98386</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5569,26 +5569,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5598,17 +5598,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R46" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127265626</v>
+        <v>127265478</v>
       </c>
       <c r="B47" t="n">
-        <v>98385</v>
+        <v>98446</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,26 +5680,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721183</v>
+        <v>721212</v>
       </c>
       <c r="R47" t="n">
-        <v>6380248</v>
+        <v>6380346</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127265597</v>
+        <v>127265626</v>
       </c>
       <c r="B48" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5824,13 +5824,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721557</v>
+        <v>721183</v>
       </c>
       <c r="R48" t="n">
-        <v>6380422</v>
+        <v>6380248</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127265478</v>
+        <v>127265597</v>
       </c>
       <c r="B49" t="n">
-        <v>98445</v>
+        <v>98386</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,26 +5902,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721212</v>
+        <v>721557</v>
       </c>
       <c r="R49" t="n">
-        <v>6380346</v>
+        <v>6380422</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127265628</v>
+        <v>127265593</v>
       </c>
       <c r="B50" t="n">
-        <v>98385</v>
+        <v>98491</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,46 +6013,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721173</v>
+        <v>721572</v>
       </c>
       <c r="R50" t="n">
-        <v>6380248</v>
+        <v>6380434</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6113,10 +6104,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127265507</v>
+        <v>127265472</v>
       </c>
       <c r="B51" t="n">
-        <v>98385</v>
+        <v>98491</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,21 +6115,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6157,13 +6148,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721307</v>
+        <v>721232</v>
       </c>
       <c r="R51" t="n">
-        <v>6380360</v>
+        <v>6380313</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6224,10 +6215,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127265593</v>
+        <v>127265628</v>
       </c>
       <c r="B52" t="n">
-        <v>98490</v>
+        <v>98386</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,37 +6226,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721572</v>
+        <v>721173</v>
       </c>
       <c r="R52" t="n">
-        <v>6380434</v>
+        <v>6380248</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127265472</v>
+        <v>127265507</v>
       </c>
       <c r="B53" t="n">
-        <v>98490</v>
+        <v>98386</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6370,13 +6370,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721232</v>
+        <v>721307</v>
       </c>
       <c r="R53" t="n">
-        <v>6380313</v>
+        <v>6380360</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6437,64 +6437,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B54" t="n">
-        <v>43235</v>
+        <v>106066</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R54" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,45 +6539,64 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B55" t="n">
-        <v>106065</v>
+        <v>43235</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R55" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6660,32 +6660,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265622</v>
+        <v>127265494</v>
       </c>
       <c r="B56" t="n">
-        <v>103923</v>
+        <v>98490</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220164</v>
+        <v>219862</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6700,17 +6700,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721252</v>
+        <v>721247</v>
       </c>
       <c r="R56" t="n">
-        <v>6380274</v>
+        <v>6380342</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6771,35 +6771,44 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265481</v>
+        <v>127265484</v>
       </c>
       <c r="B57" t="n">
-        <v>109294</v>
+        <v>98386</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
@@ -6873,48 +6882,57 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265471</v>
+        <v>127265622</v>
       </c>
       <c r="B58" t="n">
-        <v>106065</v>
+        <v>103924</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220785</v>
+        <v>220164</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721232</v>
+        <v>721252</v>
       </c>
       <c r="R58" t="n">
-        <v>6380313</v>
+        <v>6380274</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6975,44 +6993,35 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265484</v>
+        <v>127265481</v>
       </c>
       <c r="B59" t="n">
-        <v>98385</v>
+        <v>109295</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
@@ -7086,54 +7095,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265494</v>
+        <v>127265471</v>
       </c>
       <c r="B60" t="n">
-        <v>98489</v>
+        <v>106066</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721247</v>
+        <v>721232</v>
       </c>
       <c r="R60" t="n">
-        <v>6380342</v>
+        <v>6380313</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7197,45 +7197,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265505</v>
+        <v>127265495</v>
       </c>
       <c r="B61" t="n">
-        <v>106065</v>
+        <v>98446</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721284</v>
+        <v>721247</v>
       </c>
       <c r="R61" t="n">
-        <v>6380359</v>
+        <v>6380342</v>
       </c>
       <c r="S61" t="n">
         <v>7</v>
@@ -7299,48 +7308,62 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265488</v>
+        <v>127265617</v>
       </c>
       <c r="B62" t="n">
-        <v>106065</v>
+        <v>98490</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721231</v>
+        <v>721357</v>
       </c>
       <c r="R62" t="n">
-        <v>6380342</v>
+        <v>6380338</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7401,37 +7424,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265533</v>
+        <v>127265517</v>
       </c>
       <c r="B63" t="n">
-        <v>99218</v>
+        <v>98446</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7445,10 +7468,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721484</v>
+        <v>721330</v>
       </c>
       <c r="R63" t="n">
-        <v>6380450</v>
+        <v>6380365</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7512,10 +7535,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265474</v>
+        <v>127265504</v>
       </c>
       <c r="B64" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7542,7 +7565,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7556,10 +7579,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721232</v>
+        <v>721272</v>
       </c>
       <c r="R64" t="n">
-        <v>6380313</v>
+        <v>6380356</v>
       </c>
       <c r="S64" t="n">
         <v>7</v>
@@ -7623,10 +7646,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265504</v>
+        <v>127265474</v>
       </c>
       <c r="B65" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7653,7 +7676,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7667,10 +7690,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721272</v>
+        <v>721232</v>
       </c>
       <c r="R65" t="n">
-        <v>6380356</v>
+        <v>6380313</v>
       </c>
       <c r="S65" t="n">
         <v>7</v>
@@ -7737,7 +7760,7 @@
         <v>127265546</v>
       </c>
       <c r="B66" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7845,32 +7868,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265495</v>
+        <v>127265533</v>
       </c>
       <c r="B67" t="n">
-        <v>98445</v>
+        <v>99219</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>222361</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7885,17 +7908,17 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721247</v>
+        <v>721484</v>
       </c>
       <c r="R67" t="n">
-        <v>6380342</v>
+        <v>6380450</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7956,62 +7979,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265617</v>
+        <v>127265505</v>
       </c>
       <c r="B68" t="n">
-        <v>98489</v>
+        <v>106066</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721357</v>
+        <v>721284</v>
       </c>
       <c r="R68" t="n">
-        <v>6380338</v>
+        <v>6380359</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8072,57 +8081,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265517</v>
+        <v>127265488</v>
       </c>
       <c r="B69" t="n">
-        <v>98445</v>
+        <v>106066</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721330</v>
+        <v>721231</v>
       </c>
       <c r="R69" t="n">
-        <v>6380365</v>
+        <v>6380342</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8183,10 +8183,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127265525</v>
+        <v>127265476</v>
       </c>
       <c r="B70" t="n">
-        <v>98445</v>
+        <v>98386</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,26 +8194,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8223,17 +8223,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>721433</v>
+        <v>721209</v>
       </c>
       <c r="R70" t="n">
-        <v>6380417</v>
+        <v>6380333</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8263,6 +8263,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8294,10 +8299,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127265476</v>
+        <v>127265525</v>
       </c>
       <c r="B71" t="n">
-        <v>98385</v>
+        <v>98446</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8305,26 +8310,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8334,17 +8339,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>721209</v>
+        <v>721433</v>
       </c>
       <c r="R71" t="n">
-        <v>6380333</v>
+        <v>6380417</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8374,11 +8379,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8410,45 +8410,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265526</v>
+        <v>127265586</v>
       </c>
       <c r="B72" t="n">
-        <v>109294</v>
+        <v>98491</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721433</v>
+        <v>721591</v>
       </c>
       <c r="R72" t="n">
-        <v>6380417</v>
+        <v>6380497</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8481,11 +8490,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8517,54 +8521,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265586</v>
+        <v>127265526</v>
       </c>
       <c r="B73" t="n">
-        <v>98490</v>
+        <v>109295</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721591</v>
+        <v>721433</v>
       </c>
       <c r="R73" t="n">
-        <v>6380497</v>
+        <v>6380417</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8597,6 +8592,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8631,7 +8631,7 @@
         <v>127265528</v>
       </c>
       <c r="B74" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>127265588</v>
       </c>
       <c r="B75" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>127265535</v>
       </c>
       <c r="B76" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>127265508</v>
       </c>
       <c r="B77" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>127265513</v>
       </c>
       <c r="B78" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9291,27 +9291,27 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265605</v>
+        <v>127265493</v>
       </c>
       <c r="B80" t="n">
-        <v>109294</v>
+        <v>106066</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9322,17 +9322,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721466</v>
+        <v>721247</v>
       </c>
       <c r="R80" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9393,27 +9393,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265493</v>
+        <v>127265605</v>
       </c>
       <c r="B81" t="n">
-        <v>106065</v>
+        <v>109295</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9424,17 +9424,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R81" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>127265491</v>
       </c>
       <c r="B82" t="n">
-        <v>106065</v>
+        <v>106066</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>127265489</v>
       </c>
       <c r="B83" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9708,45 +9708,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265549</v>
+        <v>127265572</v>
       </c>
       <c r="B84" t="n">
-        <v>106065</v>
+        <v>98446</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721590</v>
+        <v>721594</v>
       </c>
       <c r="R84" t="n">
-        <v>6380571</v>
+        <v>6380563</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9792,7 +9801,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9810,10 +9819,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265511</v>
+        <v>127265549</v>
       </c>
       <c r="B85" t="n">
-        <v>106065</v>
+        <v>106066</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9841,17 +9850,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721315</v>
+        <v>721590</v>
       </c>
       <c r="R85" t="n">
-        <v>6380362</v>
+        <v>6380571</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9894,7 +9903,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9912,57 +9921,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265499</v>
+        <v>127265511</v>
       </c>
       <c r="B86" t="n">
-        <v>98385</v>
+        <v>106066</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721247</v>
+        <v>721315</v>
       </c>
       <c r="R86" t="n">
-        <v>6380342</v>
+        <v>6380362</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10023,10 +10023,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127265572</v>
+        <v>127265499</v>
       </c>
       <c r="B87" t="n">
-        <v>98445</v>
+        <v>98386</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10034,26 +10034,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10063,17 +10063,17 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>721594</v>
+        <v>721247</v>
       </c>
       <c r="R87" t="n">
-        <v>6380563</v>
+        <v>6380342</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>127265483</v>
       </c>
       <c r="B88" t="n">
-        <v>106065</v>
+        <v>106066</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265519</v>
+        <v>127265500</v>
       </c>
       <c r="B89" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10264,20 +10264,29 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721330</v>
+        <v>721263</v>
       </c>
       <c r="R89" t="n">
-        <v>6380365</v>
+        <v>6380356</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10338,10 +10347,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265506</v>
+        <v>127265519</v>
       </c>
       <c r="B90" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10366,29 +10375,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721284</v>
+        <v>721330</v>
       </c>
       <c r="R90" t="n">
-        <v>6380359</v>
+        <v>6380365</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10449,10 +10449,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127265500</v>
+        <v>127265506</v>
       </c>
       <c r="B91" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10493,10 +10493,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>721263</v>
+        <v>721284</v>
       </c>
       <c r="R91" t="n">
-        <v>6380356</v>
+        <v>6380359</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2432,57 +2432,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265479</v>
+        <v>127265600</v>
       </c>
       <c r="B17" t="n">
-        <v>98386</v>
+        <v>109295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721212</v>
+        <v>721547</v>
       </c>
       <c r="R17" t="n">
-        <v>6380346</v>
+        <v>6380409</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2543,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265530</v>
+        <v>127265479</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,26 +2545,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223621</v>
+        <v>223591</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2583,17 +2574,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721463</v>
+        <v>721212</v>
       </c>
       <c r="R18" t="n">
-        <v>6380440</v>
+        <v>6380346</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2654,45 +2645,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265532</v>
+        <v>127265530</v>
       </c>
       <c r="B19" t="n">
-        <v>106066</v>
+        <v>98504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>223621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721484</v>
+        <v>721463</v>
       </c>
       <c r="R19" t="n">
-        <v>6380450</v>
+        <v>6380440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265540</v>
+        <v>127265532</v>
       </c>
       <c r="B20" t="n">
         <v>106066</v>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721546</v>
+        <v>721484</v>
       </c>
       <c r="R20" t="n">
-        <v>6380552</v>
+        <v>6380450</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2858,45 +2858,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265600</v>
+        <v>127265587</v>
       </c>
       <c r="B21" t="n">
-        <v>109295</v>
+        <v>105506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721547</v>
+        <v>721591</v>
       </c>
       <c r="R21" t="n">
-        <v>6380409</v>
+        <v>6380497</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,54 +2969,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265587</v>
+        <v>127265540</v>
       </c>
       <c r="B22" t="n">
-        <v>105506</v>
+        <v>106066</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721591</v>
+        <v>721546</v>
       </c>
       <c r="R22" t="n">
-        <v>6380497</v>
+        <v>6380552</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3071,57 +3071,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265590</v>
+        <v>127265496</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>109295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721580</v>
+        <v>721247</v>
       </c>
       <c r="R23" t="n">
-        <v>6380472</v>
+        <v>6380342</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3153,11 +3144,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3169,7 +3155,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3298,48 +3284,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265496</v>
+        <v>127265590</v>
       </c>
       <c r="B25" t="n">
-        <v>109295</v>
+        <v>98504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721247</v>
+        <v>721580</v>
       </c>
       <c r="R25" t="n">
-        <v>6380342</v>
+        <v>6380472</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3371,6 +3366,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3400,57 +3400,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265624</v>
+        <v>127265503</v>
       </c>
       <c r="B26" t="n">
-        <v>98386</v>
+        <v>106066</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721199</v>
+        <v>721272</v>
       </c>
       <c r="R26" t="n">
-        <v>6380248</v>
+        <v>6380356</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,10 +3502,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265473</v>
+        <v>127265624</v>
       </c>
       <c r="B27" t="n">
-        <v>98446</v>
+        <v>98386</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,26 +3513,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3551,17 +3542,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721232</v>
+        <v>721199</v>
       </c>
       <c r="R27" t="n">
-        <v>6380313</v>
+        <v>6380248</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3622,10 +3613,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265475</v>
+        <v>127265473</v>
       </c>
       <c r="B28" t="n">
-        <v>98491</v>
+        <v>98446</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,26 +3624,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3666,13 +3657,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721209</v>
+        <v>721232</v>
       </c>
       <c r="R28" t="n">
-        <v>6380333</v>
+        <v>6380313</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3733,48 +3724,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265503</v>
+        <v>127265475</v>
       </c>
       <c r="B29" t="n">
-        <v>106066</v>
+        <v>98491</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721272</v>
+        <v>721209</v>
       </c>
       <c r="R29" t="n">
-        <v>6380356</v>
+        <v>6380333</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265548</v>
+        <v>127265598</v>
       </c>
       <c r="B30" t="n">
-        <v>99685</v>
+        <v>98491</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3846,31 +3846,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>174</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3879,13 +3879,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721578</v>
+        <v>721557</v>
       </c>
       <c r="R30" t="n">
-        <v>6380576</v>
+        <v>6380422</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,11 +3917,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3933,7 +3928,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3951,7 +3946,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265598</v>
+        <v>127265606</v>
       </c>
       <c r="B31" t="n">
         <v>98491</v>
@@ -3981,7 +3976,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3995,10 +3990,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721557</v>
+        <v>721475</v>
       </c>
       <c r="R31" t="n">
-        <v>6380422</v>
+        <v>6380396</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,7 +4039,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4062,10 +4057,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265606</v>
+        <v>127265548</v>
       </c>
       <c r="B32" t="n">
-        <v>98491</v>
+        <v>99685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,31 +4068,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>174</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4106,13 +4101,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721475</v>
+        <v>721578</v>
       </c>
       <c r="R32" t="n">
-        <v>6380396</v>
+        <v>6380576</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4144,6 +4139,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127265612</v>
+        <v>127265541</v>
       </c>
       <c r="B37" t="n">
-        <v>98505</v>
+        <v>98386</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,43 +4615,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721424</v>
+        <v>721546</v>
       </c>
       <c r="R37" t="n">
-        <v>6380372</v>
+        <v>6380552</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4697,7 +4688,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4928,10 +4919,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265541</v>
+        <v>127265612</v>
       </c>
       <c r="B40" t="n">
-        <v>98386</v>
+        <v>98505</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4939,34 +4930,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721546</v>
+        <v>721424</v>
       </c>
       <c r="R40" t="n">
-        <v>6380552</v>
+        <v>6380372</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5030,48 +5030,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127265579</v>
+        <v>127265623</v>
       </c>
       <c r="B41" t="n">
-        <v>106066</v>
+        <v>98446</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721577</v>
+        <v>721199</v>
       </c>
       <c r="R41" t="n">
-        <v>6380550</v>
+        <v>6380248</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5132,7 +5141,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265545</v>
+        <v>127265579</v>
       </c>
       <c r="B42" t="n">
         <v>106066</v>
@@ -5163,14 +5172,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721560</v>
+        <v>721577</v>
       </c>
       <c r="R42" t="n">
-        <v>6380582</v>
+        <v>6380550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5216,7 +5225,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5234,57 +5243,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127265623</v>
+        <v>127265545</v>
       </c>
       <c r="B43" t="n">
-        <v>98446</v>
+        <v>106066</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721199</v>
+        <v>721560</v>
       </c>
       <c r="R43" t="n">
-        <v>6380248</v>
+        <v>6380582</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6437,45 +6437,64 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127265583</v>
+        <v>127296631</v>
       </c>
       <c r="B54" t="n">
-        <v>106066</v>
+        <v>43235</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721601</v>
+        <v>721557</v>
       </c>
       <c r="R54" t="n">
-        <v>6380518</v>
+        <v>6380495</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6539,64 +6558,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127296631</v>
+        <v>127265583</v>
       </c>
       <c r="B55" t="n">
-        <v>43235</v>
+        <v>106066</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721557</v>
+        <v>721601</v>
       </c>
       <c r="R55" t="n">
-        <v>6380495</v>
+        <v>6380518</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6771,37 +6771,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265484</v>
+        <v>127265622</v>
       </c>
       <c r="B57" t="n">
-        <v>98386</v>
+        <v>103924</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223591</v>
+        <v>220164</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721220</v>
+        <v>721252</v>
       </c>
       <c r="R57" t="n">
-        <v>6380355</v>
+        <v>6380274</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6882,10 +6882,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265622</v>
+        <v>127265481</v>
       </c>
       <c r="B58" t="n">
-        <v>103924</v>
+        <v>109295</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6893,46 +6893,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721252</v>
+        <v>721220</v>
       </c>
       <c r="R58" t="n">
-        <v>6380274</v>
+        <v>6380355</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6993,27 +6984,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265481</v>
+        <v>127265471</v>
       </c>
       <c r="B59" t="n">
-        <v>109295</v>
+        <v>106066</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7028,10 +7019,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R59" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7095,45 +7086,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265471</v>
+        <v>127265484</v>
       </c>
       <c r="B60" t="n">
-        <v>106066</v>
+        <v>98386</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721232</v>
+        <v>721220</v>
       </c>
       <c r="R60" t="n">
-        <v>6380313</v>
+        <v>6380355</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7535,37 +7535,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265504</v>
+        <v>127265533</v>
       </c>
       <c r="B64" t="n">
-        <v>98386</v>
+        <v>99219</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7575,17 +7575,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721272</v>
+        <v>721484</v>
       </c>
       <c r="R64" t="n">
-        <v>6380356</v>
+        <v>6380450</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7646,54 +7646,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265474</v>
+        <v>127265505</v>
       </c>
       <c r="B65" t="n">
-        <v>98386</v>
+        <v>106066</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721232</v>
+        <v>721284</v>
       </c>
       <c r="R65" t="n">
-        <v>6380313</v>
+        <v>6380359</v>
       </c>
       <c r="S65" t="n">
         <v>7</v>
@@ -7757,57 +7748,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265546</v>
+        <v>127265488</v>
       </c>
       <c r="B66" t="n">
-        <v>98386</v>
+        <v>106066</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721560</v>
+        <v>721231</v>
       </c>
       <c r="R66" t="n">
-        <v>6380582</v>
+        <v>6380342</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7850,7 +7832,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7868,37 +7850,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265533</v>
+        <v>127265474</v>
       </c>
       <c r="B67" t="n">
-        <v>99219</v>
+        <v>98386</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222361</v>
+        <v>223591</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7908,17 +7890,17 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721484</v>
+        <v>721232</v>
       </c>
       <c r="R67" t="n">
-        <v>6380450</v>
+        <v>6380313</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7979,45 +7961,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265505</v>
+        <v>127265504</v>
       </c>
       <c r="B68" t="n">
-        <v>106066</v>
+        <v>98386</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721284</v>
+        <v>721272</v>
       </c>
       <c r="R68" t="n">
-        <v>6380359</v>
+        <v>6380356</v>
       </c>
       <c r="S68" t="n">
         <v>7</v>
@@ -8081,48 +8072,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265488</v>
+        <v>127265546</v>
       </c>
       <c r="B69" t="n">
-        <v>106066</v>
+        <v>98386</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721231</v>
+        <v>721560</v>
       </c>
       <c r="R69" t="n">
-        <v>6380342</v>
+        <v>6380582</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127265476</v>
+        <v>127265525</v>
       </c>
       <c r="B70" t="n">
-        <v>98386</v>
+        <v>98446</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,26 +8194,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8223,17 +8223,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>721209</v>
+        <v>721433</v>
       </c>
       <c r="R70" t="n">
-        <v>6380333</v>
+        <v>6380417</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8263,11 +8263,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8299,10 +8294,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127265525</v>
+        <v>127265476</v>
       </c>
       <c r="B71" t="n">
-        <v>98446</v>
+        <v>98386</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8310,26 +8305,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8339,17 +8334,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>721433</v>
+        <v>721209</v>
       </c>
       <c r="R71" t="n">
-        <v>6380417</v>
+        <v>6380333</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8379,6 +8374,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Varav 1 närmast vitblommig med ytterst svaga markeringar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8739,45 +8739,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B75" t="n">
-        <v>109295</v>
+        <v>98491</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R75" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8841,54 +8850,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B76" t="n">
-        <v>98491</v>
+        <v>109295</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R76" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8952,57 +8952,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127265508</v>
+        <v>127265513</v>
       </c>
       <c r="B77" t="n">
-        <v>98446</v>
+        <v>109295</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721307</v>
+        <v>721315</v>
       </c>
       <c r="R77" t="n">
-        <v>6380360</v>
+        <v>6380362</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9063,48 +9054,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127265513</v>
+        <v>127265508</v>
       </c>
       <c r="B78" t="n">
-        <v>109295</v>
+        <v>98446</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721315</v>
+        <v>721307</v>
       </c>
       <c r="R78" t="n">
-        <v>6380362</v>
+        <v>6380360</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9291,27 +9291,27 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265493</v>
+        <v>127265605</v>
       </c>
       <c r="B80" t="n">
-        <v>106066</v>
+        <v>109295</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9322,17 +9322,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R80" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9393,27 +9393,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265605</v>
+        <v>127265493</v>
       </c>
       <c r="B81" t="n">
-        <v>109295</v>
+        <v>106066</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9424,17 +9424,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721466</v>
+        <v>721247</v>
       </c>
       <c r="R81" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127265500</v>
+        <v>127265519</v>
       </c>
       <c r="B89" t="n">
         <v>98386</v>
@@ -10264,29 +10264,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>721263</v>
+        <v>721330</v>
       </c>
       <c r="R89" t="n">
-        <v>6380356</v>
+        <v>6380365</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10347,7 +10338,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265519</v>
+        <v>127265500</v>
       </c>
       <c r="B90" t="n">
         <v>98386</v>
@@ -10375,20 +10366,29 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721330</v>
+        <v>721263</v>
       </c>
       <c r="R90" t="n">
-        <v>6380365</v>
+        <v>6380356</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,57 +2099,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265497</v>
+        <v>127265540</v>
       </c>
       <c r="B14" t="n">
-        <v>98491</v>
+        <v>106067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721247</v>
+        <v>721546</v>
       </c>
       <c r="R14" t="n">
-        <v>6380342</v>
+        <v>6380552</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2192,7 +2183,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2210,54 +2201,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265518</v>
+        <v>127265600</v>
       </c>
       <c r="B15" t="n">
-        <v>98491</v>
+        <v>109296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721330</v>
+        <v>721547</v>
       </c>
       <c r="R15" t="n">
-        <v>6380365</v>
+        <v>6380409</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265492</v>
+        <v>127265497</v>
       </c>
       <c r="B16" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2333,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2365,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721239</v>
+        <v>721247</v>
       </c>
       <c r="R16" t="n">
-        <v>6380330</v>
+        <v>6380342</v>
       </c>
       <c r="S16" t="n">
         <v>7</v>
@@ -2432,27 +2414,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265600</v>
+        <v>127265532</v>
       </c>
       <c r="B17" t="n">
-        <v>109295</v>
+        <v>106067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2463,14 +2445,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721547</v>
+        <v>721484</v>
       </c>
       <c r="R17" t="n">
-        <v>6380409</v>
+        <v>6380450</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265479</v>
+        <v>127265518</v>
       </c>
       <c r="B18" t="n">
-        <v>98386</v>
+        <v>98492</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,26 +2527,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2574,17 +2556,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721212</v>
+        <v>721330</v>
       </c>
       <c r="R18" t="n">
-        <v>6380346</v>
+        <v>6380365</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2645,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265530</v>
+        <v>127265492</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98492</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,21 +2638,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2685,17 +2667,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721463</v>
+        <v>721239</v>
       </c>
       <c r="R19" t="n">
-        <v>6380440</v>
+        <v>6380330</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2756,48 +2738,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265532</v>
+        <v>127265479</v>
       </c>
       <c r="B20" t="n">
-        <v>106066</v>
+        <v>98387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721484</v>
+        <v>721212</v>
       </c>
       <c r="R20" t="n">
-        <v>6380450</v>
+        <v>6380346</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2858,10 +2849,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265587</v>
+        <v>127265530</v>
       </c>
       <c r="B21" t="n">
-        <v>105506</v>
+        <v>98505</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,21 +2860,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>223621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2898,14 +2889,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721591</v>
+        <v>721463</v>
       </c>
       <c r="R21" t="n">
-        <v>6380497</v>
+        <v>6380440</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,45 +2960,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265540</v>
+        <v>127265587</v>
       </c>
       <c r="B22" t="n">
-        <v>106066</v>
+        <v>105507</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721546</v>
+        <v>721591</v>
       </c>
       <c r="R22" t="n">
-        <v>6380552</v>
+        <v>6380497</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
         <v>127265496</v>
       </c>
       <c r="B23" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127265610</v>
+        <v>127265590</v>
       </c>
       <c r="B24" t="n">
-        <v>98386</v>
+        <v>98505</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,21 +3184,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721466</v>
+        <v>721580</v>
       </c>
       <c r="R24" t="n">
-        <v>6380394</v>
+        <v>6380472</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,6 +3255,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tallplantge 50 m O.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3266,7 +3271,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3284,10 +3289,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265590</v>
+        <v>127265610</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>98387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3295,21 +3300,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223621</v>
+        <v>223591</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3328,10 +3333,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721580</v>
+        <v>721466</v>
       </c>
       <c r="R25" t="n">
-        <v>6380472</v>
+        <v>6380394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3366,11 +3371,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tallplantge 50 m O.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog gles med döda tallar och kjolgranar..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3400,48 +3400,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265503</v>
+        <v>127265475</v>
       </c>
       <c r="B26" t="n">
-        <v>106066</v>
+        <v>98492</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721272</v>
+        <v>721209</v>
       </c>
       <c r="R26" t="n">
-        <v>6380356</v>
+        <v>6380333</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3502,57 +3511,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265624</v>
+        <v>127265503</v>
       </c>
       <c r="B27" t="n">
-        <v>98386</v>
+        <v>106067</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721199</v>
+        <v>721272</v>
       </c>
       <c r="R27" t="n">
-        <v>6380248</v>
+        <v>6380356</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>127265473</v>
       </c>
       <c r="B28" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265475</v>
+        <v>127265624</v>
       </c>
       <c r="B29" t="n">
-        <v>98491</v>
+        <v>98387</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3735,21 +3735,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721209</v>
+        <v>721199</v>
       </c>
       <c r="R29" t="n">
-        <v>6380333</v>
+        <v>6380248</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265598</v>
+        <v>127265548</v>
       </c>
       <c r="B30" t="n">
-        <v>98491</v>
+        <v>99686</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3846,31 +3846,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>174</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3879,13 +3879,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721557</v>
+        <v>721578</v>
       </c>
       <c r="R30" t="n">
-        <v>6380422</v>
+        <v>6380576</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,6 +3917,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3928,7 +3933,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3946,57 +3951,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265606</v>
+        <v>127265486</v>
       </c>
       <c r="B31" t="n">
-        <v>98491</v>
+        <v>109296</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721475</v>
+        <v>721231</v>
       </c>
       <c r="R31" t="n">
-        <v>6380396</v>
+        <v>6380342</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4057,10 +4053,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127265548</v>
+        <v>127265606</v>
       </c>
       <c r="B32" t="n">
-        <v>99685</v>
+        <v>98492</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,31 +4064,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>174</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4101,13 +4097,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721578</v>
+        <v>721475</v>
       </c>
       <c r="R32" t="n">
-        <v>6380576</v>
+        <v>6380396</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4139,11 +4135,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4155,7 +4146,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4173,48 +4164,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265486</v>
+        <v>127265598</v>
       </c>
       <c r="B33" t="n">
-        <v>109295</v>
+        <v>98492</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721231</v>
+        <v>721557</v>
       </c>
       <c r="R33" t="n">
-        <v>6380342</v>
+        <v>6380422</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127296661</v>
+        <v>127265584</v>
       </c>
       <c r="B34" t="n">
-        <v>58349</v>
+        <v>98492</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,46 +4286,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>219847</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721560</v>
+        <v>721601</v>
       </c>
       <c r="R34" t="n">
-        <v>6380582</v>
+        <v>6380518</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4386,54 +4386,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127265584</v>
+        <v>127265594</v>
       </c>
       <c r="B35" t="n">
-        <v>98491</v>
+        <v>109296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721601</v>
+        <v>721572</v>
       </c>
       <c r="R35" t="n">
-        <v>6380518</v>
+        <v>6380434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,6 +4457,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,48 +4493,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127265594</v>
+        <v>127296661</v>
       </c>
       <c r="B36" t="n">
-        <v>109295</v>
+        <v>58349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721572</v>
+        <v>721560</v>
       </c>
       <c r="R36" t="n">
-        <v>6380434</v>
+        <v>6380582</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,11 +4575,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127265541</v>
+        <v>127265612</v>
       </c>
       <c r="B37" t="n">
-        <v>98386</v>
+        <v>98506</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,34 +4615,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721546</v>
+        <v>721424</v>
       </c>
       <c r="R37" t="n">
-        <v>6380552</v>
+        <v>6380372</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,7 +4697,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4709,7 +4718,7 @@
         <v>127265566</v>
       </c>
       <c r="B38" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4811,7 +4820,7 @@
         <v>127265582</v>
       </c>
       <c r="B39" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4919,10 +4928,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265612</v>
+        <v>127265541</v>
       </c>
       <c r="B40" t="n">
-        <v>98505</v>
+        <v>98387</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,43 +4939,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721424</v>
+        <v>721546</v>
       </c>
       <c r="R40" t="n">
-        <v>6380372</v>
+        <v>6380552</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5030,57 +5030,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127265623</v>
+        <v>127265579</v>
       </c>
       <c r="B41" t="n">
-        <v>98446</v>
+        <v>106067</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721199</v>
+        <v>721577</v>
       </c>
       <c r="R41" t="n">
-        <v>6380248</v>
+        <v>6380550</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5141,48 +5132,57 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265579</v>
+        <v>127265623</v>
       </c>
       <c r="B42" t="n">
-        <v>106066</v>
+        <v>98447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721577</v>
+        <v>721199</v>
       </c>
       <c r="R42" t="n">
-        <v>6380550</v>
+        <v>6380248</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>127265545</v>
       </c>
       <c r="B43" t="n">
-        <v>106066</v>
+        <v>106067</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265515</v>
+        <v>127265571</v>
       </c>
       <c r="B44" t="n">
-        <v>98446</v>
+        <v>98387</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5356,26 +5356,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5385,17 +5385,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R44" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5456,48 +5456,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127265534</v>
+        <v>127265515</v>
       </c>
       <c r="B45" t="n">
-        <v>109295</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721493</v>
+        <v>721315</v>
       </c>
       <c r="R45" t="n">
-        <v>6380446</v>
+        <v>6380362</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5558,54 +5567,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265571</v>
+        <v>127265534</v>
       </c>
       <c r="B46" t="n">
-        <v>98386</v>
+        <v>109296</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721594</v>
+        <v>721493</v>
       </c>
       <c r="R46" t="n">
-        <v>6380563</v>
+        <v>6380446</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127265478</v>
+        <v>127265626</v>
       </c>
       <c r="B47" t="n">
-        <v>98446</v>
+        <v>98387</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,26 +5680,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721212</v>
+        <v>721183</v>
       </c>
       <c r="R47" t="n">
-        <v>6380346</v>
+        <v>6380248</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127265626</v>
+        <v>127265597</v>
       </c>
       <c r="B48" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5824,13 +5824,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721183</v>
+        <v>721557</v>
       </c>
       <c r="R48" t="n">
-        <v>6380248</v>
+        <v>6380422</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127265597</v>
+        <v>127265478</v>
       </c>
       <c r="B49" t="n">
-        <v>98386</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,26 +5902,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721557</v>
+        <v>721212</v>
       </c>
       <c r="R49" t="n">
-        <v>6380422</v>
+        <v>6380346</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6005,7 +6005,7 @@
         <v>127265593</v>
       </c>
       <c r="B50" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>127265472</v>
       </c>
       <c r="B51" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>127265628</v>
       </c>
       <c r="B52" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>127265507</v>
       </c>
       <c r="B53" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>127265583</v>
       </c>
       <c r="B55" t="n">
-        <v>106066</v>
+        <v>106067</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6660,32 +6660,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265494</v>
+        <v>127265622</v>
       </c>
       <c r="B56" t="n">
-        <v>98490</v>
+        <v>103925</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219862</v>
+        <v>220164</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6700,17 +6700,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721247</v>
+        <v>721252</v>
       </c>
       <c r="R56" t="n">
-        <v>6380342</v>
+        <v>6380274</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6771,57 +6771,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265622</v>
+        <v>127265471</v>
       </c>
       <c r="B57" t="n">
-        <v>103924</v>
+        <v>106067</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220164</v>
+        <v>220785</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721252</v>
+        <v>721232</v>
       </c>
       <c r="R57" t="n">
-        <v>6380274</v>
+        <v>6380313</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6882,45 +6873,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265481</v>
+        <v>127265494</v>
       </c>
       <c r="B58" t="n">
-        <v>109295</v>
+        <v>98491</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721220</v>
+        <v>721247</v>
       </c>
       <c r="R58" t="n">
-        <v>6380355</v>
+        <v>6380342</v>
       </c>
       <c r="S58" t="n">
         <v>7</v>
@@ -6984,27 +6984,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127265471</v>
+        <v>127265481</v>
       </c>
       <c r="B59" t="n">
-        <v>106066</v>
+        <v>109296</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7019,10 +7019,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721232</v>
+        <v>721220</v>
       </c>
       <c r="R59" t="n">
-        <v>6380313</v>
+        <v>6380355</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7089,7 +7089,7 @@
         <v>127265484</v>
       </c>
       <c r="B60" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7197,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265495</v>
+        <v>127265617</v>
       </c>
       <c r="B61" t="n">
-        <v>98446</v>
+        <v>98491</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7208,26 +7208,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7235,19 +7235,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721247</v>
+        <v>721357</v>
       </c>
       <c r="R61" t="n">
-        <v>6380342</v>
+        <v>6380338</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7308,10 +7313,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265617</v>
+        <v>127265517</v>
       </c>
       <c r="B62" t="n">
-        <v>98490</v>
+        <v>98447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7319,26 +7324,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7346,24 +7351,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721357</v>
+        <v>721330</v>
       </c>
       <c r="R62" t="n">
-        <v>6380338</v>
+        <v>6380365</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7424,57 +7424,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265517</v>
+        <v>127265505</v>
       </c>
       <c r="B63" t="n">
-        <v>98446</v>
+        <v>106067</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721330</v>
+        <v>721284</v>
       </c>
       <c r="R63" t="n">
-        <v>6380365</v>
+        <v>6380359</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7535,27 +7526,27 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265533</v>
+        <v>127265488</v>
       </c>
       <c r="B64" t="n">
-        <v>99219</v>
+        <v>106067</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222361</v>
+        <v>220785</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7563,29 +7554,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721484</v>
+        <v>721231</v>
       </c>
       <c r="R64" t="n">
-        <v>6380450</v>
+        <v>6380342</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7646,45 +7628,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127265505</v>
+        <v>127265495</v>
       </c>
       <c r="B65" t="n">
-        <v>106066</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721284</v>
+        <v>721247</v>
       </c>
       <c r="R65" t="n">
-        <v>6380359</v>
+        <v>6380342</v>
       </c>
       <c r="S65" t="n">
         <v>7</v>
@@ -7748,48 +7739,57 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265488</v>
+        <v>127265504</v>
       </c>
       <c r="B66" t="n">
-        <v>106066</v>
+        <v>98387</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721231</v>
+        <v>721272</v>
       </c>
       <c r="R66" t="n">
-        <v>6380342</v>
+        <v>6380356</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>127265474</v>
       </c>
       <c r="B67" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7961,10 +7961,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265504</v>
+        <v>127265546</v>
       </c>
       <c r="B68" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8001,17 +8001,17 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721272</v>
+        <v>721560</v>
       </c>
       <c r="R68" t="n">
-        <v>6380356</v>
+        <v>6380582</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8072,37 +8072,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265546</v>
+        <v>127265533</v>
       </c>
       <c r="B69" t="n">
-        <v>98386</v>
+        <v>99220</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721560</v>
+        <v>721484</v>
       </c>
       <c r="R69" t="n">
-        <v>6380582</v>
+        <v>6380450</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8186,7 +8186,7 @@
         <v>127265525</v>
       </c>
       <c r="B70" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>127265476</v>
       </c>
       <c r="B71" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>127265586</v>
       </c>
       <c r="B72" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>127265526</v>
       </c>
       <c r="B73" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>127265528</v>
       </c>
       <c r="B74" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8739,54 +8739,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B75" t="n">
-        <v>98491</v>
+        <v>109296</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R75" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8850,45 +8841,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B76" t="n">
-        <v>109295</v>
+        <v>98492</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R76" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8955,7 +8955,7 @@
         <v>127265513</v>
       </c>
       <c r="B77" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>127265508</v>
       </c>
       <c r="B78" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9165,67 +9165,57 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127296632</v>
+        <v>127265489</v>
       </c>
       <c r="B79" t="n">
-        <v>43235</v>
+        <v>98387</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>101242</v>
+        <v>223591</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>721578</v>
+        <v>721231</v>
       </c>
       <c r="R79" t="n">
-        <v>6380530</v>
+        <v>6380342</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9257,11 +9247,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Lundstarr rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9273,7 +9258,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9291,27 +9276,27 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265605</v>
+        <v>127265491</v>
       </c>
       <c r="B80" t="n">
-        <v>109295</v>
+        <v>106067</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9322,17 +9307,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721466</v>
+        <v>721239</v>
       </c>
       <c r="R80" t="n">
-        <v>6380394</v>
+        <v>6380330</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9396,7 +9381,7 @@
         <v>127265493</v>
       </c>
       <c r="B81" t="n">
-        <v>106066</v>
+        <v>106067</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9495,27 +9480,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265491</v>
+        <v>127265605</v>
       </c>
       <c r="B82" t="n">
-        <v>106066</v>
+        <v>109296</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9526,17 +9511,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721239</v>
+        <v>721466</v>
       </c>
       <c r="R82" t="n">
-        <v>6380330</v>
+        <v>6380394</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9597,57 +9582,67 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127265489</v>
+        <v>127296632</v>
       </c>
       <c r="B83" t="n">
-        <v>98386</v>
+        <v>43235</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721231</v>
+        <v>721578</v>
       </c>
       <c r="R83" t="n">
-        <v>6380342</v>
+        <v>6380530</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9679,6 +9674,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lundstarr rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk med blåtåtel och lundstarr.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9708,54 +9708,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127265572</v>
+        <v>127265549</v>
       </c>
       <c r="B84" t="n">
-        <v>98446</v>
+        <v>106067</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721594</v>
+        <v>721590</v>
       </c>
       <c r="R84" t="n">
-        <v>6380563</v>
+        <v>6380571</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9801,7 +9792,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9819,10 +9810,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265549</v>
+        <v>127265511</v>
       </c>
       <c r="B85" t="n">
-        <v>106066</v>
+        <v>106067</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9850,17 +9841,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721590</v>
+        <v>721315</v>
       </c>
       <c r="R85" t="n">
-        <v>6380571</v>
+        <v>6380362</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9903,7 +9894,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9921,48 +9912,57 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265511</v>
+        <v>127265572</v>
       </c>
       <c r="B86" t="n">
-        <v>106066</v>
+        <v>98447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721315</v>
+        <v>721594</v>
       </c>
       <c r="R86" t="n">
-        <v>6380362</v>
+        <v>6380563</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>127265499</v>
       </c>
       <c r="B87" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10134,45 +10134,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127265483</v>
+        <v>127265500</v>
       </c>
       <c r="B88" t="n">
-        <v>106066</v>
+        <v>98387</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>721220</v>
+        <v>721263</v>
       </c>
       <c r="R88" t="n">
-        <v>6380355</v>
+        <v>6380356</v>
       </c>
       <c r="S88" t="n">
         <v>7</v>
@@ -10239,7 +10248,7 @@
         <v>127265519</v>
       </c>
       <c r="B89" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10338,10 +10347,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127265500</v>
+        <v>127265506</v>
       </c>
       <c r="B90" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10368,7 +10377,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10382,10 +10391,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>721263</v>
+        <v>721284</v>
       </c>
       <c r="R90" t="n">
-        <v>6380356</v>
+        <v>6380359</v>
       </c>
       <c r="S90" t="n">
         <v>7</v>
@@ -10449,54 +10458,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127265506</v>
+        <v>127265483</v>
       </c>
       <c r="B91" t="n">
-        <v>98386</v>
+        <v>106067</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>721284</v>
+        <v>721220</v>
       </c>
       <c r="R91" t="n">
-        <v>6380359</v>
+        <v>6380355</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>

--- a/artfynd/A 8645-2025 artfynd.xlsx
+++ b/artfynd/A 8645-2025 artfynd.xlsx
@@ -2099,48 +2099,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127265540</v>
+        <v>127265497</v>
       </c>
       <c r="B14" t="n">
-        <v>106067</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721546</v>
+        <v>721247</v>
       </c>
       <c r="R14" t="n">
-        <v>6380552</v>
+        <v>6380342</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2183,7 +2192,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2201,27 +2210,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127265600</v>
+        <v>127265532</v>
       </c>
       <c r="B15" t="n">
-        <v>109296</v>
+        <v>106031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2232,14 +2241,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721547</v>
+        <v>721484</v>
       </c>
       <c r="R15" t="n">
-        <v>6380409</v>
+        <v>6380450</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2303,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127265497</v>
+        <v>127265518</v>
       </c>
       <c r="B16" t="n">
-        <v>98492</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2342,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2343,17 +2352,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721247</v>
+        <v>721330</v>
       </c>
       <c r="R16" t="n">
-        <v>6380342</v>
+        <v>6380365</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2414,45 +2423,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127265532</v>
+        <v>127265587</v>
       </c>
       <c r="B17" t="n">
-        <v>106067</v>
+        <v>105471</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220785</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721484</v>
+        <v>721591</v>
       </c>
       <c r="R17" t="n">
-        <v>6380450</v>
+        <v>6380497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2516,54 +2534,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127265518</v>
+        <v>127265540</v>
       </c>
       <c r="B18" t="n">
-        <v>98492</v>
+        <v>106031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721330</v>
+        <v>721546</v>
       </c>
       <c r="R18" t="n">
-        <v>6380365</v>
+        <v>6380552</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,7 +2618,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2627,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127265492</v>
+        <v>127265479</v>
       </c>
       <c r="B19" t="n">
-        <v>98492</v>
+        <v>98354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,26 +2647,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2671,13 +2680,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721239</v>
+        <v>721212</v>
       </c>
       <c r="R19" t="n">
-        <v>6380330</v>
+        <v>6380346</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2738,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127265479</v>
+        <v>127265530</v>
       </c>
       <c r="B20" t="n">
-        <v>98387</v>
+        <v>98472</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,26 +2758,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2778,17 +2787,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721212</v>
+        <v>721463</v>
       </c>
       <c r="R20" t="n">
-        <v>6380346</v>
+        <v>6380440</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2849,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127265530</v>
+        <v>127265492</v>
       </c>
       <c r="B21" t="n">
-        <v>98505</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,21 +2869,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2889,17 +2898,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721463</v>
+        <v>721239</v>
       </c>
       <c r="R21" t="n">
-        <v>6380440</v>
+        <v>6380330</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2960,54 +2969,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127265587</v>
+        <v>127265600</v>
       </c>
       <c r="B22" t="n">
-        <v>105507</v>
+        <v>109260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721591</v>
+        <v>721547</v>
       </c>
       <c r="R22" t="n">
-        <v>6380497</v>
+        <v>6380409</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,48 +3071,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127265496</v>
+        <v>127265610</v>
       </c>
       <c r="B23" t="n">
-        <v>109296</v>
+        <v>98354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721247</v>
+        <v>721466</v>
       </c>
       <c r="R23" t="n">
-        <v>6380342</v>
+        <v>6380394</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3176,7 +3185,7 @@
         <v>127265590</v>
       </c>
       <c r="B24" t="n">
-        <v>98505</v>
+        <v>98472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,57 +3298,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127265610</v>
+        <v>127265496</v>
       </c>
       <c r="B25" t="n">
-        <v>98387</v>
+        <v>109260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721466</v>
+        <v>721247</v>
       </c>
       <c r="R25" t="n">
-        <v>6380394</v>
+        <v>6380342</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127265475</v>
+        <v>127265624</v>
       </c>
       <c r="B26" t="n">
-        <v>98492</v>
+        <v>98354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3411,21 +3411,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3440,14 +3440,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721209</v>
+        <v>721199</v>
       </c>
       <c r="R26" t="n">
-        <v>6380333</v>
+        <v>6380248</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3511,45 +3511,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127265503</v>
+        <v>127265473</v>
       </c>
       <c r="B27" t="n">
-        <v>106067</v>
+        <v>98414</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721272</v>
+        <v>721232</v>
       </c>
       <c r="R27" t="n">
-        <v>6380356</v>
+        <v>6380313</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3613,10 +3622,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127265473</v>
+        <v>127265475</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,26 +3633,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3657,13 +3666,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721232</v>
+        <v>721209</v>
       </c>
       <c r="R28" t="n">
-        <v>6380313</v>
+        <v>6380333</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3724,57 +3733,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127265624</v>
+        <v>127265503</v>
       </c>
       <c r="B29" t="n">
-        <v>98387</v>
+        <v>106031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721199</v>
+        <v>721272</v>
       </c>
       <c r="R29" t="n">
-        <v>6380248</v>
+        <v>6380356</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127265548</v>
+        <v>127265598</v>
       </c>
       <c r="B30" t="n">
-        <v>99686</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3846,31 +3846,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>174</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3879,13 +3879,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721578</v>
+        <v>721557</v>
       </c>
       <c r="R30" t="n">
-        <v>6380576</v>
+        <v>6380422</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,11 +3917,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Varav 15 strån mot V.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3933,7 +3928,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3951,45 +3946,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127265486</v>
+        <v>127265548</v>
       </c>
       <c r="B31" t="n">
-        <v>109296</v>
+        <v>99653</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>174</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721231</v>
+        <v>721578</v>
       </c>
       <c r="R31" t="n">
-        <v>6380342</v>
+        <v>6380576</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4024,6 +4028,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Varav 15 strån mot V.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4035,7 +4044,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4056,7 +4065,7 @@
         <v>127265606</v>
       </c>
       <c r="B32" t="n">
-        <v>98492</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4164,57 +4173,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127265598</v>
+        <v>127265486</v>
       </c>
       <c r="B33" t="n">
-        <v>98492</v>
+        <v>109260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721557</v>
+        <v>721231</v>
       </c>
       <c r="R33" t="n">
-        <v>6380422</v>
+        <v>6380342</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127265584</v>
+        <v>127296661</v>
       </c>
       <c r="B34" t="n">
-        <v>98492</v>
+        <v>58334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,46 +4286,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721601</v>
+        <v>721560</v>
       </c>
       <c r="R34" t="n">
-        <v>6380518</v>
+        <v>6380582</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4389,7 +4389,7 @@
         <v>127265594</v>
       </c>
       <c r="B35" t="n">
-        <v>109296</v>
+        <v>109260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296661</v>
+        <v>127265584</v>
       </c>
       <c r="B36" t="n">
-        <v>58349</v>
+        <v>98459</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4504,46 +4504,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721560</v>
+        <v>721601</v>
       </c>
       <c r="R36" t="n">
-        <v>6380582</v>
+        <v>6380518</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127265612</v>
+        <v>127265541</v>
       </c>
       <c r="B37" t="n">
-        <v>98506</v>
+        <v>98354</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,43 +4615,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721424</v>
+        <v>721546</v>
       </c>
       <c r="R37" t="n">
-        <v>6380372</v>
+        <v>6380552</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4697,7 +4688,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4715,10 +4706,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127265566</v>
+        <v>127265612</v>
       </c>
       <c r="B38" t="n">
-        <v>98387</v>
+        <v>98473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4726,34 +4717,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721615</v>
+        <v>721424</v>
       </c>
       <c r="R38" t="n">
-        <v>6380615</v>
+        <v>6380372</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Åkant, troligen rätad med höga kanter.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127265582</v>
+        <v>127265566</v>
       </c>
       <c r="B39" t="n">
-        <v>98387</v>
+        <v>98354</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4845,26 +4845,17 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721601</v>
+        <v>721615</v>
       </c>
       <c r="R39" t="n">
-        <v>6380518</v>
+        <v>6380615</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4910,7 +4901,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Åkant, troligen rätad med höga kanter.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4928,10 +4919,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127265541</v>
+        <v>127265582</v>
       </c>
       <c r="B40" t="n">
-        <v>98387</v>
+        <v>98354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4956,17 +4947,26 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721546</v>
+        <v>721601</v>
       </c>
       <c r="R40" t="n">
-        <v>6380552</v>
+        <v>6380518</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5033,7 +5033,7 @@
         <v>127265579</v>
       </c>
       <c r="B41" t="n">
-        <v>106067</v>
+        <v>106031</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5132,57 +5132,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127265623</v>
+        <v>127265545</v>
       </c>
       <c r="B42" t="n">
-        <v>98447</v>
+        <v>106031</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721199</v>
+        <v>721560</v>
       </c>
       <c r="R42" t="n">
-        <v>6380248</v>
+        <v>6380582</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5225,7 +5216,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5243,48 +5234,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127265545</v>
+        <v>127265623</v>
       </c>
       <c r="B43" t="n">
-        <v>106067</v>
+        <v>98414</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721560</v>
+        <v>721199</v>
       </c>
       <c r="R43" t="n">
-        <v>6380582</v>
+        <v>6380248</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5345,54 +5345,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127265571</v>
+        <v>127265534</v>
       </c>
       <c r="B44" t="n">
-        <v>98387</v>
+        <v>109260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721594</v>
+        <v>721493</v>
       </c>
       <c r="R44" t="n">
-        <v>6380563</v>
+        <v>6380446</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5459,7 +5450,7 @@
         <v>127265515</v>
       </c>
       <c r="B45" t="n">
-        <v>98447</v>
+        <v>98414</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,45 +5558,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127265534</v>
+        <v>127265571</v>
       </c>
       <c r="B46" t="n">
-        <v>109296</v>
+        <v>98354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721493</v>
+        <v>721594</v>
       </c>
       <c r="R46" t="n">
-        <v>6380446</v>
+        <v>6380563</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127265626</v>
+        <v>127265478</v>
       </c>
       <c r="B47" t="n">
-        <v>98387</v>
+        <v>98414</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,26 +5680,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721183</v>
+        <v>721212</v>
       </c>
       <c r="R47" t="n">
-        <v>6380248</v>
+        <v>6380346</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127265597</v>
+        <v>127265626</v>
       </c>
       <c r="B48" t="n">
-        <v>98387</v>
+        <v>98354</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5824,13 +5824,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721557</v>
+        <v>721183</v>
       </c>
       <c r="R48" t="n">
-        <v>6380422</v>
+        <v>6380248</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127265478</v>
+        <v>127265597</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>98354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,26 +5902,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721212</v>
+        <v>721557</v>
       </c>
       <c r="R49" t="n">
-        <v>6380346</v>
+        <v>6380422</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, sumpig med blåtåtel..</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127265593</v>
+        <v>127265628</v>
       </c>
       <c r="B50" t="n">
-        <v>98492</v>
+        <v>98354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,37 +6013,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721572</v>
+        <v>721173</v>
       </c>
       <c r="R50" t="n">
-        <v>6380434</v>
+        <v>6380248</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6104,10 +6113,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127265472</v>
+        <v>127265507</v>
       </c>
       <c r="B51" t="n">
-        <v>98492</v>
+        <v>98354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,21 +6124,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6148,13 +6157,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721232</v>
+        <v>721307</v>
       </c>
       <c r="R51" t="n">
-        <v>6380313</v>
+        <v>6380360</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6215,10 +6224,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127265628</v>
+        <v>127265593</v>
       </c>
       <c r="B52" t="n">
-        <v>98387</v>
+        <v>98459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6226,46 +6235,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721173</v>
+        <v>721572</v>
       </c>
       <c r="R52" t="n">
-        <v>6380248</v>
+        <v>6380434</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127265507</v>
+        <v>127265472</v>
       </c>
       <c r="B53" t="n">
-        <v>98387</v>
+        <v>98459</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6370,13 +6370,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721307</v>
+        <v>721232</v>
       </c>
       <c r="R53" t="n">
-        <v>6380360</v>
+        <v>6380313</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>127296631</v>
       </c>
       <c r="B54" t="n">
-        <v>43235</v>
+        <v>43228</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>127265583</v>
       </c>
       <c r="B55" t="n">
-        <v>106067</v>
+        <v>106031</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6660,32 +6660,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127265622</v>
+        <v>127265494</v>
       </c>
       <c r="B56" t="n">
-        <v>103925</v>
+        <v>98458</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220164</v>
+        <v>219862</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6700,17 +6700,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721252</v>
+        <v>721247</v>
       </c>
       <c r="R56" t="n">
-        <v>6380274</v>
+        <v>6380342</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6771,45 +6771,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127265471</v>
+        <v>127265484</v>
       </c>
       <c r="B57" t="n">
-        <v>106067</v>
+        <v>98354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721232</v>
+        <v>721220</v>
       </c>
       <c r="R57" t="n">
-        <v>6380313</v>
+        <v>6380355</v>
       </c>
       <c r="S57" t="n">
         <v>7</v>
@@ -6873,32 +6882,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127265494</v>
+        <v>127265622</v>
       </c>
       <c r="B58" t="n">
-        <v>98491</v>
+        <v>103889</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219862</v>
+        <v>220164</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6913,17 +6922,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721247</v>
+        <v>721252</v>
       </c>
       <c r="R58" t="n">
-        <v>6380342</v>
+        <v>6380274</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6987,7 +6996,7 @@
         <v>127265481</v>
       </c>
       <c r="B59" t="n">
-        <v>109296</v>
+        <v>109260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7086,54 +7095,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127265484</v>
+        <v>127265471</v>
       </c>
       <c r="B60" t="n">
-        <v>98387</v>
+        <v>106031</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721220</v>
+        <v>721232</v>
       </c>
       <c r="R60" t="n">
-        <v>6380355</v>
+        <v>6380313</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -7197,62 +7197,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127265617</v>
+        <v>127265505</v>
       </c>
       <c r="B61" t="n">
-        <v>98491</v>
+        <v>106031</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721357</v>
+        <v>721284</v>
       </c>
       <c r="R61" t="n">
-        <v>6380338</v>
+        <v>6380359</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7313,57 +7299,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127265517</v>
+        <v>127265488</v>
       </c>
       <c r="B62" t="n">
-        <v>98447</v>
+        <v>106031</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721330</v>
+        <v>721231</v>
       </c>
       <c r="R62" t="n">
-        <v>6380365</v>
+        <v>6380342</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7424,45 +7401,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127265505</v>
+        <v>127265474</v>
       </c>
       <c r="B63" t="n">
-        <v>106067</v>
+        <v>98354</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721284</v>
+        <v>721232</v>
       </c>
       <c r="R63" t="n">
-        <v>6380359</v>
+        <v>6380313</v>
       </c>
       <c r="S63" t="n">
         <v>7</v>
@@ -7526,48 +7512,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127265488</v>
+        <v>127265504</v>
       </c>
       <c r="B64" t="n">
-        <v>106067</v>
+        <v>98354</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721231</v>
+        <v>721272</v>
       </c>
       <c r="R64" t="n">
-        <v>6380342</v>
+        <v>6380356</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7631,7 +7626,7 @@
         <v>127265495</v>
       </c>
       <c r="B65" t="n">
-        <v>98447</v>
+        <v>98414</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7739,37 +7734,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127265504</v>
+        <v>127265533</v>
       </c>
       <c r="B66" t="n">
-        <v>98387</v>
+        <v>99187</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7779,17 +7774,17 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721272</v>
+        <v>721484</v>
       </c>
       <c r="R66" t="n">
-        <v>6380356</v>
+        <v>6380450</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7850,10 +7845,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127265474</v>
+        <v>127265617</v>
       </c>
       <c r="B67" t="n">
-        <v>98387</v>
+        <v>98458</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7861,26 +7856,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7888,19 +7883,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721232</v>
+        <v>721357</v>
       </c>
       <c r="R67" t="n">
-        <v>6380313</v>
+        <v>6380338</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7961,10 +7961,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127265546</v>
+        <v>127265517</v>
       </c>
       <c r="B68" t="n">
-        <v>98387</v>
+        <v>98414</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7972,26 +7972,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721560</v>
+        <v>721330</v>
       </c>
       <c r="R68" t="n">
-        <v>6380582</v>
+        <v>6380365</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med löv.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8072,37 +8072,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127265533</v>
+        <v>127265546</v>
       </c>
       <c r="B69" t="n">
-        <v>99220</v>
+        <v>98354</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222361</v>
+        <v>223591</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721484</v>
+        <v>721560</v>
       </c>
       <c r="R69" t="n">
-        <v>6380450</v>
+        <v>6380582</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med löv.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8186,7 +8186,7 @@
         <v>127265525</v>
       </c>
       <c r="B70" t="n">
-        <v>98447</v>
+        <v>98414</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>127265476</v>
       </c>
       <c r="B71" t="n">
-        <v>98387</v>
+        <v>98354</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127265586</v>
+        <v>127265528</v>
       </c>
       <c r="B72" t="n">
-        <v>98492</v>
+        <v>98354</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721591</v>
+        <v>721460</v>
       </c>
       <c r="R72" t="n">
-        <v>6380497</v>
+        <v>6380438</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8521,45 +8521,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127265526</v>
+        <v>127265586</v>
       </c>
       <c r="B73" t="n">
-        <v>109296</v>
+        <v>98459</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721433</v>
+        <v>721591</v>
       </c>
       <c r="R73" t="n">
-        <v>6380417</v>
+        <v>6380497</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8592,11 +8601,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8628,54 +8632,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127265528</v>
+        <v>127265526</v>
       </c>
       <c r="B74" t="n">
-        <v>98387</v>
+        <v>109260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>721460</v>
+        <v>721433</v>
       </c>
       <c r="R74" t="n">
-        <v>6380438</v>
+        <v>6380417</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8708,6 +8703,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8739,45 +8739,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127265588</v>
+        <v>127265535</v>
       </c>
       <c r="B75" t="n">
-        <v>109296</v>
+        <v>98459</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721591</v>
+        <v>721493</v>
       </c>
       <c r="R75" t="n">
-        <v>6380497</v>
+        <v>6380446</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8841,54 +8850,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127265535</v>
+        <v>127265588</v>
       </c>
       <c r="B76" t="n">
-        <v>98492</v>
+        <v>109260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721493</v>
+        <v>721591</v>
       </c>
       <c r="R76" t="n">
-        <v>6380446</v>
+        <v>6380497</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8952,48 +8952,57 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127265513</v>
+        <v>127265508</v>
       </c>
       <c r="B77" t="n">
-        <v>109296</v>
+        <v>98414</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721315</v>
+        <v>721307</v>
       </c>
       <c r="R77" t="n">
-        <v>6380362</v>
+        <v>6380360</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9054,57 +9063,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127265508</v>
+        <v>127265513</v>
       </c>
       <c r="B78" t="n">
-        <v>98447</v>
+        <v>109260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2028, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2027, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721307</v>
+        <v>721315</v>
       </c>
       <c r="R78" t="n">
-        <v>6380360</v>
+        <v>6380362</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9165,57 +9165,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127265489</v>
+        <v>127265493</v>
       </c>
       <c r="B79" t="n">
-        <v>98387</v>
+        <v>106031</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>721231</v>
+        <v>721247</v>
       </c>
       <c r="R79" t="n">
         <v>6380342</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9276,27 +9267,27 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127265491</v>
+        <v>127265605</v>
       </c>
       <c r="B80" t="n">
-        <v>106067</v>
+        <v>109260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9307,17 +9298,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721239</v>
+        <v>721466</v>
       </c>
       <c r="R80" t="n">
-        <v>6380330</v>
+        <v>6380394</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9378,48 +9369,57 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127265493</v>
+        <v>127265489</v>
       </c>
       <c r="B81" t="n">
-        <v>106067</v>
+        <v>98354</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721247</v>
+        <v>721231</v>
       </c>
       <c r="R81" t="n">
         <v>6380342</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9480,27 +9480,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127265605</v>
+        <v>127265491</v>
       </c>
       <c r="B82" t="n">
-        <v>109296</v>
+        <v>106031</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9511,17 +9511,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:30 (2) A 8645-2025, Gtl</t>
+          <t>Norrlanda Broe 1:30 (2) A 8645-2029, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721466</v>
+        <v>721239</v>
       </c>
       <c r="R82" t="n">
-        <v>6380394</v>
+        <v>6380330</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>127296632</v>
       </c>
       <c r="B83" t="n">
-        <v>43235</v>
+        <v>43228</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>127265549</v>
       </c>
       <c r="B84" t="n">
-        <v>106067</v>
+        <v>106031</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>127265511</v>
       </c>
       <c r="B85" t="n">
-        <v>106067</v>
+        <v>106031</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9912,10 +9912,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265572</v>
+        <v>127265499</v>
       </c>
       <c r="B86" t="n">
-        <v>98447</v>
+        <v>98354</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9923,26 +9923,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+    